--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -323,8 +323,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K45" headerRowCount="1">
-  <autoFilter ref="A1:K45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K47" headerRowCount="1">
+  <autoFilter ref="A1:K47"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2960,40 +2960,99 @@
     <row r="41" ht="72" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>M-07</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>November 7, 2025</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Minutes Falsification</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Legal + Ethics</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish (author/distributor); Sharon Kunitz (presiding officer)</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Fiduciary duty to maintain accurate organizational records; Nonprofit corporate record standards; State law on corporate minute accuracy; Robert's Rules of Order — accurate record of motions and votes</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>The November 7, 2025 board meeting minutes (distributed Mar 9, 2026, four months late) state: 'Secretary Treasurer's Report: The current report with financial summary was approved as presented.'
+The audio recording at timestamp 25:52 shows that Grealish mentioned the budget was 'prepared for 26/27' as a passing remark tacked onto the end of the designated accounts motion — no document was presented, no figures discussed, no motion made, no second, no vote. The only thing formally voted on in the Secretary-Treasurer's report section was the Mary Scofield CPA designated accounts motion, which the minutes do record separately.
+The 'approved as presented' language for the financial summary and budget is FABRICATED and appears nowhere in the audio recording. This fictitious approval retroactively authorizes Grealish's $1,750 annual honorarium for another fiscal year without a real vote. Chip had raised written questions about the honorarium on October 31, 2025 ('Has your honorarium increased through the years as our membership has decreased? What are the measures for your honorarium?') — questions that were never answered. The false minutes entry serves to lock in that compensation without board action.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Audio Recording Nov 7, 2025, timestamp 25:52 — Grealish's remark without any motion, second, or vote; Nov 7 Minutes (distributed Mar 9, 2026) — falsified 'approved as presented' language; Oct 31, 2025 email — Chip's written questions about honorarium (thread ID: 19a3309ed58127ac); Audio recording ~46 minutes total — full context of Secretary-Treasurer's report section (no other votes on budget/financial summary)</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Minutes state a budget and financial summary were 'approved as presented,' but the audio recording proves no such motion or vote occurred. Minutes are a binding legal record of board action. A false entry that retroactively authorizes officer compensation constitutes falsification of corporate records — particularly when the fabrication appears 4 months after the meeting, after litigation has commenced.</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Audio-verified falsification — fabricated approval language contradicted by full recording</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>F-16</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Due Nov 15, 2019 — still overdue as of Oct 2025</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Regulatory Failure + False Statement</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Legal + Ethics</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>NM Nonprofit Corporation Act — annual report filing requirement with NM Secretary of State; Fiduciary duty of accurate regulatory compliance; Prohibition on false statements in official organizational records</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>On October 23, 2025, attorney Kathy Black reviewed PMTNM's NM Secretary of State business records and found: 'PMTNM's annual report is way overdue, with the due date listed as November 15, 2019.' The NM Secretary of State annual report has not been filed in over SIX YEARS.
 This directly contradicts a statement in PMTNM's own internal financial documents (Budget Documents, drafts approved by Board): 'All federal, state and local required documents and lists have been prepared and filed.' If this statement appeared in a report adopted by the board, it constitutes a false certification in an official organizational record — either Grealish failed to file and knew it, or she represented compliance to the board falsely.
@@ -3001,177 +3060,246 @@
 Also relevant: the NM AG Charitable Organization Registration (F-12) listed the organization as filing a 990-N and reporting 'solicited funds in NM: No.' The Secretary of State lapse compounds the regulatory picture: PMTNM has not maintained compliance with the most basic state corporate filing requirement since 2019, while Grealish continues to execute contracts (F-13: VIP Staffing, Oct 2025) and spend organizational funds as if the organization is in good standing.</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Kathy Black email to Chip Oct 23, 2025: 'according to New Mexico Secretary of State business records, PMTNM's annual report is way overdue, with the due date listed as November 15, 2019'; Kathy Black email Oct 30, 2025: 'At the very least, I am going to point out that the State of New Mexico annual report has not been filed'; PMTNM internal document ('Budget Documents, drafts approved by Board (1).pdf' in Drive — PMTNM folder): 'All federal, state and local required documents and lists have been prepared and filed' — DIRECT CONTRADICTION of Secretary of State records; NM Secretary of State public business records (verifiable)</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>PMTNM has been operating for 6+ years without filing its required NM Secretary of State annual report. Its own internal financial documents affirmatively claim all required filings are current — a false statement in an official record. This is simultaneously a regulatory failure, a false representation to the board, and evidence that Grealish's self-reported compliance ('The Executive Secretary-Treasurer shall be responsible for... filing of all returns with IRS, NM Taxation and Revenue Department, the NM State Corporation Commission, and any other government entity') has not been fulfilled.</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Attorney-identified + contradicted by PMTNM's own internal document</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="72" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>F-12</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Tax Year 2018 (filed ~2019); Tax Year 2023 (filed Dec 18, 2024)</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Tax Year 2018 (filed ~2019); Tax Year 2023 (filed Dec 18, 2024); Tax Year 2024 (filed Dec 12, 2025)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Regulatory / Sole Control</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>NM Attorney General Charitable Organization Registration requirements; IRS NTEE classification accuracy; NM Solicitation Disclosure Act; NM Nonprofit Corporation Act — officer record accuracy</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>TWO YEARS OF NM AG FILINGS REVIEWED — IDENTICAL SOLE-CONTROL PATTERN ACROSS SIX YEARS:
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>THREE YEARS OF NM AG FILINGS REVIEWED — IDENTICAL SOLE-CONTROL PATTERN ACROSS DECADE:
 TAX YEAR 2018 (filed ~2019):
 (1) Grealish sole responsible party for ALL FIVE financial functions. (2) PMTNM registered address = Grealish's personal home. (3) NTEE misclassification: A6B (Singing &amp; Choral Groups) — incorrect for a music TEACHERS professional association. (4) Revenue $18,817 vs. expenses $22,649 — operating deficit. (5) 'Solicited funds in NM: No' — appears false; PMTNM collects dues, conference fees, foundation contributions.
 TAX YEAR 2023 (FY 7/1/2023–6/30/2024, submitted Dec 18, 2024, status 'Registration Submitted' — not fully approved):
-(1) Grealish STILL sole responsible party for ALL FIVE functions: check signer, fund raising, fund distribution, financial records custody, and fund custody — no other officer listed for any function. (2) PMTNM address STILL Grealish's personal home: 1226 Morningside Dr NE, Albuquerque NM 87110. All officers listed at same personal address. (3) Officers listed: Larry Blind (President, $0), Jeanne Grealish (EST, $1,750), Cheryl Pachak-Brooks (Vice President, $0). CHIP MILLER NOT LISTED AS VP — but this is technically accurate: Chip became VP in August 2024, which falls in Tax Year 2024 (FY 7/1/2024–6/30/2025), not Tax Year 2023. Cheryl Pachak-Brooks WAS VP during FY 2023-2024. The filing is period-accurate. (4) 990-N filer. Revenue $15,819; Expenses $15,589; Net Assets end of year: $62,500; Contributions: $1,854. (5) Accountant: Mary Scofield, self-employed (not a CPA firm), 1308 Alcazar NE — all financial reporting routed through a sole self-employed accountant with no institutional independence. (6) 'Solicited funds in NM: No' — STILL false; Solicitation Methods listed as 'Special Events, Personal Contact' — direct internal contradiction within the same filing. (7) NTEE still includes A6B.</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>NM AG Registration Tax Year 2018 (physical PDF: 20184721935751263.pdf); NM AG Registration Tax Year 2023 (physical PDF: 20234722435369467 (2).pdf), FEIN 85-0284938, submitted Dec 18, 2024; VP appointment email from Sharon Kunitz, Aug 14, 2024 — establishes Chip's VP status four months before the Dec 2024 filing; IRS BMF confirming 990-N filer; Internal financial records (DocsFromJeanne) and Kathy Black Initial Impressions confirming same sole-control pattern 2024-2025</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Two independent NM AG filings six years apart show IDENTICAL sole-control structure. The 2023 filing, submitted four months after Chip was appointed VP, lists Cheryl Pachak-Brooks as VP and omits Chip entirely. The 'solicited funds in NM: No' false statement appears in BOTH filings despite documented solicitation activity. Combined with F-16 (NM SOS annual report overdue since 2019) and the Tax Year 2023 filing accurately reflects Cheryl as VP for that fiscal year, this is a pattern of inaccurate regulatory filings maintained while Grealish retains exclusive financial control.</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>TWO physical documents reviewed — six-year pattern confirmed at NM AG level</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>F-13</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Oct 23, 2025</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Unauthorized Contract</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Legal + Governance</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>Nonprofit governance — contracts above a de minimis threshold require board authorization; PMTNM Handbook on financial authority; Fiduciary duty</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>On October 23, 2025, PMTNM entered into a Master Terms &amp; Conditions agreement with VIP Staffing — a commercial staffing agency. Three versions of this contract are preserved in Google Drive (draft, executed, and a third copy), all dated Oct 23, 2025. PMTNM is identified as the 'Customer.' For a nonprofit that (a) filed 990-N (revenue under $50K threshold), (b) had FY2018 revenue of only $18,817, (c) claims in the NM AG filing it does not solicit funds, and (d) operates from Grealish's personal home — entering a commercial staffing contract is a significant financial and legal commitment. No board vote authorizing this contract appears in any board minutes. The Nov 7, 2025 board meeting (the only documented board meeting during this period) contains no reference to a staffing contract. Grealish, as sole financial officer, appears to have executed this agreement unilaterally.</t>
+(1) Grealish STILL sole responsible party for ALL FIVE functions: check signer, fund raising, fund distribution, financial records custody, and fund custody — no other officer listed for any function. (2) PMTNM address STILL Grealish's personal home: 1226 Morningside Dr NE, Albuquerque NM 87110. All officers listed at same personal address. (3) Officers listed: Larry Blind (President, $0), Jeanne Grealish (EST, $1,750), Cheryl Pachak-Brooks (Vice President, $0). CHIP MILLER NOT LISTED AS VP — but this is technically accurate: Chip became VP in August 2024, which falls in Tax Year 2024 (FY 7/1/2024–6/30/2025), not Tax Year 2023. Cheryl Pachak-Brooks WAS VP during FY 2023-2024. The filing is period-accurate. (4) 990-N filer. Revenue $15,819; Expenses $15,589; Net Assets end of year: $62,500; Contributions: $1,854. (5) Accountant: Mary Scofield, self-employed (not a CPA firm), 1308 Alcazar NE — all financial reporting routed through a sole self-employed accountant with no institutional independence. (6) 'Solicited funds in NM: No' — STILL false; Solicitation Methods listed as 'Special Events, Personal Contact' — direct internal contradiction within the same filing. (7) NTEE still includes A6B.
+TAX YEAR 2024 (FY 7/1/2024–6/30/2025, filed Dec 12, 2025 — after lawsuit filed Jan 27, 2026):
+(1) All five financial functions REMAIN solely Grealish. (2) Net assets declined from $62,500 to $60,555 (continuing decade-long decline from $81,975 in 2014 — total erosion of $21,420 or 26%). (3) Total gross revenue $7,114 (down 70% from $23,963 in 2014). (4) Total contributions $0.00 despite 'Special Events' and 'Personal Contact' listed as solicitation methods. (5) 'Solicited funds in NM: No' answered false for the eleventh consecutive year — systematic false statement across the entire regulatory history. (6) Chip Miller (Vice President) listed on filing. (7) This filing was submitted after the lawsuit was filed, suggesting a document created under legal awareness.</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Google Drive: '2025-10-23T16-25-09.000Z - 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1OGc7fLQguB3-ZDiqXpuUxF83sK2Rcy-L); '2025-10-23T16-49-03.000Z - Executed 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1nQAsasqmpAAk9d3-ZZJum3j4a70G92kZ); Nov 7, 2025 Board Meeting minutes and audio — no reference to any staffing contract; No board resolution authorizing staffing agreement found</t>
+          <t>NM AG Registration Tax Year 2018 (physical PDF: 20184721935751263.pdf); NM AG Registration Tax Year 2023 (physical PDF: 20234722435369467 (2).pdf); NM AG Registration Tax Year 2024 (filed Dec 12, 2025), FEIN 85-0284938; VP appointment email from Sharon Kunitz, Aug 14, 2024 — establishes Chip's VP status; IRS BMF confirming 990-N filer; Internal financial records (DocsFromJeanne) and Kathy Black Initial Impressions confirming same sole-control pattern 2024-2025</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>A commercial staffing contract executed without board authorization — by the sole financial officer of a nonprofit operating at a deficit. The contract requires PMTNM to carry Comprehensive General Liability Insurance and Employment Practices Liability Insurance. Whether PMTNM actually maintains this insurance is unknown. The agreement also contains a one-year non-solicitation clause that would bind PMTNM as an organization. This is precisely the kind of significant financial obligation that requires board authorization under standard nonprofit governance.</t>
+          <t>Three independent NM AG filings across a decade show IDENTICAL sole-control structure. The 'solicited funds in NM: No' false statement appears in all three filings despite documented solicitation activity — a systematic misrepresentation maintained throughout the regulatory history. The Tax Year 2024 filing (submitted after the lawsuit was filed) documents that Chip Miller was the VP during that year, yet all financial control remained with Grealish. Net assets and revenue continue their decade-long decline while officer compensation (Grealish honorarium) increased from 6.3% to 24.6% of revenue — compensation rising as the organization shrinks.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Physical contracts reviewed in Drive — no board authorization documented</t>
+          <t>THREE physical documents reviewed — entire decade pattern confirmed at NM AG level</t>
         </is>
       </c>
     </row>
     <row r="44" ht="72" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Oct 23, 2025</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Contract</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Legal + Governance</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Nonprofit governance — contracts above a de minimis threshold require board authorization; PMTNM Handbook on financial authority; Fiduciary duty</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>On October 23, 2025, PMTNM entered into a Master Terms &amp; Conditions agreement with VIP Staffing — a commercial staffing agency. Three versions of this contract are preserved in Google Drive (draft, executed, and a third copy), all dated Oct 23, 2025. PMTNM is identified as the 'Customer.' For a nonprofit that (a) filed 990-N (revenue under $50K threshold), (b) had FY2018 revenue of only $18,817, (c) claims in the NM AG filing it does not solicit funds, and (d) operates from Grealish's personal home — entering a commercial staffing contract is a significant financial and legal commitment. No board vote authorizing this contract appears in any board minutes. The Nov 7, 2025 board meeting (the only documented board meeting during this period) contains no reference to a staffing contract. Grealish, as sole financial officer, appears to have executed this agreement unilaterally.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Google Drive: '2025-10-23T16-25-09.000Z - 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1OGc7fLQguB3-ZDiqXpuUxF83sK2Rcy-L); '2025-10-23T16-49-03.000Z - Executed 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1nQAsasqmpAAk9d3-ZZJum3j4a70G92kZ); Nov 7, 2025 Board Meeting minutes and audio — no reference to any staffing contract; No board resolution authorizing staffing agreement found</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>A commercial staffing contract executed without board authorization — by the sole financial officer of a nonprofit operating at a deficit. The contract requires PMTNM to carry Comprehensive General Liability Insurance and Employment Practices Liability Insurance. Whether PMTNM actually maintains this insurance is unknown. The agreement also contains a one-year non-solicitation clause that would bind PMTNM as an organization. This is precisely the kind of significant financial obligation that requires board authorization under standard nonprofit governance.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Physical contracts reviewed in Drive — no board authorization documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="72" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>F-17</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing (documented 2014–2025); FY2024–25 Authorization Denied</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Financial / Officer Compensation</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Legal + Governance</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish (recipient); Sharon Kunitz (presiding officer, failed oversight); Larry Blind (Nominating Chair, failed oversight)</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Nonprofit governance — officer compensation requires board approval; PMTNM Handbook duties for EST and President; Fiduciary duty to manage organizational resources; NM corporate law — board's duty to authorize material expenses</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Grealish (Executive Secretary-Treasurer) has received annual compensation ('honorarium') of at least $1,500 (Tax Year 2014) rising to $1,750 (Tax Year 2024), disclosed in NM AG filings but never appearing in IRS records because PMTNM files 990-N. The sole financial controller of all five functions (check signing, fundraising, fund distribution, financial records, custody of funds) is the same person receiving this compensation. No independent oversight exists.
+In fiscal year 2024–25 (the year Chip served as VP), the budget containing this compensation was never formally voted on by the board:
+— The 'Budget Committee REMINDER' process (Oct 31–Nov 6, 2025) was entirely email-based, not a formal meeting
+— Larry Blind approved it by reply-all email on Nov 2 ('The budget looks ok to me')
+— The November 7 board meeting contained no motion, second, or vote on the budget — audio confirmed at timestamp 25:52 (passing remark, not a motion)
+— The minutes' 'approved as presented' language is falsified (see M-07)
+Since the budget was never formally approved by the board in FY2024–25, Grealish's $1,750 honorarium for that year was paid without authorization.
+SALARY VS. REVENUE TRAJECTORY (from NM AG filings):
+— Tax Year 2014: $1,500 salary / $23,963 revenue = 6.3%
+— Tax Year 2024: $1,750 salary / $7,114 revenue = 24.6%
+As membership and revenue collapsed 70% over a decade, Grealish's share of organizational revenue nearly quadrupled. The Tax Year 2024 NM AG filing (submitted December 12, 2025 — after the lawsuit was filed) shows $1,750 compensation resting on a board approval the audio recording and minutes contradiction prove never happened.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>NM AG Registration filings Tax Year 2014–2024 (pattern documented); Oct 31–Nov 6, 2025 'Budget Committee REMINDER' email thread (Gmail ID: 19a3309ed58127ac); Nov 7, 2025 Audio Recording, timestamp 25:52 — no motion or vote on budget; Nov 7, 2025 Minutes (distributed Mar 9, 2026): falsified 'approved as presented' language (see M-07); NM AG Tax Year 2024 filing (submitted Dec 12, 2025) showing $1,750 compensation; Revenue data from IRS EO BMF and NM AG filings 2014–2024</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>A manager received continuous compensation without formal board authorization in the final fiscal year reviewed. The email-based budget process bypassed handbook requirements (F-02). The Nov 7 board meeting produced no motion to approve the budget — only a fabricated minutes entry (M-07). The compensation increased from 6.3% to 24.6% of declining revenue, while the sole financial officer remained unilaterally in control. This is foundational financial governance failure.</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Audio-verified (no motion), Minutes-contradicted (fabricated approval), NM AG-documented (11-year pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="72" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>G-02</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Nov 7, 2025 (pre-meeting emails + meeting)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Anonymous Voting Suppressed + No Confidence Motion Defeated</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Governance + Ethics</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Larry Blind (procedural suppression); Sharon Kunitz (adjournment); Jeanne Grealish (subject of motion, present during vote call)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Robert's Rules of Order Newly Revised 12th ed. §§45:5–7, 46:32–34 (ballot voting must preserve anonymity); Robert's Rules §4 (main motions); Nonprofit governance — board members' duty to consider officer accountability motions</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>TWO-PART VIOLATION — PRE-MEETING SUPPRESSION AND IN-MEETING PROCEDURAL DEFEAT:
 PART 1: ANONYMOUS VOTING SYSTEM PREPARED AND IGNORED (Nov 7, morning, Gmail thread: 19a5ea6717e3582c)
@@ -3183,62 +3311,63 @@
 - With all in-person attendees fully visible to each other
 - Without any reference to the anonymous voting system Chip had prepared
 No one seconded. Motion died. Sharon adjourned immediately.
-Larry's 10:00 AM comment ('getting someone to the point of a motion can be challenging') was written before the meeting as a preview of his strategy — not a neutral procedural observation. The anonymous voting system was the correct remedy under RROO and was available. Its non-use ensured the vote occurred under maximum social pressure.</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+Larry's 10:00 AM comment ('getting someone to the point of a motion can be challenging') was written before the meeting as a preview of his strategy — not a neutral procedural observation. The anonymous voting system was the correct remedy under RROO and was available. Its non-use ensured the vote occurred under maximum social pressure.
+TRIGGER CONFIRMED: The Nov 6 pre-meeting coordination (Larry's 10:00 AM anonymous voting rejection, ElectionChamp setup by 10:55 AM, Cheryl briefed by evening) was preceded by Grealish forwarding Chip's retirement request to MTNA national office (Brian Shepard) and her attorney (Karen Kilgore) on Nov 5, 2025 at 7:03 PM. The sequence shows: Chip asks Grealish to retire in Nov 5 meeting → Grealish escalates to MTNA and attorney same evening → coordinated pre-meeting suppression activity begins Nov 6 morning. The anonymous voting suppression was not spontaneous — it followed a deliberate escalation the prior evening.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Gmail thread 19a5ea6717e3582c — full pre-meeting exchange: Sharon 7:07 AM (time limits); Chip 8:54 AM (anonymous voting proposal, RROO citation, two platforms offered); Larry 10:00 AM (dismissive, to Sharon only: 'getting someone to the point of a motion can be challenging'); Larry 10:11 AM (text-to-one-phone counter-proposal — not anonymous); Chip 10:27 AM (explains why Larry's method fails RROO ballot standards); Chip 10:55 AM ('ElectionChamp is set up'  — 15 board member emails loaded, test sent); Nov 7 Audio Recording 46:34–49:13: motion made, public hand-raise call, no second, motion dies; Sharon 49:13: adjourns</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>A proper anonymous voting system was live and ready. Larry rejected it that morning in favor of a non-anonymous alternative, then ran the vote publicly with the subject of the motion in the room. Members who might have seconded the motion anonymously were instead exposed to full social and professional visibility. The motion's failure cannot be separated from the voting environment Larry created and the anonymous option he suppressed.</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Email-verified pre-meeting + Audio-verified in-meeting — anonymous voting deliberately bypassed</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="72" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Email-verified pre-meeting + Audio-verified in-meeting — anonymous voting deliberately bypassed — Trigger: Nov 5, 7:03 PM forward to MTNA/attorney preceded Nov 6 coordination</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="72" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>L-07</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Nov 7, 2025 (and ongoing 2024-2025)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Conflict of Interest / Structural Governance</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Ethics + Governance + Procedural</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Larry Blind (three simultaneous conflicting roles); Sharon Kunitz (failed to manage or disclose)</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>PMTNM Handbook 2004 Section VII-Q (Nominating Committee chaired by Immediate Past President — controls VP succession); Section VI-C (President duty: 'keeps a close liaison with all officers' and should allocate duties to VP — not fulfilled while receiving exclusive advisory counsel from Past President); Robert's Rules of Order — Parliamentarian must be impartial and free of conflicts; Standard nonprofit governance — board members holding multiple conflicting roles must disclose them</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>At the November 7, 2025 board meeting and in the weeks leading up to it, Larry Blind simultaneously held THREE distinct roles — none of which were disclosed as conflicting and none of which had any handbook-defined boundaries or recusal process:
 (1) PAST PRESIDENT / INFORMAL ADVISOR TO SHARON: The 2004 PMTNM Handbook Section VI defines duties for State President, Vice President, EST, and District VPs. The Past President is NOT defined in Section VI. The advisory relationship is conventional — meaning no handbook language defines its scope, limits, or conflict-of-interest requirements. This gave Larry an unconstrained, informal advisory channel to Sharon with no procedural safeguards.
@@ -3249,17 +3378,17 @@
 NO CONFLICT DISCLOSURE, NO RECUSAL, NO PROCEDURE: There is no PMTNM conflict-of-interest policy in the handbook. No disclosure of Larry's three simultaneous roles was made at the Nov 7 meeting. No recusal procedure existed. Larry ruled on parliamentary questions at the same meeting where he had been advising the President against the VP and where he controlled the VP successor nomination process.</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>2004 PMTNM Handbook Section VII-Q (Nominating Committee: Past President chairs by convention — not formally defined in Section VI); 2004 Handbook Section VI-C (President duties: 'Keeps a close liaison with all officers' — not extended to VP during Larry's advisory relationship); Nov 7, 2025 10:00 AM email from Larry — reply to Sharon only, not Chip (Gmail thread 19a5ea6717e3582c): 'There may be a lot of talking, but getting someone to the point of a motion can be challenging' — advisory communication bypassing VP; Nov 7 Audio Recording: Larry as Parliamentarian ruling on procedural questions; Nov 7 Minutes: Larry named as Parliamentarian; Nov 5-6 hostile email from Larry to Chip (L-04): 'offensive, disrespectful, and does not deserve a response' — demonstrates pre-existing personal animus that preceded his impartial parliamentary role; No conflict-of-interest policy found in 2004 PMTNM Handbook</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>Three simultaneous conflicting roles — advisor, succession controller, parliamentary authority — held without disclosure or recusal. The informal advisory channel had no handbook boundaries. Larry's 10:00 AM email proves the advisory channel was used to coordinate meeting strategy against the VP hours before the meeting. Parliamentary rulings at Nov 7 were made by a person who had been advising the President in that direction since at least 10 AM. The Nominating Committee process is further compromised by Larry's documented financial conflicts (L-01 through L-06) and his use of organizational roles for personal and commercial benefit.</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Handbook-verified + Email evidence (10:00 AM advisory communication) + Audio record — three undisclosed simultaneous roles</t>
         </is>
@@ -3279,7 +3408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3317,7 +3446,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Financial records refusal — VP refused access to records (Mar 2025)</t>
+          <t>Financial records refusal — VP refused access to records (Mar 2025); attorney demand under statute refused (Oct 2025)</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3475,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>F-14</t>
+          <t>F-17</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized spending Jul–Nov 2025: 4+ months into fiscal year with no approved budget; continued storage, honorarium, and operating expenses without board authorization</t>
+          <t>Officer compensation without board authorization — $1,750 honorarium in FY2024–25 paid under falsified budget approval; compensation 24.6% of shrinking revenue (up from 6.3% a decade ago)</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3492,12 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CPA report 5 months late; budget adopted after fiscal year began</t>
+          <t>Unauthorized spending Jul–Nov 2025: 4+ months into fiscal year with no approved budget; continued storage, honorarium, and operating expenses without board authorization</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3509,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Financial report 'approved' in minutes — no motion/vote in recording</t>
+          <t>CPA report 5 months late; budget adopted after fiscal year began</t>
         </is>
       </c>
     </row>
@@ -3397,12 +3526,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>F-05</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Sole control of all bank accounts, CPA contact, financial records</t>
+          <t>Financial report 'approved' in minutes — no motion/vote in recording</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3543,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Personal furniture stored in PMTNM storage unit — admitted before attorney</t>
+          <t>Sole control of all bank accounts, CPA contact, financial records</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3560,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>EST honorarium $1,750/yr with no performance measures</t>
+          <t>Personal furniture stored in PMTNM storage unit — admitted before attorney</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3577,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>F-08</t>
+          <t>F-07</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Stated Teri Reck 'hadn't contributed' — potentially inaccurate/defamatory</t>
+          <t>EST honorarium $1,750/yr with no performance measures</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3594,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>F-09</t>
+          <t>F-08</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Blocked membership booklet: '90 cents to mail' vs. 30%+ budget on storage</t>
+          <t>Stated Teri Reck 'hadn't contributed' — potentially inaccurate/defamatory</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3611,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>F-10</t>
+          <t>F-09</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Storage unit: $4,600 actual vs. $3,000 budgeted — 53% overrun; even Larry questioned it</t>
+          <t>Blocked membership booklet: '90 cents to mail' vs. 30%+ budget on storage</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3628,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-10</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2025 TOTY: Three attempts to nullify Terri Reck nomination; directly contradicted by board members</t>
+          <t>Storage unit: $4,600 actual vs. $3,000 budgeted — 53% overrun; even Larry questioned it</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3645,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Auditing Committee unilaterally eliminated — written admission to Kathy Black: 'It has not had an Auditing Comm. since hiring a CPA'</t>
+          <t>2025 TOTY: Three attempts to nullify Terri Reck nomination; directly contradicted by board members</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3662,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Board meeting minutes stored in storage unit (with personal furniture); attorney demand for records refused as 'not physically possible'; no online banking</t>
+          <t>Auditing Committee unilaterally eliminated — written admission to Kathy Black: 'It has not had an Auditing Comm. since hiring a CPA'</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3679,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>F-15</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>No spring board meeting or budget committee in spring 2025; budget prepared 4 months into fiscal year — handbook requires spring preparation</t>
+          <t>Board meeting minutes stored in storage unit (with personal furniture); attorney demand for records refused as 'not physically possible'; no online banking</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3696,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>F-16</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>NM Secretary of State annual report overdue since Nov 15, 2019 — 6+ year lapse; internal PMTNM document claims 'all required documents have been filed' — direct contradiction</t>
+          <t>Minutes falsification (Nov 7, 2025): budget 'approved as presented' — audio shows no motion, second, or vote; minutes fabricated to lock in unauthorized $1,750 honorarium</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3713,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-15</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NM AG registration (2018 + 2023): sole responsible party for all 5 financial functions BOTH years; PMTNM address = personal home both years; 'no solicitation' false both years; decade-long pattern confirmed — same false statement in all 10 years of filings (2014-2024)</t>
+          <t>No spring board meeting or budget committee in spring 2025; budget prepared 4 months into fiscal year — handbook requires spring preparation</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3730,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>F-13</t>
+          <t>F-16</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>VIP Staffing contract (Oct 23, 2025): commercial staffing agreement executed without board authorization; no mention in Nov 7 minutes</t>
+          <t>NM Secretary of State annual report overdue since Nov 15, 2019 — 6+ year lapse; internal PMTNM document claims 'all required documents have been filed' — direct contradiction</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3747,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ON RECORD Oct 7, 2025: 'PMTNM does not function under any legal mandates!'</t>
+          <t>NM AG registration (2018, 2023, 2024): sole responsible party for all 5 financial functions all three years; PMTNM address = personal home all three years; 'no solicitation' false all three years; eleven-year pattern confirmed (2014-2024)</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3764,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>F-13</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Nov 7, 2025: vote of no confidence motion made formally; Larry controlled the second process; Sharon adjourned immediately after motion died; Grealish (subject of motion) had direct conflict of interest</t>
+          <t>VIP Staffing contract (Oct 23, 2025): commercial staffing agreement executed without board authorization; no mention in Nov 7 minutes</t>
         </is>
       </c>
     </row>
@@ -3652,12 +3781,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Minutes: '10-min limit' — Sharon's own email says 15 min</t>
+          <t>ON RECORD Oct 7, 2025: 'PMTNM does not function under any legal mandates!'</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3798,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Minutes: financial report 'approved' — no vote in recording</t>
+          <t>Nov 7, 2025: vote of no confidence motion made formally; Larry controlled the second process; Sharon adjourned immediately after motion died; Grealish (subject of motion) had direct conflict of interest; escalation to MTNA/attorney Nov 5 preceded coordination</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3815,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Minutes: 'time called by Parliamentarian' — not in recording</t>
+          <t>Minutes: '10-min limit' — Sharon's own email says 15 min</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3832,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Minutes: VP report 'not submitted' — contradicted by documentary evidence</t>
+          <t>Minutes: financial report 'approved' — no vote in recording</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3849,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Handbook withheld for 6 months; falsely claimed online availability</t>
+          <t>Minutes: 'time called by Parliamentarian' — not in recording</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3866,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Nov 7 minutes distributed 4 months late — after petition filed</t>
+          <t>Minutes: VP report 'not submitted' — contradicted by documentary evidence</t>
         </is>
       </c>
     </row>
@@ -3754,46 +3883,46 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Handbook withheld for 6 months; falsely claimed online availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish (EST)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Nov 7 minutes distributed 4 months late — after petition filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish (EST)</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
           <t>R-03</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Spring 2025 minutes not distributed for 7 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>L-01</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>TOTY manipulation: used business email to solicit votes for his own employee Tatiana</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>L-02</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3934,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>L-01</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>PMTNM website used to promote NM School of Music during his presidency</t>
+          <t>TOTY manipulation: used business email to solicit votes for his own employee Tatiana</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3951,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-02</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
+          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3968,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
+          <t>PMTNM website used to promote NM School of Music during his presidency</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3985,12 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
+          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
         </is>
       </c>
     </row>
@@ -3873,12 +4002,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
+          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
         </is>
       </c>
     </row>
@@ -3890,12 +4019,12 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
+          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
         </is>
       </c>
     </row>
@@ -3907,12 +4036,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
+          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
         </is>
       </c>
     </row>
@@ -3924,46 +4053,46 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Larry Blind (Past President / NMSM Owner)</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>E-04</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Larry Blind (Past President / NMSM Owner)</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
           <t>L-07</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Triple role conflict Nov 7, 2025: Past President/informal advisor to Sharon + Nominating Committee Chair + Parliamentarian — three undisclosed simultaneous conflicting roles; advisory channel used morning of Nov 7 to coordinate meeting strategy against VP (10:00 AM email to Sharon only: 'getting someone to the point of a motion can be challenging')</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (Former President)</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (Former President)</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>S-02</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
         </is>
       </c>
     </row>
@@ -3975,12 +4104,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
+          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -3992,12 +4121,12 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
+          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4138,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
         </is>
       </c>
     </row>
@@ -4026,46 +4155,46 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
+          <t>S-04</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz (Former President)</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz (Former President)</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
           <t>M-05</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>VP excluded from board packet mailing; VP's agenda items not addressed</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Nov 2023 ethics complaint — no action</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
         </is>
       </c>
     </row>
@@ -4077,10 +4206,44 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Nov 2023 ethics complaint — no action</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Brian Shepard (MTNA CEO)</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Brian Shepard (MTNA CEO)</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
           <t>E-03</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Sep 2025 + Dec 2025 affiliate complaints — deferred entirely to affiliate self-governance</t>
         </is>
@@ -4097,7 +4260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4701,34 +4864,40 @@
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Oct 31, 2025</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Board</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Budget Committee REMINDER</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Chip asks formal budget questions — most ignored. Larry witnesses.</t>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Oct 31–Nov 6, 2025</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish; Larry Blind; Sharon Kunitz; Chip Miller</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Grealish, Chip, Larry, Sharon, Heather Nasi, Laura Spitzer; CC to Kathy Black and Karen Kilgore (Grealish's attorney)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Budget Committee REMINDER — Email-based budget approval &amp; pre-litigation coordination (Gmail thread: 19a3c6e590c51011)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>F-02, F-17, G-02, M-07</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — FOUR DISTINCT VIOLATIONS IN SINGLE THREAD:
+(1) EMAIL-BASED BUDGET PROCESS BYPASSES HANDBOOK: Grealish: 'This method of arriving at a proposed budget has worked well for several years' — no formal Budget Committee meeting held. Handbook (Art. IX §2) requires VP as committee member; handbook (Section VI-B) requires formal Executive Board meeting approval. Neither occurred. Oct 31–Nov 6 exchange is purely email.
+(2) LARRY'S RUBBER-STAMP APPROVAL (F-02, F-17): Nov 2, 2025 — Larry replies 'The budget looks ok to me' to the thread, explicitly saying questions 'do not alter the basis for approving the budget as presented.' This is neither a motion nor formal approval — it's a casual reply-all email from the Past President about a budget containing Grealish's $1,750 honorarium (F-17).
+(3) CHIP'S UNANSWERED QUESTIONS ABOUT HONORARIUM COMPENSATION (F-17): Oct 31 — Chip formally asks: 'Has your honorarium increased through the years as our membership has decreased? What are the measures for your honorarium?' Sharon's response is dismissive: 'Are you a CPA or Finance expert? You have not been a member long enough to know the operations of PMTNM.' The questions were never answered. The honorarium was approved (falsely per M-07) one week later without addressing Chip's concerns.
+(4) ESCALATION TO ATTORNEYS TRIGGERS COORDINATION (G-02): Nov 5, 7:03 PM — Grealish forwards Chip's retirement request email to Brian Shepard (MTNA national) and Karen Kilgore (Grealish's attorney). This event preceded the Nov 6 pre-meeting coordination. Hours later, Nov 6 morning emails show Larry rejecting anonymous voting and Sharon setting up meeting structure (pre-litigation coordination documented in G-02).
+(5) KATHY BLACK DISCOVERY: Nov 6 — Grealish had forwarded the entire thread to both MTNA and her attorney. Kathy Black (Chip's counsel) learned from Chip that he was being opposed by coordinated parties and that Grealish had already retained legal counsel and looped in MTNA.
+RESULT: Budget 'approved' via email with no formal motion or vote. Nov 7 minutes falsified the approval (M-07). Officer compensation (F-17) authorized without genuine board action. Anonymous voting suppressed on Nov 6 morning in response to Nov 5 escalation (G-02).</t>
         </is>
       </c>
     </row>
@@ -4740,153 +4909,185 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Budget Committee REMINDER (condensed)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Chip asks formal budget questions — most ignored. Larry witnesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Oct 31, 2025</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>Sharon Kunitz</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Kathy Black (cc: Board)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>PMTNM position</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Sharon disclaims PMTNM involvement in dispute — written to Chip's attorney.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Nov 4, 2025 1:14:51</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (on recording)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Meeting attendees</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Nov 4 Finance Meeting — agenda commitment</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>S-03</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — Sharon says 'I'll put them on the agenda.' Confirmed by Kathy Black email same day at 2:54 PM.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Nov 4, 2025 2:54 PM</t>
+          <t>Nov 4, 2025 1:14:51</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Kathy Black</t>
+          <t>Sharon Kunitz (on recording)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller</t>
+          <t>Meeting attendees</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Follow-Up to Today's Meeting</t>
+          <t>Nov 4 Finance Meeting — agenda commitment</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>S-03, E-01</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Attorney confirms Sharon's agenda commitment + Grealish attorney surprise appearance.</t>
+          <t>CRITICAL — Sharon says 'I'll put them on the agenda.' Confirmed by Kathy Black email same day at 2:54 PM.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
+          <t>Nov 4, 2025 2:54 PM</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Kathy Black</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Chip Miller</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Follow-Up to Today's Meeting</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>S-03, E-01</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — Attorney confirms Sharon's agenda commitment + Grealish attorney surprise appearance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
           <t>Nov 5–6, 2025</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Larry Blind</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Chip Miller (cc: Sharon, Jeanne, Laura)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Willis Glen Miller, III</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>L-04</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Larry hostile email night before board meeting. Then serves as Parliamentarian.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Nov 6, 2025 (11:40 AM – 10:15 PM)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Cheryl Pachak-Brooks → Chip Miller</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>wgmilleriii@gmail.com</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>PMTNM concerns (Gmail thread: 19a5a7881ce060db)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>L-04, S-03</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>HIGH — PRE-MEETING CHARACTER COORDINATION: Cheryl Pachak-Brooks (former VP, no current board role) contacted Chip the day before the Nov 7 board meeting, having been briefed by an undisclosed party. Cheryl's opening: 'I have been made aware of your issues with PMTNM and Jeanne' and 'When I heard about everything that has transpired, my first thought was, he is trying to dismantle the association. I really regretted suggesting you get involved.' Her language (attacking, cruel, dismantling) mirrors exactly the characterizations used by Grealish/Sharon/Larry — indicating she was briefed by one or more of them before reaching out.
 Chip offered twice to share his documentation and offered a phone call. Cheryl declined both: 'I have heard several sides and been apprised of all that is going on. I know there are two sides, I am just suggesting you step above the fray.' She formed a conclusion without hearing his evidence.
@@ -4895,609 +5096,609 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Nov 7, 2025 7:07 AM</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Board (Larry, Laura)</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Additional RRoo wisdom!</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>M-01</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — Sharon's own email establishes 15-min rule. Minutes later say 10 min.</t>
-        </is>
-      </c>
-    </row>
     <row r="26" ht="54" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Nov 7, 2025 (pre-meeting, 7:07–10:55 AM)</t>
+          <t>Nov 7, 2025 7:07 AM</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Sharon Kunitz / Chip Miller / Larry Blind</t>
+          <t>Sharon Kunitz</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>All officers</t>
+          <t>Board (Larry, Laura)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Additional RRoo wisdom! — Anonymous voting exchange (Gmail thread: 19a5ea6717e3582c)</t>
+          <t>Additional RRoo wisdom!</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>L-04, G-02</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Chip set up ElectionChamp anonymous voting (RROO §§45:5–7, 46:32–34 compliant) and sent test election to all 15 board member emails by 10:55 AM. Larry counter-proposed text-to-one-phone (not anonymous — one person sees all votes). Chip explained why this fails RROO ballot standards. Larry's 10:00 AM reply to Sharon (ignoring Chip's proposal): 'There may be a lot of talking, but getting someone to the point of a motion can be challenging' — hours before the meeting, telegraphing his plan to prevent the motion procedurally. System was ready and never used. Vote of no confidence run as public hand-raise instead.</t>
+          <t>CRITICAL — Sharon's own email establishes 15-min rule. Minutes later say 10 min.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
+          <t>Nov 7, 2025 (pre-meeting, 7:07–10:55 AM)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz / Chip Miller / Larry Blind</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>All officers</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Additional RRoo wisdom! — Anonymous voting exchange (Gmail thread: 19a5ea6717e3582c)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>L-04, G-02</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — Chip set up ElectionChamp anonymous voting (RROO §§45:5–7, 46:32–34 compliant) and sent test election to all 15 board member emails by 10:55 AM. Larry counter-proposed text-to-one-phone (not anonymous — one person sees all votes). Chip explained why this fails RROO ballot standards. Larry's 10:00 AM reply to Sharon (ignoring Chip's proposal): 'There may be a lot of talking, but getting someone to the point of a motion can be challenging' — hours before the meeting, telegraphing his plan to prevent the motion procedurally. System was ready and never used. Vote of no confidence run as public hand-raise instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
           <t>Nov 7, 2025 (meeting)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Audio recording</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Full board</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Nov 7 Board Meeting</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>M-01 through M-05, F-04, L-04, G-02</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Full audio record. Contradicts minutes on 8 documented points. Key sequences: (1) Chip: 'I have no packet' [32:28] — excluded from board materials. (2) Grealish identifies VP report but says 'It cannot be board reports, because I don't have anything to include' [33:18]. (3) Larry copies report, then questions authorship as delay tactic [34:11]. (4) Sharon attempts adjournment without covering Chip's agenda items [41:30]. (5) Voice: 'You didn't send that' — Sharon immediately contradicts: 'two months ago, March 17, thank you' [42:43–42:52]. (6) Chip makes formal motion of no confidence [46:34]. (7) Larry controls second process, no one seconds, motion dies [48:04–49:00]. (8) Sharon adjourns [49:13]. Minutes: 'Old Business: None. New Business: None.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Sep 23 + Dec 23, 2025</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Chip Miller</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>PMTNM Ethics/Compliance Complaints</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Third and fourth complaints to MTNA. Shepard defers to affiliate self-governance.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="54" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Mar 9, 2026</t>
+          <t>Sep 23 + Dec 23, 2025</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Jeanne Grealish</t>
+          <t>Chip Miller</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Full board (Larry, Laura, Chip)</t>
+          <t>Brian Shepard (MTNA CEO)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>PMTNM MINUTES</t>
+          <t>PMTNM Ethics/Compliance Complaints</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Minutes distributed 4 months late — after petition filed, after response filed.</t>
+          <t>Third and fourth complaints to MTNA. Shepard defers to affiliate self-governance.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="54" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>Mar 9, 2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Full board (Larry, Laura, Chip)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PMTNM MINUTES</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Minutes distributed 4 months late — after petition filed, after response filed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>Mar 13, 2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Chip Miller</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Laura Spitzer</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>November 7 Board Meeting Minutes</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>M-01 through M-05</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Chip formally raises minutes inaccuracies with new president. No substantive reply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="54" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Sep 11, 2025</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>admin@pmtnm.org (Chip)</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Re: PMTNM | MTNA | The Foundation</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>S-05</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — Grealish: 'Boring and irrelevant to most of us.' Response to MTNA Foundation newsletter. Dismissive tone toward MTNA's core charitable mission.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="54" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Sep 12, 2025 12:44 AM</t>
+          <t>Sep 11, 2025</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller</t>
+          <t>Jeanne Grealish</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Grealish + Brian Shepard + Sharon Kunitz</t>
+          <t>admin@pmtnm.org (Chip)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Fwd: PMTNM | MTNA | The Foundation</t>
+          <t>Re: PMTNM | MTNA | The Foundation</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>S-05, E-03</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Chip forwards Jeanne's 'Boring and irrelevant' email to Sharon, asking 'Hi Jeanne, can you clarify?' Sharon was explicitly CC'd. Sharon said nothing.</t>
+          <t>CRITICAL — Grealish: 'Boring and irrelevant to most of us.' Response to MTNA Foundation newsletter. Dismissive tone toward MTNA's core charitable mission.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="54" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Oct 2, 2025</t>
+          <t>Sep 12, 2025 12:44 AM</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Sharon Kunitz</t>
+          <t>Chip Miller</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller (CC: Jeanne, Larry, Laura)</t>
+          <t>Grealish + Brian Shepard + Sharon Kunitz</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>Fwd: PMTNM | MTNA | The Foundation</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-05, E-03</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL CONTRAST — Sharon: 'Great article on Foundation! Beautifully written and presented.' — 21 days after receiving Jeanne's 'Boring and irrelevant' email and saying nothing.</t>
+          <t>CRITICAL — Chip forwards Jeanne's 'Boring and irrelevant' email to Sharon, asking 'Hi Jeanne, can you clarify?' Sharon was explicitly CC'd. Sharon said nothing.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="54" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Oct 7, 2025</t>
+          <t>Oct 2, 2025</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Jeanne Grealish → Chip, Sharon, Laura, Larry, Heather Nasi</t>
+          <t>Sharon Kunitz</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>All officers</t>
+          <t>Chip Miller (CC: Jeanne, Larry, Laura)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Re: Foundation. RE: BUDGET — 'No legal mandates' email (Gmail thread: 199c0d60237afa6c)</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>F-02, G-01, F-14</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — THE FULL CONTEXT: Chip had asked about the budget committee meeting. Grealish responded: 'There probably will be no need for an actual meeting.' Then: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!' This was a direct, specific rejection of the handbook's budget committee provisions — not a philosophical aside. ALL FIVE OFFICERS received this email.</t>
+          <t>CRITICAL CONTRAST — Sharon: 'Great article on Foundation! Beautifully written and presented.' — 21 days after receiving Jeanne's 'Boring and irrelevant' email and saying nothing.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="54" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Oct 23, 2025</t>
+          <t>Oct 7, 2025</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Kathy Black (Atty.) → Chip Miller</t>
+          <t>Jeanne Grealish → Chip, Sharon, Laura, Larry, Heather Nasi</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller</t>
+          <t>All officers</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Initial Impressions — NM Secretary of State annual report overdue since 2019</t>
+          <t>Re: Foundation. RE: BUDGET — 'No legal mandates' email (Gmail thread: 199c0d60237afa6c)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>F-16, F-05</t>
+          <t>F-02, G-01, F-14</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Kathy Black: 'according to New Mexico Secretary of State business records, PMTNM's annual report is way overdue, with the due date listed as November 15, 2019.' Found within days of beginning review of PMTNM records. Also noted: 'You've done a tremendous amount of work in a short period of time. Impressive.' — attorney acknowledgment of Chip's documentation effort. PMTNM's own financial documents state 'All federal, state and local required documents and lists have been prepared and filed' — a direct false statement contradicted by the Secretary of State public record.</t>
+          <t>CRITICAL — THE FULL CONTEXT: Chip had asked about the budget committee meeting. Grealish responded: 'There probably will be no need for an actual meeting.' Then: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!' This was a direct, specific rejection of the handbook's budget committee provisions — not a philosophical aside. ALL FIVE OFFICERS received this email.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="54" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Oct 29, 2025</t>
+          <t>Oct 23, 2025</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Kathy Black (Atty.) → Grealish; Grealish private letter → Kathy Black</t>
+          <t>Kathy Black (Atty.) → Chip Miller</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Forwarded to Chip Oct 30</t>
+          <t>Chip Miller</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Attorney demand + Grealish private response (Gmail thread: 19a3309ed58127ac)</t>
+          <t>Initial Impressions — NM Secretary of State annual report overdue since 2019</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>F-01, A-01, M-06, F-05</t>
+          <t>F-16, F-05</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Kathy Black formally demanded records under NMSA §53-8-27 by Oct 31. Grealish's private response (forwarded to Chip by Kathy): 'It is not physically possible for me to bring the requested items to your office on Friday.' 'PMTNM does not do online banking.' 'PMTNM does not have a separate Finance Committee. It has not had an Auditing Comm. since hiring a CPA.' 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings.' 'Current files...bank statements for all seven accounts...are kept in my home office at 1226 Morningside Dr. NE.' This single letter is Grealish's own written description of PMTNM's governance structure — sole home control, no audit committee, minutes in storage, no online access. Attorney-witnessed.</t>
+          <t>CRITICAL — Kathy Black: 'according to New Mexico Secretary of State business records, PMTNM's annual report is way overdue, with the due date listed as November 15, 2019.' Found within days of beginning review of PMTNM records. Also noted: 'You've done a tremendous amount of work in a short period of time. Impressive.' — attorney acknowledgment of Chip's documentation effort. PMTNM's own financial documents state 'All federal, state and local required documents and lists have been prepared and filed' — a direct false statement contradicted by the Secretary of State public record.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="54" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
+          <t>Oct 29, 2025</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Kathy Black (Atty.) → Grealish; Grealish private letter → Kathy Black</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Forwarded to Chip Oct 30</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Attorney demand + Grealish private response (Gmail thread: 19a3309ed58127ac)</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>F-01, A-01, M-06, F-05</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — Kathy Black formally demanded records under NMSA §53-8-27 by Oct 31. Grealish's private response (forwarded to Chip by Kathy): 'It is not physically possible for me to bring the requested items to your office on Friday.' 'PMTNM does not do online banking.' 'PMTNM does not have a separate Finance Committee. It has not had an Auditing Comm. since hiring a CPA.' 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings.' 'Current files...bank statements for all seven accounts...are kept in my home office at 1226 Morningside Dr. NE.' This single letter is Grealish's own written description of PMTNM's governance structure — sole home control, no audit committee, minutes in storage, no online access. Attorney-witnessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
           <t>Oct 29–31, 2025</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Jeanne Grealish → Budget Committee</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Sharon, Larry, Chip, Heather Nasi (CC: Laura)</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>PMTNM FY report and Proposed Budget for 2025-2026 (Gmail thread: 19a3309ed58127ac)</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>F-02, F-03, F-14</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Budget and CPA report sent 4 months into fiscal year. Grealish: 'In recent years instead of meeting we have worked via email since there were few adjustments to the budget draft.' Kathy Black: 'the organization is not following the handbook regarding committees' and 'the State of New Mexico annual report has not been filed.' Bank balances as of Oct 29: General Fund $17,475.18, Money Market $9,719.58, Joyce Walker $23,942.38, Student Travel $3,086.85, Danfelser $2,707.14, Weed $467.55, Composition $939.76, Jane Snow $2,346.73. Total: $60,685.17 + Danfelser CD $3,969.51.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="54" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>2025 (TOTY cycle)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Board</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>2025 TOTY Nomination — Terri Reck</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>HIGH — Grealish made 3 attempts to nullify Terri Reck's TOTY nomination. Stated Reck 'has not contributed very much to community service.' Immediately contradicted by board members who seconded Reck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="54" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Pre-Nov 7, 2025</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Chip Miller</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>President + EST</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>VP Report Submitted to President and EST</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>M-04, G-01, F-11</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — VP Report submitted in advance of Nov 7 meeting. Directly contradicts minutes claim that 'VP report had not been submitted.' Preserved on Google Drive (ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="54" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
+          <t>Pre-Nov 7, 2025</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Chip Miller</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>President + EST</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>VP Report Submitted to President and EST</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>M-04, G-01, F-11</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — VP Report submitted in advance of Nov 7 meeting. Directly contradicts minutes claim that 'VP report had not been submitted.' Preserved on Google Drive (ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
           <t>Sep 30, 2023</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Lawrence Blind (lawrenceblind@msn.com)</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>PMTNM (submitted as TOTY nomination)</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>TOTY Nomination — Tatiana Vetrinskaya [PHYSICAL PDF REVIEWED]</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>L-05, E-04</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Larry submitted Tatiana's nomination from his PERSONAL email (not NMSM employer email, unlike his vote solicitation). Tatiana's listed email is tatiana@nmschoolofmusic.com. Community service section = entirely NMSM activities. Future-tense item listed as achievement: 'will present a workshop at 2023 PMTNM Conference.' Closing attribute: 'business acumen — it is what I know she is most proud of.' This phrase ('I know she is most proud of') reveals Larry wrote it — a nominee does not describe herself this way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="54" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Sep 30, 2023</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Jacqueline Zander-Wall (zanderwall@gmail.com)</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>PMTNM (submitted as TOTY nomination)</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>TOTY Nomination — Terri Reck [PHYSICAL PDF REVIEWED]</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>L-05, E-04, F-11</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>HIGH — Zander-Wall submitted Reck's nomination. Terri Reck: 47 years teaching (1976–2023), Dalcroze certification across 6 institutions, 5 AMTA committee leadership roles, harpsichordist with SF Symphony / NM Symphony / NM Philharmonic, students in PMTNM/MTNA programs, Music Bowl Chair for decades, jewelry donated to PMTNM silent auctions. Every criterion directly met. This is the nomination that lost to Larry's 'storybook language' submission.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="54" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Tax Year 2018</t>
+          <t>Sep 30, 2023</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>NM Attorney General</t>
+          <t>Jacqueline Zander-Wall (zanderwall@gmail.com)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>PMTNM (FEIN 85-0284938)</t>
+          <t>PMTNM (submitted as TOTY nomination)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>NM AG Charitable Organization Registration Tax Year 2018 [PHYSICAL DOCUMENT REVIEWED]</t>
+          <t>TOTY Nomination — Terri Reck [PHYSICAL PDF REVIEWED]</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>F-05, F-12</t>
+          <t>L-05, E-04, F-11</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>HIGH — 2018 filing: Grealish sole responsible party for all 5 financial functions; PMTNM address = personal home; NTEE = A6B (misclassification); FY2018 revenue $18,817 vs. expenses $22,649 (deficit); 'Solicited funds in NM: No' (appears inaccurate). See also 2023 filing entry below.</t>
+          <t>HIGH — Zander-Wall submitted Reck's nomination. Terri Reck: 47 years teaching (1976–2023), Dalcroze certification across 6 institutions, 5 AMTA committee leadership roles, harpsichordist with SF Symphony / NM Symphony / NM Philharmonic, students in PMTNM/MTNA programs, Music Bowl Chair for decades, jewelry donated to PMTNM silent auctions. Every criterion directly met. This is the nomination that lost to Larry's 'storybook language' submission.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="54" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t>Tax Year 2018</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>NM Attorney General</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>PMTNM (FEIN 85-0284938)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>NM AG Charitable Organization Registration Tax Year 2018 [PHYSICAL DOCUMENT REVIEWED]</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>F-05, F-12</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>HIGH — 2018 filing: Grealish sole responsible party for all 5 financial functions; PMTNM address = personal home; NTEE = A6B (misclassification); FY2018 revenue $18,817 vs. expenses $22,649 (deficit); 'Solicited funds in NM: No' (appears inaccurate). See also 2023 filing entry below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="54" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>Oct 23, 2025</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish (executing for PMTNM)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>VIP Staffing</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>VIP Staffing Master Terms &amp; Conditions — Executed [PHYSICAL CONTRACT REVIEWED]</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>F-13</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>HIGH — Commercial staffing contract executed by Grealish for PMTNM on Oct 23, 2025. Three copies in Drive (draft + executed + third copy). Requires PMTNM to carry GL and EPLI insurance. Contains 1-year non-solicitation clause binding on PMTNM. No board authorization in any minutes. Nov 7 board meeting (17 days later) contains no reference to this contract.</t>
         </is>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Apr 25, 2025</t>
+          <t>Apr 28, 2025</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Financial Irregularity</t>
+          <t>Unsupported Negative Characterization</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1140,27 +1140,27 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Basic fiduciary duty; Accurate financial reporting</t>
+          <t>Board fiduciary duty; Professional conduct; Accurate characterization of member contributions</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>At the Spring 2025 Board Meeting, Grealish stated that board member Teri Reck 'hadn't contributed.' This characterization of a fellow board member's financial contributions was made in a board meeting — potentially inaccurate and defamatory.</t>
+          <t>During TOTY award discussion, Grealish made an unsupported negative characterization of Teri Reck's contributions: 'I believe the reason Terry Rett was not posted last time was she has not contributed very much to community service.' This claim was immediately contradicted by board members Chip Miller and Sharon Kunitz, who pointed to Reck's actual contributions: workshop leadership, conference activities, fundraising, and 47 years of teaching. The comment demonstrates problematic board governance — unsupported negative statements made during award decision processes can marginalize members and skew institutional recognition. See F-11 for pattern context (back-to-back TOTY suppression cycles).</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Spring 2025 Board Meeting transcript/notes</t>
+          <t>April 28, 2025 Board Meeting Audio &amp; Transcript: timestamp 01:39:00–01:39:35 (Grealish's claim at 01:39:00; Chip's contradiction at 01:39:35); Transcript lines 1851–1881 (redundant due to audio-to-text conversion artifacts); Teri Reck's own 2023 TOTY submission (PDF: Terri Reck.pdf, Gmail thread ID: 19239a27e03b7010) documenting actual contributions: 47 years teaching, Dalcroze certification, SF/NM Symphony harpsichordist, Music Bowl Chair, PMTNM silent auction donations</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>If inaccurate, this is a misrepresentation to the board about a member's standing. Potentially used to marginalize dissenting board members.</t>
+          <t>Unsupported negative characterization made during official board decision-making (TOTY award discussion). Immediately contradicted by fellow board members. Pattern evidence in F-11 shows back-to-back cycles of suppression targeting same individual.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>To be verified from transcript</t>
+          <t>Transcript-verified — Substantive challenge to characterization</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3312,16 @@
 - Without any reference to the anonymous voting system Chip had prepared
 No one seconded. Motion died. Sharon adjourned immediately.
 Larry's 10:00 AM comment ('getting someone to the point of a motion can be challenging') was written before the meeting as a preview of his strategy — not a neutral procedural observation. The anonymous voting system was the correct remedy under RROO and was available. Its non-use ensured the vote occurred under maximum social pressure.
-TRIGGER CONFIRMED: The Nov 6 pre-meeting coordination (Larry's 10:00 AM anonymous voting rejection, ElectionChamp setup by 10:55 AM, Cheryl briefed by evening) was preceded by Grealish forwarding Chip's retirement request to MTNA national office (Brian Shepard) and her attorney (Karen Kilgore) on Nov 5, 2025 at 7:03 PM. The sequence shows: Chip asks Grealish to retire in Nov 5 meeting → Grealish escalates to MTNA and attorney same evening → coordinated pre-meeting suppression activity begins Nov 6 morning. The anonymous voting suppression was not spontaneous — it followed a deliberate escalation the prior evening.</t>
+TRIGGER CONFIRMED: The Nov 6 pre-meeting coordination (Larry's 10:00 AM anonymous voting rejection, ElectionChamp setup by 10:55 AM, Cheryl briefed by evening) was preceded by Grealish forwarding Chip's retirement request to MTNA national office (Brian Shepard) and her attorney (Karen Kilgore) on Nov 5, 2025 at 7:03 PM. The sequence shows: Chip asks Grealish to retire in Nov 5 meeting → Grealish escalates to MTNA and attorney same evening → coordinated pre-meeting suppression activity begins Nov 6 morning. The anonymous voting suppression was not spontaneous — it followed a deliberate escalation the prior evening.
+2024 PRECEDENT — PERSONAL CELL PHONE VOTING (Gmail thread 1928ce26b2fe3d9c, approx. Oct 14, 2024):
+In 2024, the year before ElectionChamp was suppressed, the mechanism for online 'anonymous' voting was: board members should text their votes to Larry Blind's personal cell phone (505) 980-3941. The meeting was held at NM School of Music — Larry's own commercial school.
+WHY THIS IS NOT ANONYMOUS: Larry, as the sole recipient, could see every vote cast — identical in structure to his Nov 7, 2025 counter-proposal ('designate one person to receive the texts') that Chip rejected as non-anonymous under RROO §§45:5–7, 46:32–34. A vote-receiver who sees all votes before counting cannot provide the anonymity Robert's Rules requires for ballot votes.
+PATTERN ACROSS TWO CONSECUTIVE ELECTIONS: True anonymous voting was never available to online board members under Larry's administration. 2024: votes texted to Larry's personal cell at his own school. 2025: Chip's RROO-compliant ElectionChamp system (15 board members loaded, ready by 10:55 AM) was rejected by Larry that morning; vote run publicly instead with Grealish in the room. Two election cycles, zero genuine anonymous voting for online members. The 2025 suppression was not an oversight — it was a continuation of established practice.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Gmail thread 19a5ea6717e3582c — full pre-meeting exchange: Sharon 7:07 AM (time limits); Chip 8:54 AM (anonymous voting proposal, RROO citation, two platforms offered); Larry 10:00 AM (dismissive, to Sharon only: 'getting someone to the point of a motion can be challenging'); Larry 10:11 AM (text-to-one-phone counter-proposal — not anonymous); Chip 10:27 AM (explains why Larry's method fails RROO ballot standards); Chip 10:55 AM ('ElectionChamp is set up'  — 15 board member emails loaded, test sent); Nov 7 Audio Recording 46:34–49:13: motion made, public hand-raise call, no second, motion dies; Sharon 49:13: adjourns</t>
+          <t>Gmail thread 19a5ea6717e3582c — full pre-meeting exchange: Sharon 7:07 AM (time limits); Chip 8:54 AM (anonymous voting proposal, RROO citation, two platforms offered); Larry 10:00 AM (dismissive, to Sharon only: 'getting someone to the point of a motion can be challenging'); Larry 10:11 AM (text-to-one-phone counter-proposal — not anonymous); Chip 10:27 AM (explains why Larry's method fails RROO ballot standards); Chip 10:55 AM ('ElectionChamp is set up'  — 15 board member emails loaded, test sent); Nov 7 Audio Recording 46:34–49:13: motion made, public hand-raise call, no second, motion dies; Sharon 49:13: adjourns; Gmail thread 1928ce26b2fe3d9c — 'PMTNM Board and General Membership Meetings' (approx. Oct 14, 2024): Larry announces online members should text votes to personal cell (505) 980-3941; meeting held at NM School of Music (Larry's school) — establishes 2-year pattern of non-anonymous online voting</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4260,7 +4264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4834,62 +4838,96 @@
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Oct 14, 2024 (approx)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Larry Blind</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>PMTNM Board + General Membership</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>PMTNM Board and General Membership Meetings — cell phone voting announcement (Gmail thread: 1928ce26b2fe3d9c)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>HIGH — 2024 ANONYMOUS VOTING PRECEDENT: Larry announced that online members wishing to cast 'anonymous' secret ballot votes should text to his personal cell phone (505) 980-3941. Meeting held at NM School of Music — Larry's own commercial school.
+WHY THIS IS NOT ANONYMOUS: Larry, as the sole recipient, could see every vote cast — identical in structure to his Nov 7, 2025 counter-proposal ('designate one person to receive the texts, count the results, and then delete the texts') that Chip rejected as non-anonymous under RROO §§45:5–7, 46:32–34. A vote-receiver who sees all votes before counting cannot provide the anonymity Robert's Rules requires for ballot votes.
+PATTERN ACROSS TWO CONSECUTIVE ELECTIONS: 2024 — votes texted to Larry's personal cell at his own school. 2025 — Chip built a proper anonymous system (ElectionChamp, 15 board members loaded by 10:55 AM); Larry rejected it that morning and ran the no-confidence vote publicly instead with Grealish in the room. Two election cycles, zero genuine anonymous voting available to online members.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Oct 25–30, 2025</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Board (Larry, Chip, Laura)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>PMTNM Budget / FY Report</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>F-03</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>CPA report 5 months late. Budget confusion — Grealish unsure which year.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Oct 31–Nov 6, 2025</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Jeanne Grealish; Larry Blind; Sharon Kunitz; Chip Miller</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Grealish, Chip, Larry, Sharon, Heather Nasi, Laura Spitzer; CC to Kathy Black and Karen Kilgore (Grealish's attorney)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Budget Committee REMINDER — Email-based budget approval &amp; pre-litigation coordination (Gmail thread: 19a3c6e590c51011)</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>F-02, F-17, G-02, M-07</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — FOUR DISTINCT VIOLATIONS IN SINGLE THREAD:
 (1) EMAIL-BASED BUDGET PROCESS BYPASSES HANDBOOK: Grealish: 'This method of arriving at a proposed budget has worked well for several years' — no formal Budget Committee meeting held. Handbook (Art. IX §2) requires VP as committee member; handbook (Section VI-B) requires formal Executive Board meeting approval. Neither occurred. Oct 31–Nov 6 exchange is purely email.
@@ -4901,38 +4939,6 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Oct 31, 2025</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Board</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Budget Committee REMINDER (condensed)</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Chip asks formal budget questions — most ignored. Larry witnesses.</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -4941,153 +4947,185 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Budget Committee REMINDER (condensed)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Chip asks formal budget questions — most ignored. Larry witnesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Oct 31, 2025</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>Sharon Kunitz</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Kathy Black (cc: Board)</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>PMTNM position</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Sharon disclaims PMTNM involvement in dispute — written to Chip's attorney.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Nov 4, 2025 1:14:51</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (on recording)</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Meeting attendees</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Nov 4 Finance Meeting — agenda commitment</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>S-03</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — Sharon says 'I'll put them on the agenda.' Confirmed by Kathy Black email same day at 2:54 PM.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Nov 4, 2025 2:54 PM</t>
+          <t>Nov 4, 2025 1:14:51</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Kathy Black</t>
+          <t>Sharon Kunitz (on recording)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller</t>
+          <t>Meeting attendees</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Follow-Up to Today's Meeting</t>
+          <t>Nov 4 Finance Meeting — agenda commitment</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>S-03, E-01</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Attorney confirms Sharon's agenda commitment + Grealish attorney surprise appearance.</t>
+          <t>CRITICAL — Sharon says 'I'll put them on the agenda.' Confirmed by Kathy Black email same day at 2:54 PM.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>Nov 4, 2025 2:54 PM</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Kathy Black</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Chip Miller</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Follow-Up to Today's Meeting</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>S-03, E-01</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — Attorney confirms Sharon's agenda commitment + Grealish attorney surprise appearance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
           <t>Nov 5–6, 2025</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Larry Blind</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Chip Miller (cc: Sharon, Jeanne, Laura)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Willis Glen Miller, III</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>L-04</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Larry hostile email night before board meeting. Then serves as Parliamentarian.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Nov 6, 2025 (11:40 AM – 10:15 PM)</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Cheryl Pachak-Brooks → Chip Miller</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>wgmilleriii@gmail.com</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>PMTNM concerns (Gmail thread: 19a5a7881ce060db)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>L-04, S-03</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>HIGH — PRE-MEETING CHARACTER COORDINATION: Cheryl Pachak-Brooks (former VP, no current board role) contacted Chip the day before the Nov 7 board meeting, having been briefed by an undisclosed party. Cheryl's opening: 'I have been made aware of your issues with PMTNM and Jeanne' and 'When I heard about everything that has transpired, my first thought was, he is trying to dismantle the association. I really regretted suggesting you get involved.' Her language (attacking, cruel, dismantling) mirrors exactly the characterizations used by Grealish/Sharon/Larry — indicating she was briefed by one or more of them before reaching out.
 Chip offered twice to share his documentation and offered a phone call. Cheryl declined both: 'I have heard several sides and been apprised of all that is going on. I know there are two sides, I am just suggesting you step above the fray.' She formed a conclusion without hearing his evidence.
@@ -5096,609 +5134,609 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Nov 7, 2025 7:07 AM</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Board (Larry, Laura)</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Additional RRoo wisdom!</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>M-01</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — Sharon's own email establishes 15-min rule. Minutes later say 10 min.</t>
-        </is>
-      </c>
-    </row>
     <row r="27" ht="54" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Nov 7, 2025 (pre-meeting, 7:07–10:55 AM)</t>
+          <t>Nov 7, 2025 7:07 AM</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Sharon Kunitz / Chip Miller / Larry Blind</t>
+          <t>Sharon Kunitz</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>All officers</t>
+          <t>Board (Larry, Laura)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Additional RRoo wisdom! — Anonymous voting exchange (Gmail thread: 19a5ea6717e3582c)</t>
+          <t>Additional RRoo wisdom!</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>L-04, G-02</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Chip set up ElectionChamp anonymous voting (RROO §§45:5–7, 46:32–34 compliant) and sent test election to all 15 board member emails by 10:55 AM. Larry counter-proposed text-to-one-phone (not anonymous — one person sees all votes). Chip explained why this fails RROO ballot standards. Larry's 10:00 AM reply to Sharon (ignoring Chip's proposal): 'There may be a lot of talking, but getting someone to the point of a motion can be challenging' — hours before the meeting, telegraphing his plan to prevent the motion procedurally. System was ready and never used. Vote of no confidence run as public hand-raise instead.</t>
+          <t>CRITICAL — Sharon's own email establishes 15-min rule. Minutes later say 10 min.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
+          <t>Nov 7, 2025 (pre-meeting, 7:07–10:55 AM)</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz / Chip Miller / Larry Blind</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>All officers</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Additional RRoo wisdom! — Anonymous voting exchange (Gmail thread: 19a5ea6717e3582c)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>L-04, G-02</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — Chip set up ElectionChamp anonymous voting (RROO §§45:5–7, 46:32–34 compliant) and sent test election to all 15 board member emails by 10:55 AM. Larry counter-proposed text-to-one-phone (not anonymous — one person sees all votes). Chip explained why this fails RROO ballot standards. Larry's 10:00 AM reply to Sharon (ignoring Chip's proposal): 'There may be a lot of talking, but getting someone to the point of a motion can be challenging' — hours before the meeting, telegraphing his plan to prevent the motion procedurally. System was ready and never used. Vote of no confidence run as public hand-raise instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
           <t>Nov 7, 2025 (meeting)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Audio recording</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Full board</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Nov 7 Board Meeting</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>M-01 through M-05, F-04, L-04, G-02</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Full audio record. Contradicts minutes on 8 documented points. Key sequences: (1) Chip: 'I have no packet' [32:28] — excluded from board materials. (2) Grealish identifies VP report but says 'It cannot be board reports, because I don't have anything to include' [33:18]. (3) Larry copies report, then questions authorship as delay tactic [34:11]. (4) Sharon attempts adjournment without covering Chip's agenda items [41:30]. (5) Voice: 'You didn't send that' — Sharon immediately contradicts: 'two months ago, March 17, thank you' [42:43–42:52]. (6) Chip makes formal motion of no confidence [46:34]. (7) Larry controls second process, no one seconds, motion dies [48:04–49:00]. (8) Sharon adjourns [49:13]. Minutes: 'Old Business: None. New Business: None.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="54" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Sep 23 + Dec 23, 2025</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Chip Miller</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>PMTNM Ethics/Compliance Complaints</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Third and fourth complaints to MTNA. Shepard defers to affiliate self-governance.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="54" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Mar 9, 2026</t>
+          <t>Sep 23 + Dec 23, 2025</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Jeanne Grealish</t>
+          <t>Chip Miller</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Full board (Larry, Laura, Chip)</t>
+          <t>Brian Shepard (MTNA CEO)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>PMTNM MINUTES</t>
+          <t>PMTNM Ethics/Compliance Complaints</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Minutes distributed 4 months late — after petition filed, after response filed.</t>
+          <t>Third and fourth complaints to MTNA. Shepard defers to affiliate self-governance.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="54" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>Mar 9, 2026</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Full board (Larry, Laura, Chip)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>PMTNM MINUTES</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Minutes distributed 4 months late — after petition filed, after response filed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>Mar 13, 2026</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Chip Miller</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Laura Spitzer</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>November 7 Board Meeting Minutes</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>M-01 through M-05</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Chip formally raises minutes inaccuracies with new president. No substantive reply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Sep 11, 2025</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>admin@pmtnm.org (Chip)</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Re: PMTNM | MTNA | The Foundation</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>S-05</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — Grealish: 'Boring and irrelevant to most of us.' Response to MTNA Foundation newsletter. Dismissive tone toward MTNA's core charitable mission.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="54" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Sep 12, 2025 12:44 AM</t>
+          <t>Sep 11, 2025</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller</t>
+          <t>Jeanne Grealish</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Grealish + Brian Shepard + Sharon Kunitz</t>
+          <t>admin@pmtnm.org (Chip)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Fwd: PMTNM | MTNA | The Foundation</t>
+          <t>Re: PMTNM | MTNA | The Foundation</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>S-05, E-03</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Chip forwards Jeanne's 'Boring and irrelevant' email to Sharon, asking 'Hi Jeanne, can you clarify?' Sharon was explicitly CC'd. Sharon said nothing.</t>
+          <t>CRITICAL — Grealish: 'Boring and irrelevant to most of us.' Response to MTNA Foundation newsletter. Dismissive tone toward MTNA's core charitable mission.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="54" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Oct 2, 2025</t>
+          <t>Sep 12, 2025 12:44 AM</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Sharon Kunitz</t>
+          <t>Chip Miller</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller (CC: Jeanne, Larry, Laura)</t>
+          <t>Grealish + Brian Shepard + Sharon Kunitz</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>Fwd: PMTNM | MTNA | The Foundation</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-05, E-03</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL CONTRAST — Sharon: 'Great article on Foundation! Beautifully written and presented.' — 21 days after receiving Jeanne's 'Boring and irrelevant' email and saying nothing.</t>
+          <t>CRITICAL — Chip forwards Jeanne's 'Boring and irrelevant' email to Sharon, asking 'Hi Jeanne, can you clarify?' Sharon was explicitly CC'd. Sharon said nothing.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="54" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Oct 7, 2025</t>
+          <t>Oct 2, 2025</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Jeanne Grealish → Chip, Sharon, Laura, Larry, Heather Nasi</t>
+          <t>Sharon Kunitz</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>All officers</t>
+          <t>Chip Miller (CC: Jeanne, Larry, Laura)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Re: Foundation. RE: BUDGET — 'No legal mandates' email (Gmail thread: 199c0d60237afa6c)</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>F-02, G-01, F-14</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — THE FULL CONTEXT: Chip had asked about the budget committee meeting. Grealish responded: 'There probably will be no need for an actual meeting.' Then: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!' This was a direct, specific rejection of the handbook's budget committee provisions — not a philosophical aside. ALL FIVE OFFICERS received this email.</t>
+          <t>CRITICAL CONTRAST — Sharon: 'Great article on Foundation! Beautifully written and presented.' — 21 days after receiving Jeanne's 'Boring and irrelevant' email and saying nothing.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="54" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Oct 23, 2025</t>
+          <t>Oct 7, 2025</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Kathy Black (Atty.) → Chip Miller</t>
+          <t>Jeanne Grealish → Chip, Sharon, Laura, Larry, Heather Nasi</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Chip Miller</t>
+          <t>All officers</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Initial Impressions — NM Secretary of State annual report overdue since 2019</t>
+          <t>Re: Foundation. RE: BUDGET — 'No legal mandates' email (Gmail thread: 199c0d60237afa6c)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>F-16, F-05</t>
+          <t>F-02, G-01, F-14</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Kathy Black: 'according to New Mexico Secretary of State business records, PMTNM's annual report is way overdue, with the due date listed as November 15, 2019.' Found within days of beginning review of PMTNM records. Also noted: 'You've done a tremendous amount of work in a short period of time. Impressive.' — attorney acknowledgment of Chip's documentation effort. PMTNM's own financial documents state 'All federal, state and local required documents and lists have been prepared and filed' — a direct false statement contradicted by the Secretary of State public record.</t>
+          <t>CRITICAL — THE FULL CONTEXT: Chip had asked about the budget committee meeting. Grealish responded: 'There probably will be no need for an actual meeting.' Then: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!' This was a direct, specific rejection of the handbook's budget committee provisions — not a philosophical aside. ALL FIVE OFFICERS received this email.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="54" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Oct 29, 2025</t>
+          <t>Oct 23, 2025</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Kathy Black (Atty.) → Grealish; Grealish private letter → Kathy Black</t>
+          <t>Kathy Black (Atty.) → Chip Miller</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Forwarded to Chip Oct 30</t>
+          <t>Chip Miller</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Attorney demand + Grealish private response (Gmail thread: 19a3309ed58127ac)</t>
+          <t>Initial Impressions — NM Secretary of State annual report overdue since 2019</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>F-01, A-01, M-06, F-05</t>
+          <t>F-16, F-05</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>CRITICAL — Kathy Black formally demanded records under NMSA §53-8-27 by Oct 31. Grealish's private response (forwarded to Chip by Kathy): 'It is not physically possible for me to bring the requested items to your office on Friday.' 'PMTNM does not do online banking.' 'PMTNM does not have a separate Finance Committee. It has not had an Auditing Comm. since hiring a CPA.' 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings.' 'Current files...bank statements for all seven accounts...are kept in my home office at 1226 Morningside Dr. NE.' This single letter is Grealish's own written description of PMTNM's governance structure — sole home control, no audit committee, minutes in storage, no online access. Attorney-witnessed.</t>
+          <t>CRITICAL — Kathy Black: 'according to New Mexico Secretary of State business records, PMTNM's annual report is way overdue, with the due date listed as November 15, 2019.' Found within days of beginning review of PMTNM records. Also noted: 'You've done a tremendous amount of work in a short period of time. Impressive.' — attorney acknowledgment of Chip's documentation effort. PMTNM's own financial documents state 'All federal, state and local required documents and lists have been prepared and filed' — a direct false statement contradicted by the Secretary of State public record.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="54" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
+          <t>Oct 29, 2025</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Kathy Black (Atty.) → Grealish; Grealish private letter → Kathy Black</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Forwarded to Chip Oct 30</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Attorney demand + Grealish private response (Gmail thread: 19a3309ed58127ac)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>F-01, A-01, M-06, F-05</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — Kathy Black formally demanded records under NMSA §53-8-27 by Oct 31. Grealish's private response (forwarded to Chip by Kathy): 'It is not physically possible for me to bring the requested items to your office on Friday.' 'PMTNM does not do online banking.' 'PMTNM does not have a separate Finance Committee. It has not had an Auditing Comm. since hiring a CPA.' 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings.' 'Current files...bank statements for all seven accounts...are kept in my home office at 1226 Morningside Dr. NE.' This single letter is Grealish's own written description of PMTNM's governance structure — sole home control, no audit committee, minutes in storage, no online access. Attorney-witnessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
           <t>Oct 29–31, 2025</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Jeanne Grealish → Budget Committee</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Sharon, Larry, Chip, Heather Nasi (CC: Laura)</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>PMTNM FY report and Proposed Budget for 2025-2026 (Gmail thread: 19a3309ed58127ac)</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>F-02, F-03, F-14</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Budget and CPA report sent 4 months into fiscal year. Grealish: 'In recent years instead of meeting we have worked via email since there were few adjustments to the budget draft.' Kathy Black: 'the organization is not following the handbook regarding committees' and 'the State of New Mexico annual report has not been filed.' Bank balances as of Oct 29: General Fund $17,475.18, Money Market $9,719.58, Joyce Walker $23,942.38, Student Travel $3,086.85, Danfelser $2,707.14, Weed $467.55, Composition $939.76, Jane Snow $2,346.73. Total: $60,685.17 + Danfelser CD $3,969.51.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="54" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40" ht="54" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>2025 (TOTY cycle)</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Board</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2025 TOTY Nomination — Terri Reck</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>HIGH — Grealish made 3 attempts to nullify Terri Reck's TOTY nomination. Stated Reck 'has not contributed very much to community service.' Immediately contradicted by board members who seconded Reck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="54" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Pre-Nov 7, 2025</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Chip Miller</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>President + EST</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>VP Report Submitted to President and EST</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>M-04, G-01, F-11</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL — VP Report submitted in advance of Nov 7 meeting. Directly contradicts minutes claim that 'VP report had not been submitted.' Preserved on Google Drive (ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="54" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
+          <t>Pre-Nov 7, 2025</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Chip Miller</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>President + EST</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>VP Report Submitted to President and EST</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>M-04, G-01, F-11</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL — VP Report submitted in advance of Nov 7 meeting. Directly contradicts minutes claim that 'VP report had not been submitted.' Preserved on Google Drive (ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
           <t>Sep 30, 2023</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Lawrence Blind (lawrenceblind@msn.com)</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>PMTNM (submitted as TOTY nomination)</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>TOTY Nomination — Tatiana Vetrinskaya [PHYSICAL PDF REVIEWED]</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>L-05, E-04</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>CRITICAL — Larry submitted Tatiana's nomination from his PERSONAL email (not NMSM employer email, unlike his vote solicitation). Tatiana's listed email is tatiana@nmschoolofmusic.com. Community service section = entirely NMSM activities. Future-tense item listed as achievement: 'will present a workshop at 2023 PMTNM Conference.' Closing attribute: 'business acumen — it is what I know she is most proud of.' This phrase ('I know she is most proud of') reveals Larry wrote it — a nominee does not describe herself this way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="54" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Sep 30, 2023</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Jacqueline Zander-Wall (zanderwall@gmail.com)</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>PMTNM (submitted as TOTY nomination)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>TOTY Nomination — Terri Reck [PHYSICAL PDF REVIEWED]</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>L-05, E-04, F-11</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>HIGH — Zander-Wall submitted Reck's nomination. Terri Reck: 47 years teaching (1976–2023), Dalcroze certification across 6 institutions, 5 AMTA committee leadership roles, harpsichordist with SF Symphony / NM Symphony / NM Philharmonic, students in PMTNM/MTNA programs, Music Bowl Chair for decades, jewelry donated to PMTNM silent auctions. Every criterion directly met. This is the nomination that lost to Larry's 'storybook language' submission.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="54" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Tax Year 2018</t>
+          <t>Sep 30, 2023</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>NM Attorney General</t>
+          <t>Jacqueline Zander-Wall (zanderwall@gmail.com)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>PMTNM (FEIN 85-0284938)</t>
+          <t>PMTNM (submitted as TOTY nomination)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>NM AG Charitable Organization Registration Tax Year 2018 [PHYSICAL DOCUMENT REVIEWED]</t>
+          <t>TOTY Nomination — Terri Reck [PHYSICAL PDF REVIEWED]</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>F-05, F-12</t>
+          <t>L-05, E-04, F-11</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>HIGH — 2018 filing: Grealish sole responsible party for all 5 financial functions; PMTNM address = personal home; NTEE = A6B (misclassification); FY2018 revenue $18,817 vs. expenses $22,649 (deficit); 'Solicited funds in NM: No' (appears inaccurate). See also 2023 filing entry below.</t>
+          <t>HIGH — Zander-Wall submitted Reck's nomination. Terri Reck: 47 years teaching (1976–2023), Dalcroze certification across 6 institutions, 5 AMTA committee leadership roles, harpsichordist with SF Symphony / NM Symphony / NM Philharmonic, students in PMTNM/MTNA programs, Music Bowl Chair for decades, jewelry donated to PMTNM silent auctions. Every criterion directly met. This is the nomination that lost to Larry's 'storybook language' submission.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="54" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>Tax Year 2018</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>NM Attorney General</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>PMTNM (FEIN 85-0284938)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>NM AG Charitable Organization Registration Tax Year 2018 [PHYSICAL DOCUMENT REVIEWED]</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>F-05, F-12</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>HIGH — 2018 filing: Grealish sole responsible party for all 5 financial functions; PMTNM address = personal home; NTEE = A6B (misclassification); FY2018 revenue $18,817 vs. expenses $22,649 (deficit); 'Solicited funds in NM: No' (appears inaccurate). See also 2023 filing entry below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="54" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>Oct 23, 2025</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish (executing for PMTNM)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>VIP Staffing</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>VIP Staffing Master Terms &amp; Conditions — Executed [PHYSICAL CONTRACT REVIEWED]</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>F-13</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>HIGH — Commercial staffing contract executed by Grealish for PMTNM on Oct 23, 2025. Three copies in Drive (draft + executed + third copy). Requires PMTNM to carry GL and EPLI insurance. Contains 1-year non-solicitation clause binding on PMTNM. No board authorization in any minutes. Nov 7 board meeting (17 days later) contains no reference to this contract.</t>
         </is>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -244,6 +244,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -323,8 +329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K47" headerRowCount="1">
-  <autoFilter ref="A1:K47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K48" headerRowCount="1">
+  <autoFilter ref="A1:K48"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -631,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3395,6 +3401,63 @@
       <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Handbook-verified + Email evidence (10:00 AM advisory communication) + Audio record — three undisclosed simultaneous roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="72" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Oct 28, 2023</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Unilateral Conference Decision</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Governance + Conflict of Interest</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence Blind</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Standard nonprofit governance — significant organizational decisions require board approval and oversight; PMTNM Handbook (silent on conference programming authority, indicating governance gap); Fiduciary duty of loyalty — using organizational position and resources for personal/institutional benefit without disclosure</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The invitation was sent directly to PMTNM member teachers on October 28, 2023, as if the decision had been made with full organizational authority. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Email Oct 28, 2023 from Lawrence Blind (lblind@nmschoolofmusic.com) to PMTNM teachers, subject line 'Hello Teachers' — distributed directly inviting NMSM students to participate in PMTNM conference; Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Unilateral decision-making by a president without board oversight. Direct self-dealing: using PMTNM's conference platform to promote his own school and student base. Absence of conflict-of-interest management or disclosure. Pattern-consistent with leadership's broader governance approach (see G-01: 'PMTNM does not function under any legal mandates'). Even if conference programming fell within the president's delegated authority, the absence of any disclosure mechanism for conflicts of interest represents governance failure.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Documented via email + board minutes record (absence of decision) — Pattern consistent with unilateral leadership style</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6642,6 +6705,33 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Lawrence Blind — Oct 28, 2023 email to PMTNM teachers</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>[Unilateral invitation to NMSM students to participate in PMTNM conference benefit concert]</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>G-03, L-02</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>No board approval, no recorded vote, no disclosure of conflict. President used organizational platform to promote his own school. Handbook silent on conference programming authority, creating governance gap. Pattern consistent with leadership's 'no legal mandates' operational style.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A12:E12"/>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Oct 28, 2023</t>
+          <t>Oct 28, 2023 (approx.)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The invitation was sent directly to PMTNM member teachers on October 28, 2023, as if the decision had been made with full organizational authority. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure.</t>
+          <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The decision appears to have been communicated directly to PMTNM member teachers in late October 2023. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure. The fact of NMSM students' participation in the 2023 PMTNM conference is independently corroborated in L-02 (ethics complaint filed Nov 14, 2023 and conference program documentation).</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Email Oct 28, 2023 from Lawrence Blind (lblind@nmschoolofmusic.com) to PMTNM teachers, subject line 'Hello Teachers' — distributed directly inviting NMSM students to participate in PMTNM conference; Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions</t>
+          <t>Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions; Independent corroboration: L-02 (Nov 14, 2023 ethics complaint to MTNA) and conference program/documentation from 2023 confirming NMSM student participation in PMTNM conference</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Documented via email + board minutes record (absence of decision) — Pattern consistent with unilateral leadership style</t>
+          <t>Documented via board minutes record (absence of decision) + independent corroboration via L-02 ethics complaint and conference documentation — Pattern consistent with unilateral leadership style</t>
         </is>
       </c>
     </row>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -329,8 +329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K48" headerRowCount="1">
-  <autoFilter ref="A1:K48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K49" headerRowCount="1">
+  <autoFilter ref="A1:K49"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1629,64 +1629,68 @@
     <row r="18" ht="72" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Nov 7, 2025</t>
+          <t>Oct 2023 - Jul 2024</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Minutes Falsification</t>
+          <t>Organizational Obstruction of Ethics Process</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+          <t>Ethics + Governance</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Jeanne Grealish (minutes author); Sharon Kunitz (President, meeting chair)</t>
+          <t>Lawrence Blind (NMSM authority); Tatiana Vetrinskaya (NMSM co-founder)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>NM Nonprofit Corporation Act — accurate records requirement; Robert's Rules on minute accuracy; Potential falsification of official records</t>
+          <t>MTNA Code of Ethics § Commitment to Colleagues (teacher participation in student transitions); Professional standards for teacher-parent communication; Fiduciary duty not to use organizational position to block accountability</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>IRREGULARITY 1: Minutes state 'a 10 minute limit for each speaker.' Recording and Sharon's own pre-meeting email (7:07 AM Nov 7) confirm the limit was 15 minutes. The president's own written email contradicts her secretary's minutes.</t>
+          <t>When Chip Miller (piano teacher, MTNA member) withdrew from New Mexico School of Music in October 2023, a parent (Toni Morgan) was upset about the transition and lack of communication. Miller attempted to facilitate an open conversation between the parent and NMSM to resolve confusion — consistent with MTNA Code of Ethics: 'The teacher shall participate in the student's change of teachers with as much communication as possible between parties.'
+Larry Blind (NMSM authority) blocked this communication via text message: 'Chip, please do not contact any of your former students from our school by phone or email. This is not appropriate and I have received an email from a parent who was not very happy about your call.'
+Tatiana Vetrinskaya (NMSM co-founder/owner) reinforced the block, claiming exclusive responsibility: 'as the school owner, I am responsible for any concerns or issues our teachers or clients may express. From now on, please communicate with me directly.'
+Miller escalated the matter to MTNA Code of Ethics compliance, filing an Ethical Dispute Mediation Request with MTNA CEO Brian Shepard (Jul 27, 2024). Shepard reviewed materials but ultimately could not process the complaint because NMSM's handbook language created a structural conflict with MTNA's Code of Ethics: the school claimed exclusive control over all student/parent communication, preventing the teacher from fulfilling their MTNA ethical duty to participate in transitions.
+This demonstrates Larry Blind's pattern of using organizational structure and handbook language to create shields against professional accountability. The mechanism is systematic: design bylaws/handbooks to conflict with external ethical standards, then invoke those conflicting rules to block oversight.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Sharon Kunitz email Nov 7, 2025 at 7:07 AM ('Additional RRoo wisdom!'): '15 minutes to speak'; Nov 7 Board Meeting Audio Recording at ~2:41; Proposed Corrections to Minutes (Apr 10, 2026)</t>
+          <t>Oct 12, 2023, 12:57 PM text message from Larry Blind to Chip Miller: 'Chip, please do not contact any of your former students from our school by phone or email. This is not appropriate and I have received an email from a parent who was not very happy about your call'; Nov 14, 2023, 5:43 PM email from Tatiana Vetrinskaya: 'as the school owner, I am responsible for any concerns or issues our teachers or clients may express. From now on, please communicate with me directly'; Nov 14, 2023, 7:55 PM email from Chip Miller explaining ethical violation (MTNA Code violation, poor communication from school, Larry's inappropriate reprimand); Jul 27, 2024: Ethical Dispute Mediation Request filed by Chip Miller to Brian Shepard (bshepard@mtna.org); MTNA's subsequent inability to process complaint due to NMSM handbook conflicts with MTNA Code of Ethics; Email thread 190f4f767cafa7ff (Gmail search result)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Minutes misrepresent an established rule — documented in the president's own email hours before the meeting. Creates false record that VP exceeded time limits.</t>
+          <t>Pattern across two organizations: At PMTNM, Larry blocks anonymous voting systems and uses procedural rules to prevent board oversight. At NMSM, Larry blocks professional ethics compliance using school handbook language that conflicts with MTNA standards. In both cases, he systematically designs organizational structures to insulate himself from accountability — creating rules that prevent external standards from being applied. This is not coincidental governance variation; it is deliberate structural obstruction.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Audio-verified + Email-verified</t>
+          <t>Text + email verified — Pattern consistent with L-04 (bias as Parliamentarian) and L-07 (undisclosed roles to control processes) — Shows systematic use of organizational position to block all forms of oversight and accountability</t>
         </is>
       </c>
     </row>
     <row r="19" ht="72" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1711,39 +1715,39 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Jeanne Grealish</t>
+          <t>Jeanne Grealish (minutes author); Sharon Kunitz (President, meeting chair)</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>NM Nonprofit Corporation Act; Accurate records; Potential fraud</t>
+          <t>NM Nonprofit Corporation Act — accurate records requirement; Robert's Rules on minute accuracy; Potential falsification of official records</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>IRREGULARITY 2: Minutes state financial report 'was approved as presented.' No motion, second, or vote appears anywhere in the audio recording. The only financial motion made was about CPA-designated accounts — which minutes appear to conflate with general financial approval.</t>
+          <t>IRREGULARITY 1: Minutes state 'a 10 minute limit for each speaker.' Recording and Sharon's own pre-meeting email (7:07 AM Nov 7) confirm the limit was 15 minutes. The president's own written email contradicts her secretary's minutes.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Nov 7 Board Meeting Audio Recording; Nov 7 Transcript; INTERNAL_Minutes Review (audio-timestamped); Proposed Corrections to Minutes</t>
+          <t>Sharon Kunitz email Nov 7, 2025 at 7:07 AM ('Additional RRoo wisdom!'): '15 minutes to speak'; Nov 7 Board Meeting Audio Recording at ~2:41; Proposed Corrections to Minutes (Apr 10, 2026)</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>False approval of financial report creates appearance of board oversight where none occurred. Potentially used to legitimize financial decisions that were never actually voted on.</t>
+          <t>Minutes misrepresent an established rule — documented in the president's own email hours before the meeting. Creates false record that VP exceeded time limits.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Audio-verified — Most serious minutes issue</t>
+          <t>Audio-verified + Email-verified</t>
         </is>
       </c>
     </row>
     <row r="20" ht="72" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1768,72 +1772,129 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Jeanne Grealish; Larry Blind (named as actor)</t>
+          <t>Jeanne Grealish</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Robert's Rules — parliamentary procedure; Accurate records</t>
+          <t>NM Nonprofit Corporation Act; Accurate records; Potential fraud</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>IRREGULARITY 3: Minutes state 'time was called by the Parliamentarian.' No such event appears in the audio recording. At 49:13, President adjourns meeting. At 48:22, Parliamentarian (Larry Blind) says 'we can't discuss it unless somebody seconds it.' No time call occurs.</t>
+          <t>IRREGULARITY 2: Minutes state financial report 'was approved as presented.' No motion, second, or vote appears anywhere in the audio recording. The only financial motion made was about CPA-designated accounts — which minutes appear to conflate with general financial approval.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Nov 7 Board Meeting Audio Recording at 48:22 and 49:13; INTERNAL_Minutes Review; Proposed Corrections to Minutes</t>
+          <t>Nov 7 Board Meeting Audio Recording; Nov 7 Transcript; INTERNAL_Minutes Review (audio-timestamped); Proposed Corrections to Minutes</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Fabricated parliamentary event used to justify cutting off VP's presentation. Names Larry Blind as performing an action he did not perform.</t>
+          <t>False approval of financial report creates appearance of board oversight where none occurred. Potentially used to legitimize financial decisions that were never actually voted on.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Audio-verified — Strong contradiction</t>
+          <t>Audio-verified — Most serious minutes issue</t>
         </is>
       </c>
     </row>
     <row r="21" ht="72" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Nov 7, 2025</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Minutes Falsification</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish; Larry Blind (named as actor)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Robert's Rules — parliamentary procedure; Accurate records</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>IRREGULARITY 3: Minutes state 'time was called by the Parliamentarian.' No such event appears in the audio recording. At 49:13, President adjourns meeting. At 48:22, Parliamentarian (Larry Blind) says 'we can't discuss it unless somebody seconds it.' No time call occurs.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Nov 7 Board Meeting Audio Recording at 48:22 and 49:13; INTERNAL_Minutes Review; Proposed Corrections to Minutes</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Fabricated parliamentary event used to justify cutting off VP's presentation. Names Larry Blind as performing an action he did not perform.</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Audio-verified — Strong contradiction</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>M-04</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Nov 7, 2025</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Minutes Falsification + Document Suppression</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish; Sharon Kunitz; Larry Blind</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Accurate records requirement; Robert's Rules — reports submitted to the secretary become part of the record; VP's right to submit reports; NM Nonprofit Act — records of officer reports</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>IRREGULARITY 4: Minutes state VP report 'had not been submitted with other Board reports.' The audio recording proves the opposite — the report was physically handed to both Sharon Kunitz AND Jeanne Grealish before the meeting.
 VERBATIM FROM NOV 7 RECORDING:
@@ -1848,152 +1909,95 @@
 Grealish's statement 'It cannot be board reports, because I don't have anything to include' is admission that she controls what becomes an official board record. By claiming not to 'have anything to include,' she unilaterally excluded Chip's submitted report from the record — then the minutes recorded her exclusion as fact.</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>VP_Report_Submitted_to_President_and_EST.pdf (Google Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z); Nov 7 Audio Recording at 32:46 (Chip: 'handed to Sharon and handed to Jean'); 33:05 (Grealish identifies the document); 33:18 (Grealish: 'It cannot be board reports, because I don't have anything to include'); 33:34 (Larry: 'I can run it off on our machines'); 34:11 (Larry copy machine trip + authorship challenge); Nov 7 Minutes stating report 'had not been submitted'</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>The minutes record as fact something that is directly contradicted by audio: the report was physically present, identified by Grealish, copied by Larry, and read aloud by Larry. Grealish's statement that she controls what becomes an official board report is the mechanism of falsification. The copy machine trip proves the document existed. The minutes's false claim about non-submission is the cover-up.</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>AUDIO-VERIFIED — report physically present, identified, copied during meeting, then recorded as 'not submitted'</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="72" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="72" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>M-05</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Nov 7, 2025</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Procedural Violation — VP Excluded from Board Packet</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Sharon Kunitz; Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>VP's right to receive board meeting materials; Basic procedural fairness; Equal treatment of officers</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>VP Miller stated on recording at 32:28: 'I have no packet.' This was not disputed by any other attendee. Larry Blind, after retrieving Chip's VP report from the copy machine, said at 34:11: 'it does not say that it is from you' — implying he was working from a document not in the standard packet. The board packet had been distributed to other members in advance but Chip received nothing.
 At 42:22, after Sharon attempted to adjourn: Chip: 'I need to note that there are items on the list that were sent to you that have not been covered.' At 42:43, an unidentified voice: 'You didn't send that.' At 42:45, Chip: 'I sent you an email, Sharon, it was very specific with board agenda items.' At 42:52, Sharon herself: 'two months ago, March 17, thank you' — confirming receipt and inadvertently acknowledging she had held the items for two months without placing them on the agenda.
 MINUTES: Contain no reference to VP's lack of packet, no reference to the agenda items dispute, no reference to Sharon's adjournment attempt or Chip's objection. 'Old Business: None. New Business: None.'</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Nov 7 Audio Recording at 32:28 (Chip: 'I have no packet'); 42:22 (items not covered); 42:45 (email confirmation); 42:52 (Sharon: 'two months ago, March 17, thank you'); Oct 14, 2025 VP Agenda Request email (the items submitted); Nov 7 Board Meeting minutes ('Old Business: None'); Proposed Corrections to Minutes #8 and #9</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>VP was excluded from the pre-meeting board packet, had his submitted agenda items ignored, and when he objected to adjournment, was told by one voice that he'd never sent items — immediately contradicted by the President herself, who confirmed receipt from two months prior. The minutes erase the entire dispute.</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Audio-verified + Sharon's own self-contradiction on record</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="72" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Ongoing 2025</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Conflict of Interest</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Ethics</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz; Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Nonprofit governance — board members must be free of conflicts; Fiduciary duty</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz receives scholarship money from PMTNM. Jeanne Grealish has sole sign-off authority on scholarship disbursements. Sharon consistently backs Jeanne on all governance disputes, financial access questions, and VP complaints — creating the appearance of a quid pro quo relationship.</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>DocsFromJeanne financial records (scholarship disbursements); Spring 2025 Board Meeting records; Pattern of Sharon defending Grealish across all email threads</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>If Sharon's scholarship payments are controlled by Grealish, Sharon has a financial interest in maintaining Grealish's power. This creates an undisclosed conflict of interest on all votes where Sharon sides with Grealish.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>To be confirmed from financial records</t>
         </is>
       </c>
     </row>
     <row r="24" ht="72" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Mar 17, 2025</t>
+          <t>Ongoing 2025</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Governance Violation</t>
+          <t>Conflict of Interest</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2008,72 +2012,129 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Sharon Kunitz</t>
+          <t>Sharon Kunitz; Jeanne Grealish</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>VP's right to financial records; PMTNM Handbook on VP duties</t>
+          <t>Nonprofit governance — board members must be free of conflicts; Fiduciary duty</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>When Chip requested financial records, Sharon reinforced Grealish's refusal by telling Chip his duties were 'collecting funds for the MTNA Foundation and recruiting members' — a reductive mischaracterization designed to strip the VP of governance authority.</t>
+          <t>Sharon Kunitz receives scholarship money from PMTNM. Jeanne Grealish has sole sign-off authority on scholarship disbursements. Sharon consistently backs Jeanne on all governance disputes, financial access questions, and VP complaints — creating the appearance of a quid pro quo relationship.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Email Mar 17, 2025 (Sharon → Chip, responding to financial request); VP's documented handbook duties including Budget Committee membership</t>
+          <t>DocsFromJeanne financial records (scholarship disbursements); Spring 2025 Board Meeting records; Pattern of Sharon defending Grealish across all email threads</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>President actively undermining VP's legal right to financial records. Combined with Grealish's refusal, establishes coordinated obstruction.</t>
+          <t>If Sharon's scholarship payments are controlled by Grealish, Sharon has a financial interest in maintaining Grealish's power. This creates an undisclosed conflict of interest on all votes where Sharon sides with Grealish.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Documented — Key supporting violation</t>
+          <t>To be confirmed from financial records</t>
         </is>
       </c>
     </row>
     <row r="25" ht="72" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>S-02</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Mar 17, 2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Governance Violation</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Ethics</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>VP's right to financial records; PMTNM Handbook on VP duties</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>When Chip requested financial records, Sharon reinforced Grealish's refusal by telling Chip his duties were 'collecting funds for the MTNA Foundation and recruiting members' — a reductive mischaracterization designed to strip the VP of governance authority.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Email Mar 17, 2025 (Sharon → Chip, responding to financial request); VP's documented handbook duties including Budget Committee membership</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>President actively undermining VP's legal right to financial records. Combined with Grealish's refusal, establishes coordinated obstruction.</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Documented — Key supporting violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="72" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>S-03</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Nov 4–7, 2025</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Broken Commitment + Attempted Wrongful Adjournment</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Sharon Kunitz</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Good faith obligations; Promissory estoppel; Robert's Rules §23 (adjournment — cannot adjourn when business is pending); Due process in nonprofit governance</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>TWO SEPARATE VIOLATIONS, FOUR DAYS APART, ON AUDIO RECORD:
 (1) NOV 4, 2025 at 1:14:51 (recorded): After hearing VP's full report and Kathy Black's legal recommendations, Sharon Kunitz stated: 'I'll put them on the agenda.' Attorney Kathy Black immediately confirmed on the recording: 'She's going to put them on the agenda for Friday morning.' This commitment was made in the presence of legal counsel. Kathy Black's same-day email (2:54 PM) further confirmed: 'Sharon agreed to tee up certain agenda items.'
@@ -2082,98 +2143,41 @@
 The Nov 7 minutes record 'Old Business: None. New Business: None.' — erasing any trace of the dispute.</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Oct 14, 2025 VP Agenda Request email to Sharon (subject: ITEMS FOR BOARD AGENDA Nov 7-8, Gmail thread: 199e36adc51ecfde) — five formal items invoking Handbook Art. VIII §5 and three NM statutes; Sharon's reply Oct 14 at 16:08: 'As I have said, there is more in my life than PMTNM... Will have more time for this tomorrow morning.' — no substantive engagement with any item, no follow-up; Nov 4, 2025 Audio Recording at 1:14:51 (Sharon: 'I'll put them on the agenda'); Nov 4, 2025 Audio Recording at 1:14:53 (Kathy Black: 'She's going to put them on the agenda'); Kathy Black email Nov 4 at 2:54 PM confirming agenda commitment; Nov 7, 2025 Audio Recording at ~41:30 (Sharon: 'I did not have agenda items. So meeting is adjourned.'); Nov 7 Audio Recording at ~42:52 (Sharon: 'two months ago, March 17, thank you' — confirming receipt of Chip's earlier communication); Nov 7 Minutes: 'Old Business: None. New Business: None.'</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Sharon made a witnessed commitment before an attorney, confirmed immediately by that attorney on recording, then reversed it four days later — attempting to adjourn the meeting without addressing a single submitted agenda item. When challenged, she accidentally confirmed having received the items two months earlier. This is the clearest single sequence demonstrating intentional governance exclusion: commitment, reversal, concealment, then accidental self-contradiction.</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>DUAL AUDIO VERIFIED (Nov 4 + Nov 7) + Attorney email + Sharon's own self-contradiction on record</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="72" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Jan 2025 → Jul 2025</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Records Access</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>PMTNM Handbook: Handbook should be furnished to each member; NMSA §53-8-26</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Chip requested the PMTNM Handbook in January 2025. Grealish falsely claimed it was available online (it was not — offline for 2+ years). Chip did not receive a copy until July 13, 2025 — 6 months later.</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Jan 2025 Handbook thread; Jul 13, 2025 email distributing handbook; Grealish's false claim of online availability</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>6-month obstruction of access to governing documents is itself a governance violation. Compound with financial records refusal.</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Documented</t>
         </is>
       </c>
     </row>
     <row r="27" ht="72" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Nov 7, 2025 → Mar 9, 2026</t>
+          <t>Jan 2025 → Jul 2025</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Records Distribution</t>
+          <t>Records Access</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2188,39 +2192,39 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Standard nonprofit governance — minutes should be distributed within 30-60 days; PMTNM handbook on minutes distribution</t>
+          <t>PMTNM Handbook: Handbook should be furnished to each member; NMSA §53-8-26</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>November 7, 2025 board meeting minutes were dated January 1, 2026 and not distributed until March 9, 2026 — four months after the meeting. Distribution came after the petition was already filed (Feb 2026) and after PMTNM's answer was filed (Mar 5, 2026).</t>
+          <t>Chip requested the PMTNM Handbook in January 2025. Grealish falsely claimed it was available online (it was not — offline for 2+ years). Chip did not receive a copy until July 13, 2025 — 6 months later.</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Jan 1, 2026 date on minutes; Mar 9, 2026 distribution email from Grealish; Petition filed Jan 27, 2026; PMTNM Answer filed Mar 5, 2026</t>
+          <t>Jan 2025 Handbook thread; Jul 13, 2025 email distributing handbook; Grealish's false claim of online availability</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>4-month delay in distributing minutes is itself a governance failure. Timing of distribution (after legal proceedings filed) raises questions about deliberate delay.</t>
+          <t>6-month obstruction of access to governing documents is itself a governance violation. Compound with financial records refusal.</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Documented — Suspicious timing</t>
+          <t>Documented</t>
         </is>
       </c>
     </row>
     <row r="28" ht="72" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Apr 25, 2025 → Nov 7, 2025</t>
+          <t>Nov 7, 2025 → Mar 9, 2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2233,9 +2237,9 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2245,160 +2249,160 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Standard practice — spring board meeting minutes should be distributed before fall meeting</t>
+          <t>Standard nonprofit governance — minutes should be distributed within 30-60 days; PMTNM handbook on minutes distribution</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>As of Oct 9, 2025, Grealish stated spring minutes had not been distributed and would be 'compiled and sent with Nov first' board reports. Spring minutes (April 2025) were not circulated until November — a 7-month delay. This was noted in Chip's Oct 14 agenda request email.</t>
+          <t>November 7, 2025 board meeting minutes were dated January 1, 2026 and not distributed until March 9, 2026 — four months after the meeting. Distribution came after the petition was already filed (Feb 2026) and after PMTNM's answer was filed (Mar 5, 2026).</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Oct 9, 2025 Grealish email re: minutes distribution; Oct 14 VP Agenda Request email documenting this; Nov 7 Board Meeting (April minutes addressed at start of meeting)</t>
+          <t>Jan 1, 2026 date on minutes; Mar 9, 2026 distribution email from Grealish; Petition filed Jan 27, 2026; PMTNM Answer filed Mar 5, 2026</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Pattern of chronic delays in distributing meeting records. Creates information asymmetry between Grealish-aligned insiders and officers like Chip who have no independent access.</t>
+          <t>4-month delay in distributing minutes is itself a governance failure. Timing of distribution (after legal proceedings filed) raises questions about deliberate delay.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Documented</t>
+          <t>Documented — Suspicious timing</t>
         </is>
       </c>
     </row>
     <row r="29" ht="72" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Apr 25, 2025 → Nov 7, 2025</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Records Distribution</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Standard practice — spring board meeting minutes should be distributed before fall meeting</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>As of Oct 9, 2025, Grealish stated spring minutes had not been distributed and would be 'compiled and sent with Nov first' board reports. Spring minutes (April 2025) were not circulated until November — a 7-month delay. This was noted in Chip's Oct 14 agenda request email.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Oct 9, 2025 Grealish email re: minutes distribution; Oct 14 VP Agenda Request email documenting this; Nov 7 Board Meeting (April minutes addressed at start of meeting)</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Pattern of chronic delays in distributing meeting records. Creates information asymmetry between Grealish-aligned insiders and officers like Chip who have no independent access.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>L-05</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Oct 2023</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>TOTY Manipulation</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Ethics + Governance</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Larry Blind; Tatiana Vetrinskaya (NMSM)</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>MTNA Code of Ethics §3 (conflicts of interest); Nonprofit election integrity; Robert's Rules on impartiality</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2023 TOTY had two nominees: Terri Reck (nomination written by Jackie Zander-Wall, AMTA president) vs. Tatiana Vetrinskaya (nomination written by Larry Blind, her employer and NMSM director). Larry administered the vote from lblind@nmschoolofmusic.com and explicitly stated in his voting email: 'I decided to extend the nomination period' — a unilateral extension with no board approval. Chip's side-by-side analysis: Terri Reck's bio = 'dense list of information highlighting work done in the PMTNM community this past year.' Tatiana's bio (written by Larry) = 'storybook language throughout that causes emotional reactions, often unrelated to the question at hand. Highlights work done in NMSM.' Haewon Yang admitted voting for 'the person whose bio looked the best.' Tatiana won. No conflict of interest was disclosed by Larry.
 VERBATIM FROM TATIANA'S ACTUAL SUBMISSION (submitted by lawrenceblind@msn.com, signed 9-30-23): Community service section = entirely NMSM activities. Closing line: 'business acumen... it is what I know she is most proud of.' [Note: 'business acumen' is not a PMTNM TOTY criterion.] Future-tense item listed under achievements: 'will present a workshop at 2023 PMTNM Conference' — event had not yet occurred at time of submission. Tatiana's listed email: tatiana@nmschoolofmusic.com (NMSM institutional address).
 VERBATIM FROM TERRI RECK'S ACTUAL SUBMISSION (submitted by zanderwall@gmail.com / Jacqueline Zander-Wall, signed 9/30/23): 47 years of teaching (1976–2023). Dalcroze certification across 6 institutions. 5 AMTA committee leadership roles. Harpsichord performances with SF Symphony, NM Symphony, NM Philharmonic. Students enrolled in PMTNM/MTNA programs. Music Bowl Chair for decades. Jewelry donated to PMTNM silent auctions.</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Oct 4, 2023 email from lblind@nmschoolofmusic.com TO lblind@nmschoolofmusic.com (BCC to board): Larry explicitly states 'I decided to extend the nomination period'; Two TOTY PDFs sent with vote solicitation: 'Terri Reck.pdf' and 'Tatiana Vetrinskaya.pdf' (Gmail thread ID: 19239a27e03b7010); PHYSICAL PDFs READ — Tatiana's PDF: submitted by lawrenceblind@msn.com, Tatiana email tatiana@nmschoolofmusic.com, closing 'business acumen — it is what I know she is most proud of,' future-tense 'will present a workshop at 2023 PMTNM Conference,' all community service through NMSM; Terri's PDF: submitted by zanderwall@gmail.com, 47 years teaching, Dalcroze certification, 5 AMTA committee roles, harpsichord with major orchestras, decades as Music Bowl Chair, jewelry to PMTNM silent auctions; Haewon thread Sep 27-28, 2024: 'last year I voted for Tatyana because I had no idea who these people were and just voted for the person whose bio looked the best'; Chip to Jackie Sep 29, 2024: 'The other submission paints a picture of a larger timeframe and uses storybook language throughout that causes emotional reactions, and are often unrelated to the question at hand. It highlights work done in NMSM'; Jacqueline Zander-Wall response: 'I am not contesting the decision made at all. I think one needs to move on.'</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Employer wrote a polished 'storybook' bio for his employee vs. an independent teacher's factual PMTNM community service record. The winning submission listed a future event (not yet a completed achievement), described 'business acumen' (not a TOTY criterion), and used the nominee's NMSM institutional email — all pointing to an NMSM marketing document rather than a community service record. The losing submission documented 47 years of verifiable community service across PMTNM, AMTA, and major NM orchestras. Vote administered by the conflicted party from NMSM business email. Unilateral deadline extension. Haewon's admission confirms votes cast on presentation quality, not merit. Jackie Zander-Wall (AMTA president) declined to contest — the quiet resignation of a community teacher facing institutional power.</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Email evidence + Haewon on-record admission + Chip comparative analysis (verbatim) + PHYSICAL PDFs READ AND ANALYZED</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="72" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>L-06</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Ongoing 2023–2025</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>NMSM Business Promotion via PMTNM</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Ethics + Financial</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Larry Blind</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>MTNA Code of Ethics: 'Represent our art honestly'; IRS private benefit prohibition; Nonprofit duty of loyalty</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Larry's NMSM director biography uses systematically misleading language: 'students have an opportunity to perform internationally' (they pay to attend European recitals — this is not performance, it is tourism); 'returned for an encore performance' at Carnegie Hall (how he accessed the hall is unsubstantiated — the concern is the misleading framing). NMSM employs uncredentialed faculty (flute majors teaching piano, teachers in first jobs). Larry used PMTNM's conference platform and handbook to promote NMSM, diluting PMTNM value to independent member teachers whose market is directly harmed by NMSM's growth.</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>NMSM director biography (nmschoolofmusic.com/director---lawrence-blind — live web evidence); 2023 PMTNM conference program featuring NMSM students; VP Report documenting biography misrepresentation; PMTNM member impact analysis</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Using nonprofit organizational credibility and platform to market a competing commercial music school. Misleading language in NMSM materials violates MTNA's core principle of honest representation. NMSM's 700-student enrollment at $70/hr directly harms independent PMTNM members' livelihoods.</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Web evidence + conference records + VP Report</t>
         </is>
       </c>
     </row>
     <row r="31" ht="72" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>F-10</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>Ongoing 2023–2025</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Financial Self-Dealing</t>
+          <t>NMSM Business Promotion via PMTNM</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2413,170 +2417,170 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Jeanne Grealish</t>
+          <t>Larry Blind</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>IRS private benefit prohibition; Fiduciary duty; PMTNM budget oversight</t>
+          <t>MTNA Code of Ethics: 'Represent our art honestly'; IRS private benefit prohibition; Nonprofit duty of loyalty</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Storage unit operating expense documented as $4,600 actual vs. $3,000 budgeted — a 53% overrun. Even Larry Blind, who has a financial relationship with Grealish, raised the discrepancy in a Nov 2 email asking about the expense. Grealish had already admitted (before attorney Kathy Black) that she stores personal furniture in the PMTNM storage unit.</t>
+          <t>Larry's NMSM director biography uses systematically misleading language: 'students have an opportunity to perform internationally' (they pay to attend European recitals — this is not performance, it is tourism); 'returned for an encore performance' at Carnegie Hall (how he accessed the hall is unsubstantiated — the concern is the misleading framing). NMSM employs uncredentialed faculty (flute majors teaching piano, teachers in first jobs). Larry used PMTNM's conference platform and handbook to promote NMSM, diluting PMTNM value to independent member teachers whose market is directly harmed by NMSM's growth.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Nov 2, 2025 Larry Blind email raising $4,600 storage question; Nov 4 meeting transcript (Grealish personal furniture admission before Kathy Black); DocsFromJeanne budget documents showing $3,000 budget vs. $4,600 actual</t>
+          <t>NMSM director biography (nmschoolofmusic.com/director---lawrence-blind — live web evidence); 2023 PMTNM conference program featuring NMSM students; VP Report documenting biography misrepresentation; PMTNM member impact analysis</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>53% budget overrun on personal-use storage. Even the past president questioned it in writing. Attorney-witnessed admission of personal property in PMTNM storage creates clear private-benefit violation.</t>
+          <t>Using nonprofit organizational credibility and platform to market a competing commercial music school. Misleading language in NMSM materials violates MTNA's core principle of honest representation. NMSM's 700-student enrollment at $70/hr directly harms independent PMTNM members' livelihoods.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Attorney-witnessed + Larry Blind email confirmation</t>
+          <t>Web evidence + conference records + VP Report</t>
         </is>
       </c>
     </row>
     <row r="32" ht="72" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Financial Self-Dealing</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ethics + Financial</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>IRS private benefit prohibition; Fiduciary duty; PMTNM budget oversight</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Storage unit operating expense documented as $4,600 actual vs. $3,000 budgeted — a 53% overrun. Even Larry Blind, who has a financial relationship with Grealish, raised the discrepancy in a Nov 2 email asking about the expense. Grealish had already admitted (before attorney Kathy Black) that she stores personal furniture in the PMTNM storage unit.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Nov 2, 2025 Larry Blind email raising $4,600 storage question; Nov 4 meeting transcript (Grealish personal furniture admission before Kathy Black); DocsFromJeanne budget documents showing $3,000 budget vs. $4,600 actual</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>53% budget overrun on personal-use storage. Even the past president questioned it in writing. Attorney-witnessed admission of personal property in PMTNM storage creates clear private-benefit violation.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Attorney-witnessed + Larry Blind email confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>E-04</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Oct 2023</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>TOTY Procedural Violation</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Ethics + Governance</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Larry Blind; Tatiana Vetrinskaya (NMSM)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>MTNA Code of Ethics — conflicts must be disclosed; PMTNM TOTY award criteria (Criterion B3: 'outstanding professional relationship with students, fellow music teachers, and community leaders'; B4: 'consistent record of high standards of teaching and promoting music teaching in New Mexico')</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>The TOTY award criteria require demonstrated community service within New Mexico's music teaching community. Criterion-by-criterion analysis of the actual PDFs:
 TERRI RECK (loser): B1 ✓ — 47 years teaching, Dalcroze certification. B2 ✓ — 5 AMTA committee leadership roles, SF Symphony, NM Symphony, NM Philharmonic harpsichordist. B3 ✓ — Students in PMTNM/MTNA programs, Music Bowl Chair decades, jewelry donations to PMTNM silent auctions. B4 ✓ — Entire career in NM; engaged with PMTNM community across multiple decades.
 TATIANA VETRINSKAYA (winner, written by her employer Larry Blind): B1 ✓ — teaching background listed. B2 — ambiguous; achievements framed around NMSM institutional activity. B3 ✗ — community service section entirely NMSM activities, not PMTNM/NM music teaching community. B4 ✗ (future tense disqualifier) — submission lists 'will present a workshop at 2023 PMTNM Conference' — an event that had NOT YET OCCURRED when submission was filed on 9-30-23. Closing attribute 'business acumen' is not a TOTY criterion. No conflict of interest disclosed.</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>PHYSICAL PDFs read and analyzed: 'Terri Reck.pdf' (submitted zanderwall@gmail.com, signed 9/30/23) and 'Tatiana Vetrinskaya.pdf' (submitted lawrenceblind@msn.com, signed 9-30-23); Larry's Oct 4, 2023 voting email with award criteria (Gmail thread ID: 19239a27e03b7010): B3 and B4 require PMTNM community service; Chip to Jackie Sep 29 (verbatim comparison): 'The other submission... highlights work done in NMSM' vs. 'Your submission... highlights work done in the PMTNM community this past year'; Haewon admission that she voted based on bio appearance; Tatiana's future-tense 'will present a workshop' listed as an achievement</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Award designed to honor PMTNM community service given to NMSM institutional promotion. The winning bio fails B3 entirely and lists a future event as an achievement. The losing bio meets all four criteria with verifiable, decades-long records. No conflict disclosure made by the employer who wrote the winning nomination and administered the vote.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>PHYSICAL PDFs analyzed + verbatim comparative analysis in email record</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="72" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>S-04</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Mar 2025 – Feb 2026</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Governance Obstruction</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Ethics + Legal</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>VP's statutory right to financial information (NMSA §53-8-26); PMTNM Handbook on VP Budget Committee membership; Presidential duty of good faith</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>For 11+ months, Sharon used her position as President to block Chip's financial access: (1) Mar 2025 — reinforced Grealish's records refusal, falsely characterizing VP's duties; (2) Oct 2025 — dismissed budget committee requests by deferring to Grealish; (3) Oct 2025 — told Chip that scholarship coordination was 'not your territory'; (4) Nov 4 — committed to place agenda items before board, then broke that commitment at Nov 7.</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Mar 17, 2025 email (Sharon reinforces Grealish refusal); Oct 2 email (budget committee deferral); Oct 14 agenda request reply (dismissive); Nov 4 audio recording (commitment at 1:14:51); Kathy Black email Nov 4 at 2:54 PM (confirms commitment); Nov 7 meeting (commitment broken)</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Sustained 11-month pattern of presidential obstruction of VP's statutory inspection rights. Pattern of coordination with Grealish to maintain financial information asymmetry.</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>11-month documented pattern — four distinct incidents</t>
         </is>
       </c>
     </row>
     <row r="34" ht="72" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Sep – Oct 2025</t>
+          <t>Mar 2025 – Feb 2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Failure to Act on Known Misconduct</t>
+          <t>Governance Obstruction</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Ethics + Legal</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2591,111 +2595,111 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>MTNA Code of Ethics — board members must not tolerate known misconduct; Presidential responsibility for board conduct standards; Duty of candor</t>
+          <t>VP's statutory right to financial information (NMSA §53-8-26); PMTNM Handbook on VP Budget Committee membership; Presidential duty of good faith</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Sep 11, 2025: Jeanne Grealish responded to Chip's MTNA Foundation newsletter: 'Boring and irrelevant to most of us.' Sep 12, 12:44 AM: Chip forwarded Jeanne's response to Jeanne, Brian Shepard, AND Sharon Kunitz (slkunitz@aol.com) asking 'Hi Jeanne, can you clarify?' Sharon received this email — and said nothing. No defense of Chip's work, no pushback on Jeanne's dismissive characterization. Oct 2, 2025 — 21 days later — Sharon sent Chip a separate email: 'Great article on Foundation! Beautifully written and presented.' (CCed to Jeanne, Larry, Laura Spitzer). Sharon knew the article had merit. She praised it privately. She chose not to say so when Jeanne publicly dismissed it to Chip's face.</t>
+          <t>For 11+ months, Sharon used her position as President to block Chip's financial access: (1) Mar 2025 — reinforced Grealish's records refusal, falsely characterizing VP's duties; (2) Oct 2025 — dismissed budget committee requests by deferring to Grealish; (3) Oct 2025 — told Chip that scholarship coordination was 'not your territory'; (4) Nov 4 — committed to place agenda items before board, then broke that commitment at Nov 7.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Sep 12, 2025 12:44 AM email: Chip → Jeanne + bshepard@mtna.org + slkunitz@aol.com: 'Hi Jeanne, can you clarify?' (Gmail thread ID: 1993b54101446b14); Oct 2, 2025 Sharon → Chip (CC Jeanne, Larry, Laura): 'Great article on Foundation! Beautifully written and presented.' (Gmail thread ID: 199a581f54374d6f); No Sharon response in the Sep 12 thread</t>
+          <t>Mar 17, 2025 email (Sharon reinforces Grealish refusal); Oct 2 email (budget committee deferral); Oct 14 agenda request reply (dismissive); Nov 4 audio recording (commitment at 1:14:51); Kathy Black email Nov 4 at 2:54 PM (confirms commitment); Nov 7 meeting (commitment broken)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Sharon's silence in the moment — combined with her private praise 21 days later — proves she recognized Jeanne's conduct was wrong and chose not to intervene. As President, she had the authority and responsibility to address Grealish's conduct toward a fellow officer.</t>
+          <t>Sustained 11-month pattern of presidential obstruction of VP's statutory inspection rights. Pattern of coordination with Grealish to maintain financial information asymmetry.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Two emails, 21 days apart — documentary contrast</t>
+          <t>11-month documented pattern — four distinct incidents</t>
         </is>
       </c>
     </row>
     <row r="35" ht="72" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Oct 7, 2025</t>
+          <t>Sep – Oct 2025</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Legal Compliance Repudiation</t>
+          <t>Failure to Act on Known Misconduct</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Legal + Ethics</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+          <t>Ethics</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Jeanne Grealish</t>
+          <t>Sharon Kunitz</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>IRS 501(c)(3) obligations; NM Nonprofit Corporation Act; Fiduciary duty to act within statutory constraints; PMTNM Handbook (Bylaws) provisions for budget committee and fiscal governance</t>
+          <t>MTNA Code of Ethics — board members must not tolerate known misconduct; Presidential responsibility for board conduct standards; Duty of candor</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>On Oct 7, 2025, Jeanne Grealish sent an email to Chip, Sharon, Laura, Larry, and Heather Nasi. The FULL CONTEXT: Chip had asked about the budget committee meeting required by the PMTNM Handbook. Grealish responded by dismissing the handbook's budget committee provisions as 'grossly out of date,' then wrote: 'Thanks heaven, PMTNM does not function under any legal mandates!' This statement was NOT an offhand philosophical remark — it was a deliberate, specific rejection of the handbook governance requirements Chip was invoking to justify a budget committee meeting. Grealish also stated during this period: conference venue research was 'a waste of everyone's time and a senseless cluttering up of mail boxes'; the website was 'a big waste of time'; 'Please, no more useless emails' (re: venue research). The statement is additionally documented in the VP Report submitted to the President and EST (Section 3.3).</t>
+          <t>Sep 11, 2025: Jeanne Grealish responded to Chip's MTNA Foundation newsletter: 'Boring and irrelevant to most of us.' Sep 12, 12:44 AM: Chip forwarded Jeanne's response to Jeanne, Brian Shepard, AND Sharon Kunitz (slkunitz@aol.com) asking 'Hi Jeanne, can you clarify?' Sharon received this email — and said nothing. No defense of Chip's work, no pushback on Jeanne's dismissive characterization. Oct 2, 2025 — 21 days later — Sharon sent Chip a separate email: 'Great article on Foundation! Beautifully written and presented.' (CCed to Jeanne, Larry, Laura Spitzer). Sharon knew the article had merit. She praised it privately. She chose not to say so when Jeanne publicly dismissed it to Chip's face.</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Oct 7, 2025 email from Grealish → Chip + Sharon + Laura + Larry + Heather Nasi (Gmail thread ID: 199c0d60237afa6c): VERBATIM: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!'; VP_Report_Submitted_to_President_and_EST.pdf Section 3.3 (Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z) independently documenting the same statement</t>
+          <t>Sep 12, 2025 12:44 AM email: Chip → Jeanne + bshepard@mtna.org + slkunitz@aol.com: 'Hi Jeanne, can you clarify?' (Gmail thread ID: 1993b54101446b14); Oct 2, 2025 Sharon → Chip (CC Jeanne, Larry, Laura): 'Great article on Foundation! Beautifully written and presented.' (Gmail thread ID: 199a581f54374d6f); No Sharon response in the Sep 12 thread</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>EST explicitly disclaiming legal obligations on the record — and doing so SPECIFICALLY to shut down VP's invocation of handbook governance requirements for the budget committee. The person controlling all of PMTNM's finances and records publicly stated the organization operates without legal mandates in response to a compliance question. This is the most unambiguous single statement supporting the petition and a future AG complaint.</t>
+          <t>Sharon's silence in the moment — combined with her private praise 21 days later — proves she recognized Jeanne's conduct was wrong and chose not to intervene. As President, she had the authority and responsibility to address Grealish's conduct toward a fellow officer.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>VERBATIM email + VP Report — dual source verification of same statement</t>
+          <t>Two emails, 21 days apart — documentary contrast</t>
         </is>
       </c>
     </row>
     <row r="36" ht="72" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Oct 7, 2025</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TOTY Process Interference — Terri Reck Pattern</t>
+          <t>Legal Compliance Repudiation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Ethics + Governance</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Legal + Ethics</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2705,360 +2709,417 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nonprofit election integrity; MTNA Code of Ethics — fair processes; PMTNM TOTY procedural standards</t>
+          <t>IRS 501(c)(3) obligations; NM Nonprofit Corporation Act; Fiduciary duty to act within statutory constraints; PMTNM Handbook (Bylaws) provisions for budget committee and fiscal governance</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>CRITICAL PATTERN: Terri Reck was ALSO the 2023 TOTY nominee who lost to Tatiana Vetrinskaya when Larry administered the biased process (L-05, E-04). In 2025, Grealish made three separate attempts to nullify Reck's nomination again, stating: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service.' This claim was immediately contradicted by other board members who seconded Reck's nomination. Grealish's 'last time' reference is itself an admission — she knows Terri was nominated before and is aware of the prior cycle. Terri Reck — an independent community teacher with 47 years of teaching, 5 AMTA committee roles, and decades as Music Bowl Chair (per her own 2023 TOTY submission) — has been the target of TOTY suppression in back-to-back cycles: 2023 (Larry's biased process blocked her) and 2025 (Grealish's three direct nullification attempts).</t>
+          <t>On Oct 7, 2025, Jeanne Grealish sent an email to Chip, Sharon, Laura, Larry, and Heather Nasi. The FULL CONTEXT: Chip had asked about the budget committee meeting required by the PMTNM Handbook. Grealish responded by dismissing the handbook's budget committee provisions as 'grossly out of date,' then wrote: 'Thanks heaven, PMTNM does not function under any legal mandates!' This statement was NOT an offhand philosophical remark — it was a deliberate, specific rejection of the handbook governance requirements Chip was invoking to justify a budget committee meeting. Grealish also stated during this period: conference venue research was 'a waste of everyone's time and a senseless cluttering up of mail boxes'; the website was 'a big waste of time'; 'Please, no more useless emails' (re: venue research). The statement is additionally documented in the VP Report submitted to the President and EST (Section 3.3).</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>VP_Report_Submitted_to_President_and_EST.pdf — 2025 TOTY section (Google Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z): Grealish: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service'; Board members seconding Reck contradicting Grealish; 2023 TOTY PDF 'Terri Reck.pdf' (submitted zanderwall@gmail.com, Gmail thread ID: 19239a27e03b7010) documents Reck's actual community record: 47 years teaching, Dalcroze certification, SF/NM Symphony harpsichordist, Music Bowl Chair, PMTNM silent auction donations</t>
+          <t>Oct 7, 2025 email from Grealish → Chip + Sharon + Laura + Larry + Heather Nasi (Gmail thread ID: 199c0d60237afa6c): VERBATIM: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!'; VP_Report_Submitted_to_President_and_EST.pdf Section 3.3 (Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z) independently documenting the same statement</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>The same independent community teacher — with a documented record that exceeds TOTY criteria — has been suppressed in consecutive cycles by different insiders: Larry in 2023, Grealish in 2025. Grealish's claim that Reck 'has not contributed very much' is directly contradicted by Reck's own 2023 submission PDF. This is the clearest evidence that the TOTY process is being used to protect institutional interests rather than honor community service.</t>
+          <t>EST explicitly disclaiming legal obligations on the record — and doing so SPECIFICALLY to shut down VP's invocation of handbook governance requirements for the budget committee. The person controlling all of PMTNM's finances and records publicly stated the organization operates without legal mandates in response to a compliance question. This is the most unambiguous single statement supporting the petition and a future AG complaint.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>VP Report + 2023 TOTY PDF (physical document analyzed) + two-cycle targeting pattern</t>
+          <t>VERBATIM email + VP Report — dual source verification of same statement</t>
         </is>
       </c>
     </row>
     <row r="37" ht="72" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>F-11</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>TOTY Process Interference — Terri Reck Pattern</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Ethics + Governance</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Nonprofit election integrity; MTNA Code of Ethics — fair processes; PMTNM TOTY procedural standards</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>CRITICAL PATTERN: Terri Reck was ALSO the 2023 TOTY nominee who lost to Tatiana Vetrinskaya when Larry administered the biased process (L-05, E-04). In 2025, Grealish made three separate attempts to nullify Reck's nomination again, stating: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service.' This claim was immediately contradicted by other board members who seconded Reck's nomination. Grealish's 'last time' reference is itself an admission — she knows Terri was nominated before and is aware of the prior cycle. Terri Reck — an independent community teacher with 47 years of teaching, 5 AMTA committee roles, and decades as Music Bowl Chair (per her own 2023 TOTY submission) — has been the target of TOTY suppression in back-to-back cycles: 2023 (Larry's biased process blocked her) and 2025 (Grealish's three direct nullification attempts).</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>VP_Report_Submitted_to_President_and_EST.pdf — 2025 TOTY section (Google Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z): Grealish: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service'; Board members seconding Reck contradicting Grealish; 2023 TOTY PDF 'Terri Reck.pdf' (submitted zanderwall@gmail.com, Gmail thread ID: 19239a27e03b7010) documents Reck's actual community record: 47 years teaching, Dalcroze certification, SF/NM Symphony harpsichordist, Music Bowl Chair, PMTNM silent auction donations</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>The same independent community teacher — with a documented record that exceeds TOTY criteria — has been suppressed in consecutive cycles by different insiders: Larry in 2023, Grealish in 2025. Grealish's claim that Reck 'has not contributed very much' is directly contradicted by Reck's own 2023 submission PDF. This is the clearest evidence that the TOTY process is being used to protect institutional interests rather than honor community service.</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>VP Report + 2023 TOTY PDF (physical document analyzed) + two-cycle targeting pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>F-14</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Jul 1 – Nov 7, 2025</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Unauthorized Spending</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Standard nonprofit governance — expenditures require an approved budget; PMTNM Handbook: budget must be approved by Executive Board at a board meeting; NM Nonprofit Corporation Act — fiduciary duty</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>PMTNM's fiscal year 2025-2026 began July 1, 2025. Grealish's own Oct 7 email confirms the CPA report was not expected until 'around November 1st' because the CPA 'was out of the country all summer.' The proposed budget was not sent to the budget committee until Oct 29, 2025 — four months into the fiscal year. A formal budget committee meeting never took place (replaced by emails, per Grealish's direction). The budget was presented at the Nov 7 board meeting, but no formal vote was documented in the audio recording (consistent with M-02).
 During the Jul 1 – Nov 7 period, Grealish continued spending organizational funds — including $4,600 in storage costs (F-10), her $1,750 annual honorarium (F-07), and operational expenses — without any board-approved budget authorizing those expenditures. Grealish justified this by saying 'Conference expenses and all expenses in the 2025-2026 fiscal year are covered in the current budget' (Oct 7 email) — but no 2025-2026 budget existed yet. The only operative document was the prior year's budget, which was itself adopted under disputed circumstances.</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Oct 7, 2025 Grealish email (thread ID: 199c0d60237afa6c): 'The budget for 2026-2027 will be prepared once the accountant completes the year end report...That report will be available around November 1st'; 'No harm done since any new budget will not become affective [sic] July 1, 2026'; Oct 29, 2025: CPA report and draft budget distributed — 4 months after fiscal year start; Nov 7, 2025: budget 'voted on' but no formal vote in audio recording (see M-02); DocsFromJeanne financial records showing ongoing expenditures during Jul–Nov 2025</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Four months of organizational spending with no board-approved budget. Grealish dismissed the problem by claiming 'no harm done' — while simultaneously blocking all committee oversight. Combined with F-05 (sole financial control) and F-06 (personal benefit from storage), the 4-month gap represents completely unaccountable spending by a single officer.</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Email-documented timeline — fiscal year gap confirmed</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="72" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>A-01</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Ongoing (confirmed Oct 30, 2025)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Auditing Committee Abandoned</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>PMTNM Handbook 2004 Section VII-D (Auditing Committee): 'Makes a complete audit of the books prior to (if possible) or during the State Conference. All figures in the ledgers, journals, check book, receipts, and vouchers should be checked. Makes a report at the State Conference Business Meeting.'</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>In her private letter to attorney Kathy Black (Oct 30, 2025), Grealish stated: 'PMTNM does not have a separate Finance Committee. It has not had an Auditing Comm. since hiring a CPA to double check all activity and file all required reports with IRS and the State of NM.' This is a written admission that a standing committee required by the PMTNM Handbook has been unilaterally eliminated.
 The distinction is legally critical: a CPA preparing tax returns and an annual fiscal report is NOT an audit. The handbook Auditing Committee is an internal oversight function — committee members verify the ledgers, journals, checkbook, receipts, and vouchers against each other and report at the State Conference. That independent check of the books has not existed for years. Kathy Black confirmed: 'The function of an audit committee should be to retain a CPA for a formal audit, which this organization does not do.'
 The elimination of the Auditing Committee means Grealish's financial records — held exclusively at her home with no online access, no other signatories, and no independent verification — have gone unchecked by any committee member. The CPA she hired (Mary Scofield) prepares reports based solely on materials Grealish provides her.</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Grealish private letter to Kathy Black, Oct 30, 2025 (forwarded to Chip by Kathy Black, Gmail thread ID: 19a3309ed58127ac): 'It has not had an Auditing Comm. since hiring a CPA to double check all activity and file all required reports with IRS and the State of NM'; Kathy Black Oct 30, 2025: 'The function of an audit committee should be to retain a CPA for a formal audit, which this organization does not do'; 2004 Handbook Section VII-D: verbatim Auditing Committee duties requiring complete audit at State Conference; CPA Mary Scofield — prepares tax returns only, not independent audit</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Standing committee required by the handbook has been eliminated without board vote. The internal financial oversight function that would have caught irregularities in storage expenses (F-10), personal property co-mingling (F-06), and sole-signatory arrangements (F-05) has not operated for years. Grealish's justification — hiring a CPA — is legally incorrect as preparation of tax returns is not an independent audit of the books.</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Grealish's own written admission — attorney-forwarded</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="72" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>M-06</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Oct 30, 2025 (confirmed in writing)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Records in Storage — Minutes Inaccessible</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>NM Nonprofit Corporation Act NMSA §53-8-26 — records must be available for inspection; PMTNM Handbook (2004): 'The records should be open to any member at all times' (EST duties section, re: Auditing Committee); Standard nonprofit governance — minutes are the authoritative record of corporate actions</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>In her private letter to Kathy Black (Oct 30, 2025), Grealish confirmed: 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings.' The board minutes — the organization's official legal record of all votes, decisions, and actions — are stored in the same storage unit where Grealish also stores personal furniture (F-06). Current financial records (CPA reports, checkbook, bank statements, deposit records, membership records) are kept at her personal home office.
 This means: (1) Past meeting minutes cannot be accessed without retrieving them from the storage unit. (2) Current financial records cannot be accessed without visiting Grealish's home. (3) 'PMTNM does not do online banking' — no electronic access exists. (4) When Kathy Black formally demanded records by Oct 31, 2025, Grealish said it was 'not physically possible' to comply. This is a textbook records-access failure under NMSA §53-8-26.</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Grealish private letter to Kathy Black, Oct 30, 2025 (Gmail thread ID: 19a3309ed58127ac): 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings'; 'Current files (CPA reports, checkbook, bank statements for all seven accounts, deposit records, and membership records) are kept in my home office at 1226 Morningside Dr. NE'; 'PMTNM does not do online banking'; 'It is not physically possible for me to bring the requested items to your office on Friday, October 31, 2025'; Kathy Black letter to Grealish (Oct 29, 2025) citing NMSA §53-8-27: formal demand for inspection of records</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Board meeting minutes — the organization's legal record of its decisions — are locked in a storage unit controlled solely by Grealish. When an attorney formally demanded records under NM statute, Grealish said it was physically impossible to produce them in a business day. Combined with F-05 (sole control), this means no board member, member, or attorney can independently verify any of PMTNM's financial history without Grealish's physical cooperation.</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Written admission in attorney-forwarded letter — direct statutory violation</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="72" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>F-15</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Spring 2025 (failure to act)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Budget Timing Violation</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish; Sharon Kunitz</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>PMTNM Handbook 2004 Section VII-E (Budget Committee): 'Meets before the Spring Board Meeting each year to prepare a budget for the coming year and presents it to the Executive Board for approval.'</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>The PMTNM Handbook requires the Budget Committee to meet BEFORE THE SPRING BOARD MEETING to prepare the budget for the coming fiscal year. PMTNM's fiscal year runs July 1 – June 30. For FY 2025-2026, the budget should have been prepared in spring 2025 (before a spring board meeting), approved by the Executive Board at that meeting, then recommended to the membership at the State Conference.
 Instead: No spring board meeting was held in 2025. No budget committee convened in spring 2025. The CPA was 'out of the country all summer.' The budget was not even drafted until October 29, 2025 — four months into the fiscal year — and was based on figures that only arrived October 26. The organization operated without any approved budget from July 1 through at least November 7, 2025.
 This is not a one-time delay. The pattern of fall-only board meetings and no spring budget process appears to be the standard practice under Grealish's administration.</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>Oct 7, 2025 Grealish email (thread ID: 199c0d60237afa6c): 'The budget for 2026-2027 will be prepared once the accountant completes the year end report... That report will be available around November 1st'; 2004 Handbook Section VII-E: 'Meets before the Spring Board Meeting each year'; No spring 2025 board meeting documented; Budget draft sent Oct 29, 2025 — 4 months into FY 2025-2026; Grealish Oct 7: 'No harm done since any new budget will not become affective [sic] July 1, 2026' [note: this confusingly refers to next year's budget, showing Grealish herself was confused about the timeline]</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>The handbook-required spring budget process has been systematically bypassed. No spring board meeting, no spring budget committee, no pre-fiscal-year budget approval. Four months of unauthorized spending under no approved budget. The person responsible for calling the committee is also the person whose spending would have been scrutinized by that committee.</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Documentary — handbook vs. actual calendar</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="72" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>M-07</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>November 7, 2025</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Minutes Falsification</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Legal + Ethics</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish (author/distributor); Sharon Kunitz (presiding officer)</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Fiduciary duty to maintain accurate organizational records; Nonprofit corporate record standards; State law on corporate minute accuracy; Robert's Rules of Order — accurate record of motions and votes</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>The November 7, 2025 board meeting minutes (distributed Mar 9, 2026, four months late) state: 'Secretary Treasurer's Report: The current report with financial summary was approved as presented.'
 The audio recording at timestamp 25:52 shows that Grealish mentioned the budget was 'prepared for 26/27' as a passing remark tacked onto the end of the designated accounts motion — no document was presented, no figures discussed, no motion made, no second, no vote. The only thing formally voted on in the Secretary-Treasurer's report section was the Mary Scofield CPA designated accounts motion, which the minutes do record separately.
 The 'approved as presented' language for the financial summary and budget is FABRICATED and appears nowhere in the audio recording. This fictitious approval retroactively authorizes Grealish's $1,750 annual honorarium for another fiscal year without a real vote. Chip had raised written questions about the honorarium on October 31, 2025 ('Has your honorarium increased through the years as our membership has decreased? What are the measures for your honorarium?') — questions that were never answered. The false minutes entry serves to lock in that compensation without board action.</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Audio Recording Nov 7, 2025, timestamp 25:52 — Grealish's remark without any motion, second, or vote; Nov 7 Minutes (distributed Mar 9, 2026) — falsified 'approved as presented' language; Oct 31, 2025 email — Chip's written questions about honorarium (thread ID: 19a3309ed58127ac); Audio recording ~46 minutes total — full context of Secretary-Treasurer's report section (no other votes on budget/financial summary)</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Minutes state a budget and financial summary were 'approved as presented,' but the audio recording proves no such motion or vote occurred. Minutes are a binding legal record of board action. A false entry that retroactively authorizes officer compensation constitutes falsification of corporate records — particularly when the fabrication appears 4 months after the meeting, after litigation has commenced.</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Audio-verified falsification — fabricated approval language contradicted by full recording</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="72" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>F-16</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Due Nov 15, 2019 — still overdue as of Oct 2025</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Regulatory Failure + False Statement</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Legal + Ethics</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>NM Nonprofit Corporation Act — annual report filing requirement with NM Secretary of State; Fiduciary duty of accurate regulatory compliance; Prohibition on false statements in official organizational records</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>On October 23, 2025, attorney Kathy Black reviewed PMTNM's NM Secretary of State business records and found: 'PMTNM's annual report is way overdue, with the due date listed as November 15, 2019.' The NM Secretary of State annual report has not been filed in over SIX YEARS.
 This directly contradicts a statement in PMTNM's own internal financial documents (Budget Documents, drafts approved by Board): 'All federal, state and local required documents and lists have been prepared and filed.' If this statement appeared in a report adopted by the board, it constitutes a false certification in an official organizational record — either Grealish failed to file and knew it, or she represented compliance to the board falsely.
@@ -3066,59 +3127,59 @@
 Also relevant: the NM AG Charitable Organization Registration (F-12) listed the organization as filing a 990-N and reporting 'solicited funds in NM: No.' The Secretary of State lapse compounds the regulatory picture: PMTNM has not maintained compliance with the most basic state corporate filing requirement since 2019, while Grealish continues to execute contracts (F-13: VIP Staffing, Oct 2025) and spend organizational funds as if the organization is in good standing.</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>Kathy Black email to Chip Oct 23, 2025: 'according to New Mexico Secretary of State business records, PMTNM's annual report is way overdue, with the due date listed as November 15, 2019'; Kathy Black email Oct 30, 2025: 'At the very least, I am going to point out that the State of New Mexico annual report has not been filed'; PMTNM internal document ('Budget Documents, drafts approved by Board (1).pdf' in Drive — PMTNM folder): 'All federal, state and local required documents and lists have been prepared and filed' — DIRECT CONTRADICTION of Secretary of State records; NM Secretary of State public business records (verifiable)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>PMTNM has been operating for 6+ years without filing its required NM Secretary of State annual report. Its own internal financial documents affirmatively claim all required filings are current — a false statement in an official record. This is simultaneously a regulatory failure, a false representation to the board, and evidence that Grealish's self-reported compliance ('The Executive Secretary-Treasurer shall be responsible for... filing of all returns with IRS, NM Taxation and Revenue Department, the NM State Corporation Commission, and any other government entity') has not been fulfilled.</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Attorney-identified + contradicted by PMTNM's own internal document</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44" ht="72" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>F-12</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Tax Year 2018 (filed ~2019); Tax Year 2023 (filed Dec 18, 2024); Tax Year 2024 (filed Dec 12, 2025)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Regulatory / Sole Control</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>NM Attorney General Charitable Organization Registration requirements; IRS NTEE classification accuracy; NM Solicitation Disclosure Act; NM Nonprofit Corporation Act — officer record accuracy</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>THREE YEARS OF NM AG FILINGS REVIEWED — IDENTICAL SOLE-CONTROL PATTERN ACROSS DECADE:
 TAX YEAR 2018 (filed ~2019):
@@ -3129,116 +3190,116 @@
 (1) All five financial functions REMAIN solely Grealish. (2) Net assets declined from $62,500 to $60,555 (continuing decade-long decline from $81,975 in 2014 — total erosion of $21,420 or 26%). (3) Total gross revenue $7,114 (down 70% from $23,963 in 2014). (4) Total contributions $0.00 despite 'Special Events' and 'Personal Contact' listed as solicitation methods. (5) 'Solicited funds in NM: No' answered false for the eleventh consecutive year — systematic false statement across the entire regulatory history. (6) Chip Miller (Vice President) listed on filing. (7) This filing was submitted after the lawsuit was filed, suggesting a document created under legal awareness.</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>NM AG Registration Tax Year 2018 (physical PDF: 20184721935751263.pdf); NM AG Registration Tax Year 2023 (physical PDF: 20234722435369467 (2).pdf); NM AG Registration Tax Year 2024 (filed Dec 12, 2025), FEIN 85-0284938; VP appointment email from Sharon Kunitz, Aug 14, 2024 — establishes Chip's VP status; IRS BMF confirming 990-N filer; Internal financial records (DocsFromJeanne) and Kathy Black Initial Impressions confirming same sole-control pattern 2024-2025</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Three independent NM AG filings across a decade show IDENTICAL sole-control structure. The 'solicited funds in NM: No' false statement appears in all three filings despite documented solicitation activity — a systematic misrepresentation maintained throughout the regulatory history. The Tax Year 2024 filing (submitted after the lawsuit was filed) documents that Chip Miller was the VP during that year, yet all financial control remained with Grealish. Net assets and revenue continue their decade-long decline while officer compensation (Grealish honorarium) increased from 6.3% to 24.6% of revenue — compensation rising as the organization shrinks.</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>THREE physical documents reviewed — entire decade pattern confirmed at NM AG level</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="72" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>F-13</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Oct 23, 2025</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Unauthorized Contract</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Legal + Governance</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Nonprofit governance — contracts above a de minimis threshold require board authorization; PMTNM Handbook on financial authority; Fiduciary duty</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>On October 23, 2025, PMTNM entered into a Master Terms &amp; Conditions agreement with VIP Staffing — a commercial staffing agency. Three versions of this contract are preserved in Google Drive (draft, executed, and a third copy), all dated Oct 23, 2025. PMTNM is identified as the 'Customer.' For a nonprofit that (a) filed 990-N (revenue under $50K threshold), (b) had FY2018 revenue of only $18,817, (c) claims in the NM AG filing it does not solicit funds, and (d) operates from Grealish's personal home — entering a commercial staffing contract is a significant financial and legal commitment. No board vote authorizing this contract appears in any board minutes. The Nov 7, 2025 board meeting (the only documented board meeting during this period) contains no reference to a staffing contract. Grealish, as sole financial officer, appears to have executed this agreement unilaterally.</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Google Drive: '2025-10-23T16-25-09.000Z - 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1OGc7fLQguB3-ZDiqXpuUxF83sK2Rcy-L); '2025-10-23T16-49-03.000Z - Executed 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1nQAsasqmpAAk9d3-ZZJum3j4a70G92kZ); Nov 7, 2025 Board Meeting minutes and audio — no reference to any staffing contract; No board resolution authorizing staffing agreement found</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>A commercial staffing contract executed without board authorization — by the sole financial officer of a nonprofit operating at a deficit. The contract requires PMTNM to carry Comprehensive General Liability Insurance and Employment Practices Liability Insurance. Whether PMTNM actually maintains this insurance is unknown. The agreement also contains a one-year non-solicitation clause that would bind PMTNM as an organization. This is precisely the kind of significant financial obligation that requires board authorization under standard nonprofit governance.</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Physical contracts reviewed in Drive — no board authorization documented</t>
         </is>
       </c>
     </row>
     <row r="45" ht="72" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Oct 23, 2025</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Unauthorized Contract</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Legal + Governance</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Nonprofit governance — contracts above a de minimis threshold require board authorization; PMTNM Handbook on financial authority; Fiduciary duty</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>On October 23, 2025, PMTNM entered into a Master Terms &amp; Conditions agreement with VIP Staffing — a commercial staffing agency. Three versions of this contract are preserved in Google Drive (draft, executed, and a third copy), all dated Oct 23, 2025. PMTNM is identified as the 'Customer.' For a nonprofit that (a) filed 990-N (revenue under $50K threshold), (b) had FY2018 revenue of only $18,817, (c) claims in the NM AG filing it does not solicit funds, and (d) operates from Grealish's personal home — entering a commercial staffing contract is a significant financial and legal commitment. No board vote authorizing this contract appears in any board minutes. The Nov 7, 2025 board meeting (the only documented board meeting during this period) contains no reference to a staffing contract. Grealish, as sole financial officer, appears to have executed this agreement unilaterally.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Google Drive: '2025-10-23T16-25-09.000Z - 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1OGc7fLQguB3-ZDiqXpuUxF83sK2Rcy-L); '2025-10-23T16-49-03.000Z - Executed 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1nQAsasqmpAAk9d3-ZZJum3j4a70G92kZ); Nov 7, 2025 Board Meeting minutes and audio — no reference to any staffing contract; No board resolution authorizing staffing agreement found</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>A commercial staffing contract executed without board authorization — by the sole financial officer of a nonprofit operating at a deficit. The contract requires PMTNM to carry Comprehensive General Liability Insurance and Employment Practices Liability Insurance. Whether PMTNM actually maintains this insurance is unknown. The agreement also contains a one-year non-solicitation clause that would bind PMTNM as an organization. This is precisely the kind of significant financial obligation that requires board authorization under standard nonprofit governance.</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Physical contracts reviewed in Drive — no board authorization documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="72" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>F-17</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Ongoing (documented 2014–2025); FY2024–25 Authorization Denied</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Financial / Officer Compensation</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish (recipient); Sharon Kunitz (presiding officer, failed oversight); Larry Blind (Nominating Chair, failed oversight)</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Nonprofit governance — officer compensation requires board approval; PMTNM Handbook duties for EST and President; Fiduciary duty to manage organizational resources; NM corporate law — board's duty to authorize material expenses</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Grealish (Executive Secretary-Treasurer) has received annual compensation ('honorarium') of at least $1,500 (Tax Year 2014) rising to $1,750 (Tax Year 2024), disclosed in NM AG filings but never appearing in IRS records because PMTNM files 990-N. The sole financial controller of all five functions (check signing, fundraising, fund distribution, financial records, custody of funds) is the same person receiving this compensation. No independent oversight exists.
 In fiscal year 2024–25 (the year Chip served as VP), the budget containing this compensation was never formally voted on by the board:
@@ -3253,59 +3314,59 @@
 As membership and revenue collapsed 70% over a decade, Grealish's share of organizational revenue nearly quadrupled. The Tax Year 2024 NM AG filing (submitted December 12, 2025 — after the lawsuit was filed) shows $1,750 compensation resting on a board approval the audio recording and minutes contradiction prove never happened.</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>NM AG Registration filings Tax Year 2014–2024 (pattern documented); Oct 31–Nov 6, 2025 'Budget Committee REMINDER' email thread (Gmail ID: 19a3309ed58127ac); Nov 7, 2025 Audio Recording, timestamp 25:52 — no motion or vote on budget; Nov 7, 2025 Minutes (distributed Mar 9, 2026): falsified 'approved as presented' language (see M-07); NM AG Tax Year 2024 filing (submitted Dec 12, 2025) showing $1,750 compensation; Revenue data from IRS EO BMF and NM AG filings 2014–2024</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>A manager received continuous compensation without formal board authorization in the final fiscal year reviewed. The email-based budget process bypassed handbook requirements (F-02). The Nov 7 board meeting produced no motion to approve the budget — only a fabricated minutes entry (M-07). The compensation increased from 6.3% to 24.6% of declining revenue, while the sole financial officer remained unilaterally in control. This is foundational financial governance failure.</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Audio-verified (no motion), Minutes-contradicted (fabricated approval), NM AG-documented (11-year pattern)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="72" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47" ht="72" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>G-02</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Nov 7, 2025 (pre-meeting emails + meeting)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Anonymous Voting Suppressed + No Confidence Motion Defeated</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Governance + Ethics</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Larry Blind (procedural suppression); Sharon Kunitz (adjournment); Jeanne Grealish (subject of motion, present during vote call)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Robert's Rules of Order Newly Revised 12th ed. §§45:5–7, 46:32–34 (ballot voting must preserve anonymity); Robert's Rules §4 (main motions); Nonprofit governance — board members' duty to consider officer accountability motions</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>TWO-PART VIOLATION — PRE-MEETING SUPPRESSION AND IN-MEETING PROCEDURAL DEFEAT:
 PART 1: ANONYMOUS VOTING SYSTEM PREPARED AND IGNORED (Nov 7, morning, Gmail thread: 19a5ea6717e3582c)
@@ -3325,59 +3386,59 @@
 PATTERN ACROSS TWO CONSECUTIVE ELECTIONS: True anonymous voting was never available to online board members under Larry's administration. 2024: votes texted to Larry's personal cell at his own school. 2025: Chip's RROO-compliant ElectionChamp system (15 board members loaded, ready by 10:55 AM) was rejected by Larry that morning; vote run publicly instead with Grealish in the room. Two election cycles, zero genuine anonymous voting for online members. The 2025 suppression was not an oversight — it was a continuation of established practice.</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>Gmail thread 19a5ea6717e3582c — full pre-meeting exchange: Sharon 7:07 AM (time limits); Chip 8:54 AM (anonymous voting proposal, RROO citation, two platforms offered); Larry 10:00 AM (dismissive, to Sharon only: 'getting someone to the point of a motion can be challenging'); Larry 10:11 AM (text-to-one-phone counter-proposal — not anonymous); Chip 10:27 AM (explains why Larry's method fails RROO ballot standards); Chip 10:55 AM ('ElectionChamp is set up'  — 15 board member emails loaded, test sent); Nov 7 Audio Recording 46:34–49:13: motion made, public hand-raise call, no second, motion dies; Sharon 49:13: adjourns; Gmail thread 1928ce26b2fe3d9c — 'PMTNM Board and General Membership Meetings' (approx. Oct 14, 2024): Larry announces online members should text votes to personal cell (505) 980-3941; meeting held at NM School of Music (Larry's school) — establishes 2-year pattern of non-anonymous online voting</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>A proper anonymous voting system was live and ready. Larry rejected it that morning in favor of a non-anonymous alternative, then ran the vote publicly with the subject of the motion in the room. Members who might have seconded the motion anonymously were instead exposed to full social and professional visibility. The motion's failure cannot be separated from the voting environment Larry created and the anonymous option he suppressed.</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Email-verified pre-meeting + Audio-verified in-meeting — anonymous voting deliberately bypassed — Trigger: Nov 5, 7:03 PM forward to MTNA/attorney preceded Nov 6 coordination</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="72" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="48" ht="72" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>L-07</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Nov 7, 2025 (and ongoing 2024-2025)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Conflict of Interest / Structural Governance</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Ethics + Governance + Procedural</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Larry Blind (three simultaneous conflicting roles); Sharon Kunitz (failed to manage or disclose)</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>PMTNM Handbook 2004 Section VII-Q (Nominating Committee chaired by Immediate Past President — controls VP succession); Section VI-C (President duty: 'keeps a close liaison with all officers' and should allocate duties to VP — not fulfilled while receiving exclusive advisory counsel from Past President); Robert's Rules of Order — Parliamentarian must be impartial and free of conflicts; Standard nonprofit governance — board members holding multiple conflicting roles must disclose them</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>At the November 7, 2025 board meeting and in the weeks leading up to it, Larry Blind simultaneously held THREE distinct roles — none of which were disclosed as conflicting and none of which had any handbook-defined boundaries or recusal process:
 (1) PAST PRESIDENT / INFORMAL ADVISOR TO SHARON: The 2004 PMTNM Handbook Section VI defines duties for State President, Vice President, EST, and District VPs. The Past President is NOT defined in Section VI. The advisory relationship is conventional — meaning no handbook language defines its scope, limits, or conflict-of-interest requirements. This gave Larry an unconstrained, informal advisory channel to Sharon with no procedural safeguards.
@@ -3388,74 +3449,74 @@
 NO CONFLICT DISCLOSURE, NO RECUSAL, NO PROCEDURE: There is no PMTNM conflict-of-interest policy in the handbook. No disclosure of Larry's three simultaneous roles was made at the Nov 7 meeting. No recusal procedure existed. Larry ruled on parliamentary questions at the same meeting where he had been advising the President against the VP and where he controlled the VP successor nomination process.</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>2004 PMTNM Handbook Section VII-Q (Nominating Committee: Past President chairs by convention — not formally defined in Section VI); 2004 Handbook Section VI-C (President duties: 'Keeps a close liaison with all officers' — not extended to VP during Larry's advisory relationship); Nov 7, 2025 10:00 AM email from Larry — reply to Sharon only, not Chip (Gmail thread 19a5ea6717e3582c): 'There may be a lot of talking, but getting someone to the point of a motion can be challenging' — advisory communication bypassing VP; Nov 7 Audio Recording: Larry as Parliamentarian ruling on procedural questions; Nov 7 Minutes: Larry named as Parliamentarian; Nov 5-6 hostile email from Larry to Chip (L-04): 'offensive, disrespectful, and does not deserve a response' — demonstrates pre-existing personal animus that preceded his impartial parliamentary role; No conflict-of-interest policy found in 2004 PMTNM Handbook</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Three simultaneous conflicting roles — advisor, succession controller, parliamentary authority — held without disclosure or recusal. The informal advisory channel had no handbook boundaries. Larry's 10:00 AM email proves the advisory channel was used to coordinate meeting strategy against the VP hours before the meeting. Parliamentary rulings at Nov 7 were made by a person who had been advising the President in that direction since at least 10 AM. The Nominating Committee process is further compromised by Larry's documented financial conflicts (L-01 through L-06) and his use of organizational roles for personal and commercial benefit.</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Handbook-verified + Email evidence (10:00 AM advisory communication) + Audio record — three undisclosed simultaneous roles</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="72" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49" ht="72" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>G-03</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Oct 28, 2023 (approx.)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Unilateral Conference Decision</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Governance + Conflict of Interest</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Lawrence Blind</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Standard nonprofit governance — significant organizational decisions require board approval and oversight; PMTNM Handbook (silent on conference programming authority, indicating governance gap); Fiduciary duty of loyalty — using organizational position and resources for personal/institutional benefit without disclosure</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The decision appears to have been communicated directly to PMTNM member teachers in late October 2023. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure. The fact of NMSM students' participation in the 2023 PMTNM conference is independently corroborated in L-02 (ethics complaint filed Nov 14, 2023 and conference program documentation).</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions; Independent corroboration: L-02 (Nov 14, 2023 ethics complaint to MTNA) and conference program/documentation from 2023 confirming NMSM student participation in PMTNM conference</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>Unilateral decision-making by a president without board oversight. Direct self-dealing: using PMTNM's conference platform to promote his own school and student base. Absence of conflict-of-interest management or disclosure. Pattern-consistent with leadership's broader governance approach (see G-01: 'PMTNM does not function under any legal mandates'). Even if conference programming fell within the president's delegated authority, the absence of any disclosure mechanism for conflicts of interest represents governance failure.</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Documented via board minutes record (absence of decision) + independent corroboration via L-02 ethics complaint and conference documentation — Pattern consistent with unilateral leadership style</t>
         </is>
@@ -5816,7 +5877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6732,6 +6793,33 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Lawrence Blind — Oct 12, 2023 text message to Chip Miller (NMSM context)</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>'Chip, please do not contact any of your former students from our school by phone or email. This is not appropriate.'</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>E-04, L-04</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Used NMSM authority to block teacher from complying with MTNA Code of Ethics requiring teacher participation in student transitions. When escalated to MTNA (Jul 2024), the organization could not enforce ethics standards because Larry designed NMSM handbook to conflict with MTNA code. Pattern: systematically uses organizational structure to block accountability mechanisms.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A12:E12"/>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Violations Database" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="By Person" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Key Email Threads" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MTNA Ethics Cross-Ref" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Violations Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Person" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Email Threads" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MTNA Ethics Cross-Ref" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -329,8 +329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K49" headerRowCount="1">
-  <autoFilter ref="A1:K49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K50" headerRowCount="1">
+  <autoFilter ref="A1:K50"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3522,6 +3522,74 @@
         </is>
       </c>
     </row>
+    <row r="50" ht="72" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>L-08</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Nov 8, 2024; Nov 7, 2025</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Undisclosed Voting Conflict / Proxy Voting</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Governance + Conflict of Interest</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Marcus York; Lawrence Blind (as supervisor/authority)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Nonprofit governance — voting members must disclose conflicts of interest; PMTNM governance standards requiring impartial board member conduct; Proxy voting prohibition under standard nonprofit law; Fiduciary duty of loyalty</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Marcus York, an employee/associate of NM School of Music (which is controlled by Lawrence Blind as owner/director), voted on critical financial matters at PMTNM board meetings while his employment relationship with Blind and his role on the Nominating Committee (chaired by Blind) were undisclosed:
+NOVEMBER 8, 2024 BOARD MEETING (Blind was President):
+— Marcus York made a motion on the Treasurer's Financial Report (which was 'unanimously approved')
+— Marcus York seconded a motion on the Budget (which was 'declared in order')
+— York was physically in-person at the meeting held at NM School of Music (Blind's school)
+— No disclosure of NMSM employment relationship appears in the minutes
+— No conflict-of-interest statement or recusal was documented
+NOVEMBER 7, 2025 BOARD MEETING (Blind was no longer President but served as Parliamentarian):
+— Marcus York was listed as a member of the Nominating Committee, chaired by Lawrence Blind
+— The Nominating Committee controlled VP succession — a position Blind had just vacated and that was critical to the no-confidence motion against Grealish
+— York was not physically present at this Nov 7 meeting, but his continued appointment to the Blind-chaired Nominating Committee represents an ongoing undisclosed conflict
+THE CONFLICT: York was voting (Nov 2024) on matters affecting the organization while being employed by someone with authority over him, while also serving on a committee chaired by that same person that controlled officer succession. NMSM's organizational authority structure gave Blind direct control over York's employment, creating the classic hallmark of proxy voting: a voting member whose interests are materially affected by someone else's authority.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Board Minutes Nov 8, 2024: 'With a motion by Marcus York and a second by Sharon Kunitz the Treasurer's current financial report was unanimously approved'; 'Upon a motion by Janna Warren with a second by Marcus York [budget] was declared in order'; Meeting location: 'New Mexico School of Music, Albuquerque'; Board Minutes Nov 7, 2025: 'Nominating Committee Slate of Officers for 2026-2027: Chair Lawrence Blind thanked his committee members Astrid Groth and Marcus York'; Marcus York's NMSM email/employment confirmed in July 2024 communication identifying him as associated with 'the School of Music'</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>A voting board member whose employment is controlled by someone else (Blind) voted on financial matters while serving on a succession-control committee chaired by that same person. No conflict was disclosed. This pattern extends Blind's demonstrated use of organizational positions to embed people aligned with his interests — similar to how he controlled the 2023 TOTY vote through his employee Tatiana. York's position represents potential proxy voting: his vote on financial matters affected the organization's assets, but his employment relationship with Blind creates a conflict of interest in that voting.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Board minutes verified — undisclosed conflict documented across two consecutive board meeting cycles</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3536,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4225,19 +4293,19 @@
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (Former President)</t>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Marcus York (Board Member / NMSM Employee)</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
+          <t>Voted on financial matters (Nov 2024) while employed by Larry Blind; served on Blind-chaired Nominating Committee (Nov 2024–2025) — no disclosure of conflict; proxy voting concern due to Blind's employment authority over York</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4317,12 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
+          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4334,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
+          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4351,12 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
+          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4368,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
         </is>
       </c>
     </row>
@@ -4317,29 +4385,29 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz (Former President)</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
           <t>M-05</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>VP excluded from board packet mailing; VP's agenda items not addressed</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4419,12 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4368,10 +4436,27 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Brian Shepard (MTNA CEO)</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
           <t>E-03</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Sep 2025 + Dec 2025 affiliate complaints — deferred entirely to affiliate self-governance</t>
         </is>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Undisclosed Voting Conflict / Proxy Voting</t>
+          <t>Unmanaged Conflict of Interest / Proxy Voting</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Nonprofit governance — voting members must disclose conflicts of interest; PMTNM governance standards requiring impartial board member conduct; Proxy voting prohibition under standard nonprofit law; Fiduciary duty of loyalty</t>
+          <t>Nonprofit governance — voting members with conflicts of interest must be subject to formal conflict-of-interest procedures (disclosure, recusal, abstention); PMTNM governance standards requiring impartial board member conduct; Proxy voting prohibition under standard nonprofit law; Fiduciary duty of loyalty</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Marcus York, an employee/associate of NM School of Music (which is controlled by Lawrence Blind as owner/director), voted on critical financial matters at PMTNM board meetings while his employment relationship with Blind and his role on the Nominating Committee (chaired by Blind) were undisclosed:
+          <t>Marcus York, an employee of NM School of Music (controlled by Lawrence Blind as owner/director), voted on critical financial matters at PMTNM board meetings while under employment relationship with Blind — with no formal conflict-of-interest procedure to manage or mitigate that relationship. Although PMTNM members likely knew York worked for Larry, the board took no formal action to address this conflict:
 NOVEMBER 8, 2024 BOARD MEETING (Blind was President):
 — Marcus York made a motion on the Treasurer's Financial Report (which was 'unanimously approved')
 — Marcus York seconded a motion on the Budget (which was 'declared in order')
@@ -3581,12 +3581,12 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>A voting board member whose employment is controlled by someone else (Blind) voted on financial matters while serving on a succession-control committee chaired by that same person. No conflict was disclosed. This pattern extends Blind's demonstrated use of organizational positions to embed people aligned with his interests — similar to how he controlled the 2023 TOTY vote through his employee Tatiana. York's position represents potential proxy voting: his vote on financial matters affected the organization's assets, but his employment relationship with Blind creates a conflict of interest in that voting.</t>
+          <t>A voting board member whose employment is controlled by someone else (Blind) voted on financial matters while serving on a succession-control committee chaired by that same person. Although people knew York worked for Larry, the board took no formal action to manage this conflict — no required disclosure, no recusal procedure, no abstention protocol. PMTNM has no written conflict-of-interest policy. This pattern extends Blind's demonstrated use of organizational positions to embed people aligned with his interests — similar to how he controlled the 2023 TOTY vote through his employee Tatiana. York's situation represents proxy-voting conditions: voting on matters affecting the organization while under employment relationship with an interested party, with no organizational safeguards.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Board minutes verified — undisclosed conflict documented across two consecutive board meeting cycles</t>
+          <t>Board minutes verified — unmanaged employment conflict documented across voting and committee roles</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Voted on financial matters (Nov 2024) while employed by Larry Blind; served on Blind-chaired Nominating Committee (Nov 2024–2025) — no disclosure of conflict; proxy voting concern due to Blind's employment authority over York</t>
+          <t>Voted on financial matters (Nov 2024) while employed by Larry Blind; served on Blind-chaired Nominating Committee (Nov 2024–2025) — no formal conflict-of-interest procedure invoked; unmanaged proxy voting situation due to Blind's employment authority over York</t>
         </is>
       </c>
     </row>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -329,8 +329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K50" headerRowCount="1">
-  <autoFilter ref="A1:K50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K51" headerRowCount="1">
+  <autoFilter ref="A1:K51"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2219,27 +2219,27 @@
     <row r="28" ht="72" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nov 7, 2025 → Mar 9, 2026</t>
+          <t>Date of distribution unknown (referenced in 'PMTNM. LIST AND EMAIL ADDRESSES' thread)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Records Distribution</t>
+          <t>Inaccurate Credential Documentation</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Records + Governance</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2249,39 +2249,39 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Standard nonprofit governance — minutes should be distributed within 30-60 days; PMTNM handbook on minutes distribution</t>
+          <t>Nonprofit record-keeping standards; Accuracy of member status documentation; Fiduciary duty to maintain accurate organizational records; MTNA credential verification</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>November 7, 2025 board meeting minutes were dated January 1, 2026 and not distributed until March 9, 2026 — four months after the meeting. Distribution came after the petition was already filed (Feb 2026) and after PMTNM's answer was filed (Mar 5, 2026).</t>
+          <t>PMTNM's official internal member list ('PMTNM. LIST AND EMAIL ADDRESSES') lists Sharon Kunitz as 'NCTM' (National Certified Teacher of Music). Official MTNA data (MTNAData.csv, dated 2024) shows Sharon Kunitz with a blank DESIGNATION field — no NCTM credential listed. By contrast, verified NCTMs in the same MTNA dataset (Jeanne Grealish, Cheryl Pachak-Brooks, and others) all display 'NCTM' in the DESIGNATION field. NCTM is an earned honor from MTNA requiring ongoing fees and maintenance. Sharon either never attained the credential, allowed it to lapse, or failed to renew. Grealish, as Executive Secretary-Treasurer responsible for accurate member records, circulated an official organizational document misrepresenting Sharon's status. This is particularly problematic because: (1) it damages organizational credibility with external parties, (2) it reflects the pattern of inaccurate record-keeping by Grealish (R-01, R-02, R-03, M-04), and (3) it involves Sharon, who has been Grealish's consistent supporter on the board despite receiving scholarship funds controlled by Grealish (S-01).</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Jan 1, 2026 date on minutes; Mar 9, 2026 distribution email from Grealish; Petition filed Jan 27, 2026; PMTNM Answer filed Mar 5, 2026</t>
+          <t>Official MTNA data (MTNAData.csv): Sharon Kunitz (row 40) shows blank DESIGNATION field vs. Jeanne Grealish (row 30) and Cheryl Pachak-Brooks (row 52) both showing 'NCTM' in DESIGNATION field; PMTNM internal member list email thread ('PMTNM. LIST AND EMAIL ADDRESSES'): lists Sharon as NCTM; Email attachment: 'Email addresses (2).xlsx' showing same false NCTM designation for Sharon</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>4-month delay in distributing minutes is itself a governance failure. Timing of distribution (after legal proceedings filed) raises questions about deliberate delay.</t>
+          <t>False representation of member credentials in official organizational documentation. Pattern of inaccurate EST record-keeping. Damages organizational credibility. Misrepresentation could affect external perceptions of PMTNM's accuracy and governance.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Documented — Suspicious timing</t>
+          <t>Documented — MTNA data vs. PMTNM internal list verified</t>
         </is>
       </c>
     </row>
     <row r="29" ht="72" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Apr 25, 2025 → Nov 7, 2025</t>
+          <t>Nov 7, 2025 → Mar 9, 2026</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2294,9 +2294,9 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2306,160 +2306,160 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Standard practice — spring board meeting minutes should be distributed before fall meeting</t>
+          <t>Standard nonprofit governance — minutes should be distributed within 30-60 days; PMTNM handbook on minutes distribution</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>As of Oct 9, 2025, Grealish stated spring minutes had not been distributed and would be 'compiled and sent with Nov first' board reports. Spring minutes (April 2025) were not circulated until November — a 7-month delay. This was noted in Chip's Oct 14 agenda request email.</t>
+          <t>November 7, 2025 board meeting minutes were dated January 1, 2026 and not distributed until March 9, 2026 — four months after the meeting. Distribution came after the petition was already filed (Feb 2026) and after PMTNM's answer was filed (Mar 5, 2026).</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Oct 9, 2025 Grealish email re: minutes distribution; Oct 14 VP Agenda Request email documenting this; Nov 7 Board Meeting (April minutes addressed at start of meeting)</t>
+          <t>Jan 1, 2026 date on minutes; Mar 9, 2026 distribution email from Grealish; Petition filed Jan 27, 2026; PMTNM Answer filed Mar 5, 2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Pattern of chronic delays in distributing meeting records. Creates information asymmetry between Grealish-aligned insiders and officers like Chip who have no independent access.</t>
+          <t>4-month delay in distributing minutes is itself a governance failure. Timing of distribution (after legal proceedings filed) raises questions about deliberate delay.</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Documented</t>
+          <t>Documented — Suspicious timing</t>
         </is>
       </c>
     </row>
     <row r="30" ht="72" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Apr 25, 2025 → Nov 7, 2025</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Records Distribution</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Standard practice — spring board meeting minutes should be distributed before fall meeting</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>As of Oct 9, 2025, Grealish stated spring minutes had not been distributed and would be 'compiled and sent with Nov first' board reports. Spring minutes (April 2025) were not circulated until November — a 7-month delay. This was noted in Chip's Oct 14 agenda request email.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Oct 9, 2025 Grealish email re: minutes distribution; Oct 14 VP Agenda Request email documenting this; Nov 7 Board Meeting (April minutes addressed at start of meeting)</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Pattern of chronic delays in distributing meeting records. Creates information asymmetry between Grealish-aligned insiders and officers like Chip who have no independent access.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>L-05</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Oct 2023</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>TOTY Manipulation</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Ethics + Governance</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Larry Blind; Tatiana Vetrinskaya (NMSM)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>MTNA Code of Ethics §3 (conflicts of interest); Nonprofit election integrity; Robert's Rules on impartiality</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>2023 TOTY had two nominees: Terri Reck (nomination written by Jackie Zander-Wall, AMTA president) vs. Tatiana Vetrinskaya (nomination written by Larry Blind, her employer and NMSM director). Larry administered the vote from lblind@nmschoolofmusic.com and explicitly stated in his voting email: 'I decided to extend the nomination period' — a unilateral extension with no board approval. Chip's side-by-side analysis: Terri Reck's bio = 'dense list of information highlighting work done in the PMTNM community this past year.' Tatiana's bio (written by Larry) = 'storybook language throughout that causes emotional reactions, often unrelated to the question at hand. Highlights work done in NMSM.' Haewon Yang admitted voting for 'the person whose bio looked the best.' Tatiana won. No conflict of interest was disclosed by Larry.
 VERBATIM FROM TATIANA'S ACTUAL SUBMISSION (submitted by lawrenceblind@msn.com, signed 9-30-23): Community service section = entirely NMSM activities. Closing line: 'business acumen... it is what I know she is most proud of.' [Note: 'business acumen' is not a PMTNM TOTY criterion.] Future-tense item listed under achievements: 'will present a workshop at 2023 PMTNM Conference' — event had not yet occurred at time of submission. Tatiana's listed email: tatiana@nmschoolofmusic.com (NMSM institutional address).
 VERBATIM FROM TERRI RECK'S ACTUAL SUBMISSION (submitted by zanderwall@gmail.com / Jacqueline Zander-Wall, signed 9/30/23): 47 years of teaching (1976–2023). Dalcroze certification across 6 institutions. 5 AMTA committee leadership roles. Harpsichord performances with SF Symphony, NM Symphony, NM Philharmonic. Students enrolled in PMTNM/MTNA programs. Music Bowl Chair for decades. Jewelry donated to PMTNM silent auctions.</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>Oct 4, 2023 email from lblind@nmschoolofmusic.com TO lblind@nmschoolofmusic.com (BCC to board): Larry explicitly states 'I decided to extend the nomination period'; Two TOTY PDFs sent with vote solicitation: 'Terri Reck.pdf' and 'Tatiana Vetrinskaya.pdf' (Gmail thread ID: 19239a27e03b7010); PHYSICAL PDFs READ — Tatiana's PDF: submitted by lawrenceblind@msn.com, Tatiana email tatiana@nmschoolofmusic.com, closing 'business acumen — it is what I know she is most proud of,' future-tense 'will present a workshop at 2023 PMTNM Conference,' all community service through NMSM; Terri's PDF: submitted by zanderwall@gmail.com, 47 years teaching, Dalcroze certification, 5 AMTA committee roles, harpsichord with major orchestras, decades as Music Bowl Chair, jewelry to PMTNM silent auctions; Haewon thread Sep 27-28, 2024: 'last year I voted for Tatyana because I had no idea who these people were and just voted for the person whose bio looked the best'; Chip to Jackie Sep 29, 2024: 'The other submission paints a picture of a larger timeframe and uses storybook language throughout that causes emotional reactions, and are often unrelated to the question at hand. It highlights work done in NMSM'; Jacqueline Zander-Wall response: 'I am not contesting the decision made at all. I think one needs to move on.'</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>Employer wrote a polished 'storybook' bio for his employee vs. an independent teacher's factual PMTNM community service record. The winning submission listed a future event (not yet a completed achievement), described 'business acumen' (not a TOTY criterion), and used the nominee's NMSM institutional email — all pointing to an NMSM marketing document rather than a community service record. The losing submission documented 47 years of verifiable community service across PMTNM, AMTA, and major NM orchestras. Vote administered by the conflicted party from NMSM business email. Unilateral deadline extension. Haewon's admission confirms votes cast on presentation quality, not merit. Jackie Zander-Wall (AMTA president) declined to contest — the quiet resignation of a community teacher facing institutional power.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Email evidence + Haewon on-record admission + Chip comparative analysis (verbatim) + PHYSICAL PDFs READ AND ANALYZED</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="72" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>L-06</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Ongoing 2023–2025</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>NMSM Business Promotion via PMTNM</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Ethics + Financial</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Larry Blind</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>MTNA Code of Ethics: 'Represent our art honestly'; IRS private benefit prohibition; Nonprofit duty of loyalty</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Larry's NMSM director biography uses systematically misleading language: 'students have an opportunity to perform internationally' (they pay to attend European recitals — this is not performance, it is tourism); 'returned for an encore performance' at Carnegie Hall (how he accessed the hall is unsubstantiated — the concern is the misleading framing). NMSM employs uncredentialed faculty (flute majors teaching piano, teachers in first jobs). Larry used PMTNM's conference platform and handbook to promote NMSM, diluting PMTNM value to independent member teachers whose market is directly harmed by NMSM's growth.</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>NMSM director biography (nmschoolofmusic.com/director---lawrence-blind — live web evidence); 2023 PMTNM conference program featuring NMSM students; VP Report documenting biography misrepresentation; PMTNM member impact analysis</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Using nonprofit organizational credibility and platform to market a competing commercial music school. Misleading language in NMSM materials violates MTNA's core principle of honest representation. NMSM's 700-student enrollment at $70/hr directly harms independent PMTNM members' livelihoods.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Web evidence + conference records + VP Report</t>
         </is>
       </c>
     </row>
     <row r="32" ht="72" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>F-10</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>Ongoing 2023–2025</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Financial Self-Dealing</t>
+          <t>NMSM Business Promotion via PMTNM</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2474,170 +2474,170 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Jeanne Grealish</t>
+          <t>Larry Blind</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>IRS private benefit prohibition; Fiduciary duty; PMTNM budget oversight</t>
+          <t>MTNA Code of Ethics: 'Represent our art honestly'; IRS private benefit prohibition; Nonprofit duty of loyalty</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Storage unit operating expense documented as $4,600 actual vs. $3,000 budgeted — a 53% overrun. Even Larry Blind, who has a financial relationship with Grealish, raised the discrepancy in a Nov 2 email asking about the expense. Grealish had already admitted (before attorney Kathy Black) that she stores personal furniture in the PMTNM storage unit.</t>
+          <t>Larry's NMSM director biography uses systematically misleading language: 'students have an opportunity to perform internationally' (they pay to attend European recitals — this is not performance, it is tourism); 'returned for an encore performance' at Carnegie Hall (how he accessed the hall is unsubstantiated — the concern is the misleading framing). NMSM employs uncredentialed faculty (flute majors teaching piano, teachers in first jobs). Larry used PMTNM's conference platform and handbook to promote NMSM, diluting PMTNM value to independent member teachers whose market is directly harmed by NMSM's growth.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Nov 2, 2025 Larry Blind email raising $4,600 storage question; Nov 4 meeting transcript (Grealish personal furniture admission before Kathy Black); DocsFromJeanne budget documents showing $3,000 budget vs. $4,600 actual</t>
+          <t>NMSM director biography (nmschoolofmusic.com/director---lawrence-blind — live web evidence); 2023 PMTNM conference program featuring NMSM students; VP Report documenting biography misrepresentation; PMTNM member impact analysis</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>53% budget overrun on personal-use storage. Even the past president questioned it in writing. Attorney-witnessed admission of personal property in PMTNM storage creates clear private-benefit violation.</t>
+          <t>Using nonprofit organizational credibility and platform to market a competing commercial music school. Misleading language in NMSM materials violates MTNA's core principle of honest representation. NMSM's 700-student enrollment at $70/hr directly harms independent PMTNM members' livelihoods.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Attorney-witnessed + Larry Blind email confirmation</t>
+          <t>Web evidence + conference records + VP Report</t>
         </is>
       </c>
     </row>
     <row r="33" ht="72" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Financial Self-Dealing</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Ethics + Financial</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>IRS private benefit prohibition; Fiduciary duty; PMTNM budget oversight</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Storage unit operating expense documented as $4,600 actual vs. $3,000 budgeted — a 53% overrun. Even Larry Blind, who has a financial relationship with Grealish, raised the discrepancy in a Nov 2 email asking about the expense. Grealish had already admitted (before attorney Kathy Black) that she stores personal furniture in the PMTNM storage unit.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Nov 2, 2025 Larry Blind email raising $4,600 storage question; Nov 4 meeting transcript (Grealish personal furniture admission before Kathy Black); DocsFromJeanne budget documents showing $3,000 budget vs. $4,600 actual</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>53% budget overrun on personal-use storage. Even the past president questioned it in writing. Attorney-witnessed admission of personal property in PMTNM storage creates clear private-benefit violation.</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Attorney-witnessed + Larry Blind email confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>E-04</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Oct 2023</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>TOTY Procedural Violation</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Ethics + Governance</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Larry Blind; Tatiana Vetrinskaya (NMSM)</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>MTNA Code of Ethics — conflicts must be disclosed; PMTNM TOTY award criteria (Criterion B3: 'outstanding professional relationship with students, fellow music teachers, and community leaders'; B4: 'consistent record of high standards of teaching and promoting music teaching in New Mexico')</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>The TOTY award criteria require demonstrated community service within New Mexico's music teaching community. Criterion-by-criterion analysis of the actual PDFs:
 TERRI RECK (loser): B1 ✓ — 47 years teaching, Dalcroze certification. B2 ✓ — 5 AMTA committee leadership roles, SF Symphony, NM Symphony, NM Philharmonic harpsichordist. B3 ✓ — Students in PMTNM/MTNA programs, Music Bowl Chair decades, jewelry donations to PMTNM silent auctions. B4 ✓ — Entire career in NM; engaged with PMTNM community across multiple decades.
 TATIANA VETRINSKAYA (winner, written by her employer Larry Blind): B1 ✓ — teaching background listed. B2 — ambiguous; achievements framed around NMSM institutional activity. B3 ✗ — community service section entirely NMSM activities, not PMTNM/NM music teaching community. B4 ✗ (future tense disqualifier) — submission lists 'will present a workshop at 2023 PMTNM Conference' — an event that had NOT YET OCCURRED when submission was filed on 9-30-23. Closing attribute 'business acumen' is not a TOTY criterion. No conflict of interest disclosed.</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>PHYSICAL PDFs read and analyzed: 'Terri Reck.pdf' (submitted zanderwall@gmail.com, signed 9/30/23) and 'Tatiana Vetrinskaya.pdf' (submitted lawrenceblind@msn.com, signed 9-30-23); Larry's Oct 4, 2023 voting email with award criteria (Gmail thread ID: 19239a27e03b7010): B3 and B4 require PMTNM community service; Chip to Jackie Sep 29 (verbatim comparison): 'The other submission... highlights work done in NMSM' vs. 'Your submission... highlights work done in the PMTNM community this past year'; Haewon admission that she voted based on bio appearance; Tatiana's future-tense 'will present a workshop' listed as an achievement</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Award designed to honor PMTNM community service given to NMSM institutional promotion. The winning bio fails B3 entirely and lists a future event as an achievement. The losing bio meets all four criteria with verifiable, decades-long records. No conflict disclosure made by the employer who wrote the winning nomination and administered the vote.</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>PHYSICAL PDFs analyzed + verbatim comparative analysis in email record</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="72" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>S-04</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2025 – Feb 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Governance Obstruction</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Ethics + Legal</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>VP's statutory right to financial information (NMSA §53-8-26); PMTNM Handbook on VP Budget Committee membership; Presidential duty of good faith</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>For 11+ months, Sharon used her position as President to block Chip's financial access: (1) Mar 2025 — reinforced Grealish's records refusal, falsely characterizing VP's duties; (2) Oct 2025 — dismissed budget committee requests by deferring to Grealish; (3) Oct 2025 — told Chip that scholarship coordination was 'not your territory'; (4) Nov 4 — committed to place agenda items before board, then broke that commitment at Nov 7.</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Mar 17, 2025 email (Sharon reinforces Grealish refusal); Oct 2 email (budget committee deferral); Oct 14 agenda request reply (dismissive); Nov 4 audio recording (commitment at 1:14:51); Kathy Black email Nov 4 at 2:54 PM (confirms commitment); Nov 7 meeting (commitment broken)</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Sustained 11-month pattern of presidential obstruction of VP's statutory inspection rights. Pattern of coordination with Grealish to maintain financial information asymmetry.</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>11-month documented pattern — four distinct incidents</t>
         </is>
       </c>
     </row>
     <row r="35" ht="72" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Sep – Oct 2025</t>
+          <t>Mar 2025 – Feb 2026</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Failure to Act on Known Misconduct</t>
+          <t>Governance Obstruction</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Ethics + Legal</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2652,111 +2652,111 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>MTNA Code of Ethics — board members must not tolerate known misconduct; Presidential responsibility for board conduct standards; Duty of candor</t>
+          <t>VP's statutory right to financial information (NMSA §53-8-26); PMTNM Handbook on VP Budget Committee membership; Presidential duty of good faith</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Sep 11, 2025: Jeanne Grealish responded to Chip's MTNA Foundation newsletter: 'Boring and irrelevant to most of us.' Sep 12, 12:44 AM: Chip forwarded Jeanne's response to Jeanne, Brian Shepard, AND Sharon Kunitz (slkunitz@aol.com) asking 'Hi Jeanne, can you clarify?' Sharon received this email — and said nothing. No defense of Chip's work, no pushback on Jeanne's dismissive characterization. Oct 2, 2025 — 21 days later — Sharon sent Chip a separate email: 'Great article on Foundation! Beautifully written and presented.' (CCed to Jeanne, Larry, Laura Spitzer). Sharon knew the article had merit. She praised it privately. She chose not to say so when Jeanne publicly dismissed it to Chip's face.</t>
+          <t>For 11+ months, Sharon used her position as President to block Chip's financial access: (1) Mar 2025 — reinforced Grealish's records refusal, falsely characterizing VP's duties; (2) Oct 2025 — dismissed budget committee requests by deferring to Grealish; (3) Oct 2025 — told Chip that scholarship coordination was 'not your territory'; (4) Nov 4 — committed to place agenda items before board, then broke that commitment at Nov 7.</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Sep 12, 2025 12:44 AM email: Chip → Jeanne + bshepard@mtna.org + slkunitz@aol.com: 'Hi Jeanne, can you clarify?' (Gmail thread ID: 1993b54101446b14); Oct 2, 2025 Sharon → Chip (CC Jeanne, Larry, Laura): 'Great article on Foundation! Beautifully written and presented.' (Gmail thread ID: 199a581f54374d6f); No Sharon response in the Sep 12 thread</t>
+          <t>Mar 17, 2025 email (Sharon reinforces Grealish refusal); Oct 2 email (budget committee deferral); Oct 14 agenda request reply (dismissive); Nov 4 audio recording (commitment at 1:14:51); Kathy Black email Nov 4 at 2:54 PM (confirms commitment); Nov 7 meeting (commitment broken)</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Sharon's silence in the moment — combined with her private praise 21 days later — proves she recognized Jeanne's conduct was wrong and chose not to intervene. As President, she had the authority and responsibility to address Grealish's conduct toward a fellow officer.</t>
+          <t>Sustained 11-month pattern of presidential obstruction of VP's statutory inspection rights. Pattern of coordination with Grealish to maintain financial information asymmetry.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Two emails, 21 days apart — documentary contrast</t>
+          <t>11-month documented pattern — four distinct incidents</t>
         </is>
       </c>
     </row>
     <row r="36" ht="72" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Oct 7, 2025</t>
+          <t>Sep – Oct 2025</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Legal Compliance Repudiation</t>
+          <t>Failure to Act on Known Misconduct</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Legal + Ethics</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
+          <t>Ethics</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Jeanne Grealish</t>
+          <t>Sharon Kunitz</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>IRS 501(c)(3) obligations; NM Nonprofit Corporation Act; Fiduciary duty to act within statutory constraints; PMTNM Handbook (Bylaws) provisions for budget committee and fiscal governance</t>
+          <t>MTNA Code of Ethics — board members must not tolerate known misconduct; Presidential responsibility for board conduct standards; Duty of candor</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>On Oct 7, 2025, Jeanne Grealish sent an email to Chip, Sharon, Laura, Larry, and Heather Nasi. The FULL CONTEXT: Chip had asked about the budget committee meeting required by the PMTNM Handbook. Grealish responded by dismissing the handbook's budget committee provisions as 'grossly out of date,' then wrote: 'Thanks heaven, PMTNM does not function under any legal mandates!' This statement was NOT an offhand philosophical remark — it was a deliberate, specific rejection of the handbook governance requirements Chip was invoking to justify a budget committee meeting. Grealish also stated during this period: conference venue research was 'a waste of everyone's time and a senseless cluttering up of mail boxes'; the website was 'a big waste of time'; 'Please, no more useless emails' (re: venue research). The statement is additionally documented in the VP Report submitted to the President and EST (Section 3.3).</t>
+          <t>Sep 11, 2025: Jeanne Grealish responded to Chip's MTNA Foundation newsletter: 'Boring and irrelevant to most of us.' Sep 12, 12:44 AM: Chip forwarded Jeanne's response to Jeanne, Brian Shepard, AND Sharon Kunitz (slkunitz@aol.com) asking 'Hi Jeanne, can you clarify?' Sharon received this email — and said nothing. No defense of Chip's work, no pushback on Jeanne's dismissive characterization. Oct 2, 2025 — 21 days later — Sharon sent Chip a separate email: 'Great article on Foundation! Beautifully written and presented.' (CCed to Jeanne, Larry, Laura Spitzer). Sharon knew the article had merit. She praised it privately. She chose not to say so when Jeanne publicly dismissed it to Chip's face.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Oct 7, 2025 email from Grealish → Chip + Sharon + Laura + Larry + Heather Nasi (Gmail thread ID: 199c0d60237afa6c): VERBATIM: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!'; VP_Report_Submitted_to_President_and_EST.pdf Section 3.3 (Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z) independently documenting the same statement</t>
+          <t>Sep 12, 2025 12:44 AM email: Chip → Jeanne + bshepard@mtna.org + slkunitz@aol.com: 'Hi Jeanne, can you clarify?' (Gmail thread ID: 1993b54101446b14); Oct 2, 2025 Sharon → Chip (CC Jeanne, Larry, Laura): 'Great article on Foundation! Beautifully written and presented.' (Gmail thread ID: 199a581f54374d6f); No Sharon response in the Sep 12 thread</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>EST explicitly disclaiming legal obligations on the record — and doing so SPECIFICALLY to shut down VP's invocation of handbook governance requirements for the budget committee. The person controlling all of PMTNM's finances and records publicly stated the organization operates without legal mandates in response to a compliance question. This is the most unambiguous single statement supporting the petition and a future AG complaint.</t>
+          <t>Sharon's silence in the moment — combined with her private praise 21 days later — proves she recognized Jeanne's conduct was wrong and chose not to intervene. As President, she had the authority and responsibility to address Grealish's conduct toward a fellow officer.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>VERBATIM email + VP Report — dual source verification of same statement</t>
+          <t>Two emails, 21 days apart — documentary contrast</t>
         </is>
       </c>
     </row>
     <row r="37" ht="72" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Oct 7, 2025</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>TOTY Process Interference — Terri Reck Pattern</t>
+          <t>Legal Compliance Repudiation</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Ethics + Governance</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Legal + Ethics</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2766,360 +2766,417 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Nonprofit election integrity; MTNA Code of Ethics — fair processes; PMTNM TOTY procedural standards</t>
+          <t>IRS 501(c)(3) obligations; NM Nonprofit Corporation Act; Fiduciary duty to act within statutory constraints; PMTNM Handbook (Bylaws) provisions for budget committee and fiscal governance</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>CRITICAL PATTERN: Terri Reck was ALSO the 2023 TOTY nominee who lost to Tatiana Vetrinskaya when Larry administered the biased process (L-05, E-04). In 2025, Grealish made three separate attempts to nullify Reck's nomination again, stating: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service.' This claim was immediately contradicted by other board members who seconded Reck's nomination. Grealish's 'last time' reference is itself an admission — she knows Terri was nominated before and is aware of the prior cycle. Terri Reck — an independent community teacher with 47 years of teaching, 5 AMTA committee roles, and decades as Music Bowl Chair (per her own 2023 TOTY submission) — has been the target of TOTY suppression in back-to-back cycles: 2023 (Larry's biased process blocked her) and 2025 (Grealish's three direct nullification attempts).</t>
+          <t>On Oct 7, 2025, Jeanne Grealish sent an email to Chip, Sharon, Laura, Larry, and Heather Nasi. The FULL CONTEXT: Chip had asked about the budget committee meeting required by the PMTNM Handbook. Grealish responded by dismissing the handbook's budget committee provisions as 'grossly out of date,' then wrote: 'Thanks heaven, PMTNM does not function under any legal mandates!' This statement was NOT an offhand philosophical remark — it was a deliberate, specific rejection of the handbook governance requirements Chip was invoking to justify a budget committee meeting. Grealish also stated during this period: conference venue research was 'a waste of everyone's time and a senseless cluttering up of mail boxes'; the website was 'a big waste of time'; 'Please, no more useless emails' (re: venue research). The statement is additionally documented in the VP Report submitted to the President and EST (Section 3.3).</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>VP_Report_Submitted_to_President_and_EST.pdf — 2025 TOTY section (Google Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z): Grealish: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service'; Board members seconding Reck contradicting Grealish; 2023 TOTY PDF 'Terri Reck.pdf' (submitted zanderwall@gmail.com, Gmail thread ID: 19239a27e03b7010) documents Reck's actual community record: 47 years teaching, Dalcroze certification, SF/NM Symphony harpsichordist, Music Bowl Chair, PMTNM silent auction donations</t>
+          <t>Oct 7, 2025 email from Grealish → Chip + Sharon + Laura + Larry + Heather Nasi (Gmail thread ID: 199c0d60237afa6c): VERBATIM: 'As for any statements in the Handbook regarding the budget, committee, dates, etc. these would be grossly out of date since the Handbook itself is no longer current and requires serious revision. Thanks heaven, PMTNM does not function under any legal mandates!'; VP_Report_Submitted_to_President_and_EST.pdf Section 3.3 (Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z) independently documenting the same statement</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>The same independent community teacher — with a documented record that exceeds TOTY criteria — has been suppressed in consecutive cycles by different insiders: Larry in 2023, Grealish in 2025. Grealish's claim that Reck 'has not contributed very much' is directly contradicted by Reck's own 2023 submission PDF. This is the clearest evidence that the TOTY process is being used to protect institutional interests rather than honor community service.</t>
+          <t>EST explicitly disclaiming legal obligations on the record — and doing so SPECIFICALLY to shut down VP's invocation of handbook governance requirements for the budget committee. The person controlling all of PMTNM's finances and records publicly stated the organization operates without legal mandates in response to a compliance question. This is the most unambiguous single statement supporting the petition and a future AG complaint.</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>VP Report + 2023 TOTY PDF (physical document analyzed) + two-cycle targeting pattern</t>
+          <t>VERBATIM email + VP Report — dual source verification of same statement</t>
         </is>
       </c>
     </row>
     <row r="38" ht="72" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>F-11</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>TOTY Process Interference — Terri Reck Pattern</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Ethics + Governance</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Nonprofit election integrity; MTNA Code of Ethics — fair processes; PMTNM TOTY procedural standards</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL PATTERN: Terri Reck was ALSO the 2023 TOTY nominee who lost to Tatiana Vetrinskaya when Larry administered the biased process (L-05, E-04). In 2025, Grealish made three separate attempts to nullify Reck's nomination again, stating: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service.' This claim was immediately contradicted by other board members who seconded Reck's nomination. Grealish's 'last time' reference is itself an admission — she knows Terri was nominated before and is aware of the prior cycle. Terri Reck — an independent community teacher with 47 years of teaching, 5 AMTA committee roles, and decades as Music Bowl Chair (per her own 2023 TOTY submission) — has been the target of TOTY suppression in back-to-back cycles: 2023 (Larry's biased process blocked her) and 2025 (Grealish's three direct nullification attempts).</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>VP_Report_Submitted_to_President_and_EST.pdf — 2025 TOTY section (Google Drive ID: 1d-vg5v87N7DwF7EUisJ6M-HYiYrbuC3Z): Grealish: 'I believe the reason Terri Reck was not nominated last time was she has not contributed very much to community service'; Board members seconding Reck contradicting Grealish; 2023 TOTY PDF 'Terri Reck.pdf' (submitted zanderwall@gmail.com, Gmail thread ID: 19239a27e03b7010) documents Reck's actual community record: 47 years teaching, Dalcroze certification, SF/NM Symphony harpsichordist, Music Bowl Chair, PMTNM silent auction donations</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>The same independent community teacher — with a documented record that exceeds TOTY criteria — has been suppressed in consecutive cycles by different insiders: Larry in 2023, Grealish in 2025. Grealish's claim that Reck 'has not contributed very much' is directly contradicted by Reck's own 2023 submission PDF. This is the clearest evidence that the TOTY process is being used to protect institutional interests rather than honor community service.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>VP Report + 2023 TOTY PDF (physical document analyzed) + two-cycle targeting pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>F-14</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Jul 1 – Nov 7, 2025</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Unauthorized Spending</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Standard nonprofit governance — expenditures require an approved budget; PMTNM Handbook: budget must be approved by Executive Board at a board meeting; NM Nonprofit Corporation Act — fiduciary duty</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>PMTNM's fiscal year 2025-2026 began July 1, 2025. Grealish's own Oct 7 email confirms the CPA report was not expected until 'around November 1st' because the CPA 'was out of the country all summer.' The proposed budget was not sent to the budget committee until Oct 29, 2025 — four months into the fiscal year. A formal budget committee meeting never took place (replaced by emails, per Grealish's direction). The budget was presented at the Nov 7 board meeting, but no formal vote was documented in the audio recording (consistent with M-02).
 During the Jul 1 – Nov 7 period, Grealish continued spending organizational funds — including $4,600 in storage costs (F-10), her $1,750 annual honorarium (F-07), and operational expenses — without any board-approved budget authorizing those expenditures. Grealish justified this by saying 'Conference expenses and all expenses in the 2025-2026 fiscal year are covered in the current budget' (Oct 7 email) — but no 2025-2026 budget existed yet. The only operative document was the prior year's budget, which was itself adopted under disputed circumstances.</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Oct 7, 2025 Grealish email (thread ID: 199c0d60237afa6c): 'The budget for 2026-2027 will be prepared once the accountant completes the year end report...That report will be available around November 1st'; 'No harm done since any new budget will not become affective [sic] July 1, 2026'; Oct 29, 2025: CPA report and draft budget distributed — 4 months after fiscal year start; Nov 7, 2025: budget 'voted on' but no formal vote in audio recording (see M-02); DocsFromJeanne financial records showing ongoing expenditures during Jul–Nov 2025</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Four months of organizational spending with no board-approved budget. Grealish dismissed the problem by claiming 'no harm done' — while simultaneously blocking all committee oversight. Combined with F-05 (sole financial control) and F-06 (personal benefit from storage), the 4-month gap represents completely unaccountable spending by a single officer.</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Email-documented timeline — fiscal year gap confirmed</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="72" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>A-01</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Ongoing (confirmed Oct 30, 2025)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Auditing Committee Abandoned</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>PMTNM Handbook 2004 Section VII-D (Auditing Committee): 'Makes a complete audit of the books prior to (if possible) or during the State Conference. All figures in the ledgers, journals, check book, receipts, and vouchers should be checked. Makes a report at the State Conference Business Meeting.'</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>In her private letter to attorney Kathy Black (Oct 30, 2025), Grealish stated: 'PMTNM does not have a separate Finance Committee. It has not had an Auditing Comm. since hiring a CPA to double check all activity and file all required reports with IRS and the State of NM.' This is a written admission that a standing committee required by the PMTNM Handbook has been unilaterally eliminated.
 The distinction is legally critical: a CPA preparing tax returns and an annual fiscal report is NOT an audit. The handbook Auditing Committee is an internal oversight function — committee members verify the ledgers, journals, checkbook, receipts, and vouchers against each other and report at the State Conference. That independent check of the books has not existed for years. Kathy Black confirmed: 'The function of an audit committee should be to retain a CPA for a formal audit, which this organization does not do.'
 The elimination of the Auditing Committee means Grealish's financial records — held exclusively at her home with no online access, no other signatories, and no independent verification — have gone unchecked by any committee member. The CPA she hired (Mary Scofield) prepares reports based solely on materials Grealish provides her.</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Grealish private letter to Kathy Black, Oct 30, 2025 (forwarded to Chip by Kathy Black, Gmail thread ID: 19a3309ed58127ac): 'It has not had an Auditing Comm. since hiring a CPA to double check all activity and file all required reports with IRS and the State of NM'; Kathy Black Oct 30, 2025: 'The function of an audit committee should be to retain a CPA for a formal audit, which this organization does not do'; 2004 Handbook Section VII-D: verbatim Auditing Committee duties requiring complete audit at State Conference; CPA Mary Scofield — prepares tax returns only, not independent audit</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Standing committee required by the handbook has been eliminated without board vote. The internal financial oversight function that would have caught irregularities in storage expenses (F-10), personal property co-mingling (F-06), and sole-signatory arrangements (F-05) has not operated for years. Grealish's justification — hiring a CPA — is legally incorrect as preparation of tax returns is not an independent audit of the books.</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Grealish's own written admission — attorney-forwarded</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="72" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>M-06</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Oct 30, 2025 (confirmed in writing)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Records in Storage — Minutes Inaccessible</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>NM Nonprofit Corporation Act NMSA §53-8-26 — records must be available for inspection; PMTNM Handbook (2004): 'The records should be open to any member at all times' (EST duties section, re: Auditing Committee); Standard nonprofit governance — minutes are the authoritative record of corporate actions</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>In her private letter to Kathy Black (Oct 30, 2025), Grealish confirmed: 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings.' The board minutes — the organization's official legal record of all votes, decisions, and actions — are stored in the same storage unit where Grealish also stores personal furniture (F-06). Current financial records (CPA reports, checkbook, bank statements, deposit records, membership records) are kept at her personal home office.
 This means: (1) Past meeting minutes cannot be accessed without retrieving them from the storage unit. (2) Current financial records cannot be accessed without visiting Grealish's home. (3) 'PMTNM does not do online banking' — no electronic access exists. (4) When Kathy Black formally demanded records by Oct 31, 2025, Grealish said it was 'not physically possible' to comply. This is a textbook records-access failure under NMSA §53-8-26.</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>Grealish private letter to Kathy Black, Oct 30, 2025 (Gmail thread ID: 19a3309ed58127ac): 'Past records and tax documents (both federal and state) are kept securely in storage along with Minutes from Board and General Meetings'; 'Current files (CPA reports, checkbook, bank statements for all seven accounts, deposit records, and membership records) are kept in my home office at 1226 Morningside Dr. NE'; 'PMTNM does not do online banking'; 'It is not physically possible for me to bring the requested items to your office on Friday, October 31, 2025'; Kathy Black letter to Grealish (Oct 29, 2025) citing NMSA §53-8-27: formal demand for inspection of records</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>Board meeting minutes — the organization's legal record of its decisions — are locked in a storage unit controlled solely by Grealish. When an attorney formally demanded records under NM statute, Grealish said it was physically impossible to produce them in a business day. Combined with F-05 (sole control), this means no board member, member, or attorney can independently verify any of PMTNM's financial history without Grealish's physical cooperation.</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Written admission in attorney-forwarded letter — direct statutory violation</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="72" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>F-15</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Spring 2025 (failure to act)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Budget Timing Violation</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish; Sharon Kunitz</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>PMTNM Handbook 2004 Section VII-E (Budget Committee): 'Meets before the Spring Board Meeting each year to prepare a budget for the coming year and presents it to the Executive Board for approval.'</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>The PMTNM Handbook requires the Budget Committee to meet BEFORE THE SPRING BOARD MEETING to prepare the budget for the coming fiscal year. PMTNM's fiscal year runs July 1 – June 30. For FY 2025-2026, the budget should have been prepared in spring 2025 (before a spring board meeting), approved by the Executive Board at that meeting, then recommended to the membership at the State Conference.
 Instead: No spring board meeting was held in 2025. No budget committee convened in spring 2025. The CPA was 'out of the country all summer.' The budget was not even drafted until October 29, 2025 — four months into the fiscal year — and was based on figures that only arrived October 26. The organization operated without any approved budget from July 1 through at least November 7, 2025.
 This is not a one-time delay. The pattern of fall-only board meetings and no spring budget process appears to be the standard practice under Grealish's administration.</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Oct 7, 2025 Grealish email (thread ID: 199c0d60237afa6c): 'The budget for 2026-2027 will be prepared once the accountant completes the year end report... That report will be available around November 1st'; 2004 Handbook Section VII-E: 'Meets before the Spring Board Meeting each year'; No spring 2025 board meeting documented; Budget draft sent Oct 29, 2025 — 4 months into FY 2025-2026; Grealish Oct 7: 'No harm done since any new budget will not become affective [sic] July 1, 2026' [note: this confusingly refers to next year's budget, showing Grealish herself was confused about the timeline]</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>The handbook-required spring budget process has been systematically bypassed. No spring board meeting, no spring budget committee, no pre-fiscal-year budget approval. Four months of unauthorized spending under no approved budget. The person responsible for calling the committee is also the person whose spending would have been scrutinized by that committee.</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Documentary — handbook vs. actual calendar</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="72" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>M-07</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>November 7, 2025</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Minutes Falsification</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Legal + Ethics</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish (author/distributor); Sharon Kunitz (presiding officer)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>Fiduciary duty to maintain accurate organizational records; Nonprofit corporate record standards; State law on corporate minute accuracy; Robert's Rules of Order — accurate record of motions and votes</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>The November 7, 2025 board meeting minutes (distributed Mar 9, 2026, four months late) state: 'Secretary Treasurer's Report: The current report with financial summary was approved as presented.'
 The audio recording at timestamp 25:52 shows that Grealish mentioned the budget was 'prepared for 26/27' as a passing remark tacked onto the end of the designated accounts motion — no document was presented, no figures discussed, no motion made, no second, no vote. The only thing formally voted on in the Secretary-Treasurer's report section was the Mary Scofield CPA designated accounts motion, which the minutes do record separately.
 The 'approved as presented' language for the financial summary and budget is FABRICATED and appears nowhere in the audio recording. This fictitious approval retroactively authorizes Grealish's $1,750 annual honorarium for another fiscal year without a real vote. Chip had raised written questions about the honorarium on October 31, 2025 ('Has your honorarium increased through the years as our membership has decreased? What are the measures for your honorarium?') — questions that were never answered. The false minutes entry serves to lock in that compensation without board action.</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>Audio Recording Nov 7, 2025, timestamp 25:52 — Grealish's remark without any motion, second, or vote; Nov 7 Minutes (distributed Mar 9, 2026) — falsified 'approved as presented' language; Oct 31, 2025 email — Chip's written questions about honorarium (thread ID: 19a3309ed58127ac); Audio recording ~46 minutes total — full context of Secretary-Treasurer's report section (no other votes on budget/financial summary)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>Minutes state a budget and financial summary were 'approved as presented,' but the audio recording proves no such motion or vote occurred. Minutes are a binding legal record of board action. A false entry that retroactively authorizes officer compensation constitutes falsification of corporate records — particularly when the fabrication appears 4 months after the meeting, after litigation has commenced.</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Audio-verified falsification — fabricated approval language contradicted by full recording</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44" ht="72" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>F-16</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Due Nov 15, 2019 — still overdue as of Oct 2025</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Regulatory Failure + False Statement</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Legal + Ethics</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>NM Nonprofit Corporation Act — annual report filing requirement with NM Secretary of State; Fiduciary duty of accurate regulatory compliance; Prohibition on false statements in official organizational records</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>On October 23, 2025, attorney Kathy Black reviewed PMTNM's NM Secretary of State business records and found: 'PMTNM's annual report is way overdue, with the due date listed as November 15, 2019.' The NM Secretary of State annual report has not been filed in over SIX YEARS.
 This directly contradicts a statement in PMTNM's own internal financial documents (Budget Documents, drafts approved by Board): 'All federal, state and local required documents and lists have been prepared and filed.' If this statement appeared in a report adopted by the board, it constitutes a false certification in an official organizational record — either Grealish failed to file and knew it, or she represented compliance to the board falsely.
@@ -3127,59 +3184,59 @@
 Also relevant: the NM AG Charitable Organization Registration (F-12) listed the organization as filing a 990-N and reporting 'solicited funds in NM: No.' The Secretary of State lapse compounds the regulatory picture: PMTNM has not maintained compliance with the most basic state corporate filing requirement since 2019, while Grealish continues to execute contracts (F-13: VIP Staffing, Oct 2025) and spend organizational funds as if the organization is in good standing.</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Kathy Black email to Chip Oct 23, 2025: 'according to New Mexico Secretary of State business records, PMTNM's annual report is way overdue, with the due date listed as November 15, 2019'; Kathy Black email Oct 30, 2025: 'At the very least, I am going to point out that the State of New Mexico annual report has not been filed'; PMTNM internal document ('Budget Documents, drafts approved by Board (1).pdf' in Drive — PMTNM folder): 'All federal, state and local required documents and lists have been prepared and filed' — DIRECT CONTRADICTION of Secretary of State records; NM Secretary of State public business records (verifiable)</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>PMTNM has been operating for 6+ years without filing its required NM Secretary of State annual report. Its own internal financial documents affirmatively claim all required filings are current — a false statement in an official record. This is simultaneously a regulatory failure, a false representation to the board, and evidence that Grealish's self-reported compliance ('The Executive Secretary-Treasurer shall be responsible for... filing of all returns with IRS, NM Taxation and Revenue Department, the NM State Corporation Commission, and any other government entity') has not been fulfilled.</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Attorney-identified + contradicted by PMTNM's own internal document</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="72" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45" ht="72" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>F-12</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Tax Year 2018 (filed ~2019); Tax Year 2023 (filed Dec 18, 2024); Tax Year 2024 (filed Dec 12, 2025)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Regulatory / Sole Control</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>NM Attorney General Charitable Organization Registration requirements; IRS NTEE classification accuracy; NM Solicitation Disclosure Act; NM Nonprofit Corporation Act — officer record accuracy</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>THREE YEARS OF NM AG FILINGS REVIEWED — IDENTICAL SOLE-CONTROL PATTERN ACROSS DECADE:
 TAX YEAR 2018 (filed ~2019):
@@ -3190,116 +3247,116 @@
 (1) All five financial functions REMAIN solely Grealish. (2) Net assets declined from $62,500 to $60,555 (continuing decade-long decline from $81,975 in 2014 — total erosion of $21,420 or 26%). (3) Total gross revenue $7,114 (down 70% from $23,963 in 2014). (4) Total contributions $0.00 despite 'Special Events' and 'Personal Contact' listed as solicitation methods. (5) 'Solicited funds in NM: No' answered false for the eleventh consecutive year — systematic false statement across the entire regulatory history. (6) Chip Miller (Vice President) listed on filing. (7) This filing was submitted after the lawsuit was filed, suggesting a document created under legal awareness.</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>NM AG Registration Tax Year 2018 (physical PDF: 20184721935751263.pdf); NM AG Registration Tax Year 2023 (physical PDF: 20234722435369467 (2).pdf); NM AG Registration Tax Year 2024 (filed Dec 12, 2025), FEIN 85-0284938; VP appointment email from Sharon Kunitz, Aug 14, 2024 — establishes Chip's VP status; IRS BMF confirming 990-N filer; Internal financial records (DocsFromJeanne) and Kathy Black Initial Impressions confirming same sole-control pattern 2024-2025</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>Three independent NM AG filings across a decade show IDENTICAL sole-control structure. The 'solicited funds in NM: No' false statement appears in all three filings despite documented solicitation activity — a systematic misrepresentation maintained throughout the regulatory history. The Tax Year 2024 filing (submitted after the lawsuit was filed) documents that Chip Miller was the VP during that year, yet all financial control remained with Grealish. Net assets and revenue continue their decade-long decline while officer compensation (Grealish honorarium) increased from 6.3% to 24.6% of revenue — compensation rising as the organization shrinks.</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>THREE physical documents reviewed — entire decade pattern confirmed at NM AG level</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="72" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>F-13</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Oct 23, 2025</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Unauthorized Contract</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Legal + Governance</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Jeanne Grealish</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>Nonprofit governance — contracts above a de minimis threshold require board authorization; PMTNM Handbook on financial authority; Fiduciary duty</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>On October 23, 2025, PMTNM entered into a Master Terms &amp; Conditions agreement with VIP Staffing — a commercial staffing agency. Three versions of this contract are preserved in Google Drive (draft, executed, and a third copy), all dated Oct 23, 2025. PMTNM is identified as the 'Customer.' For a nonprofit that (a) filed 990-N (revenue under $50K threshold), (b) had FY2018 revenue of only $18,817, (c) claims in the NM AG filing it does not solicit funds, and (d) operates from Grealish's personal home — entering a commercial staffing contract is a significant financial and legal commitment. No board vote authorizing this contract appears in any board minutes. The Nov 7, 2025 board meeting (the only documented board meeting during this period) contains no reference to a staffing contract. Grealish, as sole financial officer, appears to have executed this agreement unilaterally.</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Google Drive: '2025-10-23T16-25-09.000Z - 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1OGc7fLQguB3-ZDiqXpuUxF83sK2Rcy-L); '2025-10-23T16-49-03.000Z - Executed 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1nQAsasqmpAAk9d3-ZZJum3j4a70G92kZ); Nov 7, 2025 Board Meeting minutes and audio — no reference to any staffing contract; No board resolution authorizing staffing agreement found</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>A commercial staffing contract executed without board authorization — by the sole financial officer of a nonprofit operating at a deficit. The contract requires PMTNM to carry Comprehensive General Liability Insurance and Employment Practices Liability Insurance. Whether PMTNM actually maintains this insurance is unknown. The agreement also contains a one-year non-solicitation clause that would bind PMTNM as an organization. This is precisely the kind of significant financial obligation that requires board authorization under standard nonprofit governance.</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>Physical contracts reviewed in Drive — no board authorization documented</t>
         </is>
       </c>
     </row>
     <row r="46" ht="72" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Oct 23, 2025</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Contract</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Legal + Governance</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Nonprofit governance — contracts above a de minimis threshold require board authorization; PMTNM Handbook on financial authority; Fiduciary duty</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>On October 23, 2025, PMTNM entered into a Master Terms &amp; Conditions agreement with VIP Staffing — a commercial staffing agency. Three versions of this contract are preserved in Google Drive (draft, executed, and a third copy), all dated Oct 23, 2025. PMTNM is identified as the 'Customer.' For a nonprofit that (a) filed 990-N (revenue under $50K threshold), (b) had FY2018 revenue of only $18,817, (c) claims in the NM AG filing it does not solicit funds, and (d) operates from Grealish's personal home — entering a commercial staffing contract is a significant financial and legal commitment. No board vote authorizing this contract appears in any board minutes. The Nov 7, 2025 board meeting (the only documented board meeting during this period) contains no reference to a staffing contract. Grealish, as sole financial officer, appears to have executed this agreement unilaterally.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Google Drive: '2025-10-23T16-25-09.000Z - 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1OGc7fLQguB3-ZDiqXpuUxF83sK2Rcy-L); '2025-10-23T16-49-03.000Z - Executed 2025 VIP Staffing Master Terms Conditions- Professional Music Teachers of New Mexico.pdf' (Drive ID: 1nQAsasqmpAAk9d3-ZZJum3j4a70G92kZ); Nov 7, 2025 Board Meeting minutes and audio — no reference to any staffing contract; No board resolution authorizing staffing agreement found</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>A commercial staffing contract executed without board authorization — by the sole financial officer of a nonprofit operating at a deficit. The contract requires PMTNM to carry Comprehensive General Liability Insurance and Employment Practices Liability Insurance. Whether PMTNM actually maintains this insurance is unknown. The agreement also contains a one-year non-solicitation clause that would bind PMTNM as an organization. This is precisely the kind of significant financial obligation that requires board authorization under standard nonprofit governance.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Physical contracts reviewed in Drive — no board authorization documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="72" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>F-17</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Ongoing (documented 2014–2025); FY2024–25 Authorization Denied</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Financial / Officer Compensation</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Legal + Governance</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Jeanne Grealish (recipient); Sharon Kunitz (presiding officer, failed oversight); Larry Blind (Nominating Chair, failed oversight)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Nonprofit governance — officer compensation requires board approval; PMTNM Handbook duties for EST and President; Fiduciary duty to manage organizational resources; NM corporate law — board's duty to authorize material expenses</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>Grealish (Executive Secretary-Treasurer) has received annual compensation ('honorarium') of at least $1,500 (Tax Year 2014) rising to $1,750 (Tax Year 2024), disclosed in NM AG filings but never appearing in IRS records because PMTNM files 990-N. The sole financial controller of all five functions (check signing, fundraising, fund distribution, financial records, custody of funds) is the same person receiving this compensation. No independent oversight exists.
 In fiscal year 2024–25 (the year Chip served as VP), the budget containing this compensation was never formally voted on by the board:
@@ -3314,59 +3371,59 @@
 As membership and revenue collapsed 70% over a decade, Grealish's share of organizational revenue nearly quadrupled. The Tax Year 2024 NM AG filing (submitted December 12, 2025 — after the lawsuit was filed) shows $1,750 compensation resting on a board approval the audio recording and minutes contradiction prove never happened.</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>NM AG Registration filings Tax Year 2014–2024 (pattern documented); Oct 31–Nov 6, 2025 'Budget Committee REMINDER' email thread (Gmail ID: 19a3309ed58127ac); Nov 7, 2025 Audio Recording, timestamp 25:52 — no motion or vote on budget; Nov 7, 2025 Minutes (distributed Mar 9, 2026): falsified 'approved as presented' language (see M-07); NM AG Tax Year 2024 filing (submitted Dec 12, 2025) showing $1,750 compensation; Revenue data from IRS EO BMF and NM AG filings 2014–2024</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>A manager received continuous compensation without formal board authorization in the final fiscal year reviewed. The email-based budget process bypassed handbook requirements (F-02). The Nov 7 board meeting produced no motion to approve the budget — only a fabricated minutes entry (M-07). The compensation increased from 6.3% to 24.6% of declining revenue, while the sole financial officer remained unilaterally in control. This is foundational financial governance failure.</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Audio-verified (no motion), Minutes-contradicted (fabricated approval), NM AG-documented (11-year pattern)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="72" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="48" ht="72" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>G-02</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Nov 7, 2025 (pre-meeting emails + meeting)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Anonymous Voting Suppressed + No Confidence Motion Defeated</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Governance + Ethics</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Larry Blind (procedural suppression); Sharon Kunitz (adjournment); Jeanne Grealish (subject of motion, present during vote call)</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Robert's Rules of Order Newly Revised 12th ed. §§45:5–7, 46:32–34 (ballot voting must preserve anonymity); Robert's Rules §4 (main motions); Nonprofit governance — board members' duty to consider officer accountability motions</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>TWO-PART VIOLATION — PRE-MEETING SUPPRESSION AND IN-MEETING PROCEDURAL DEFEAT:
 PART 1: ANONYMOUS VOTING SYSTEM PREPARED AND IGNORED (Nov 7, morning, Gmail thread: 19a5ea6717e3582c)
@@ -3386,59 +3443,59 @@
 PATTERN ACROSS TWO CONSECUTIVE ELECTIONS: True anonymous voting was never available to online board members under Larry's administration. 2024: votes texted to Larry's personal cell at his own school. 2025: Chip's RROO-compliant ElectionChamp system (15 board members loaded, ready by 10:55 AM) was rejected by Larry that morning; vote run publicly instead with Grealish in the room. Two election cycles, zero genuine anonymous voting for online members. The 2025 suppression was not an oversight — it was a continuation of established practice.</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Gmail thread 19a5ea6717e3582c — full pre-meeting exchange: Sharon 7:07 AM (time limits); Chip 8:54 AM (anonymous voting proposal, RROO citation, two platforms offered); Larry 10:00 AM (dismissive, to Sharon only: 'getting someone to the point of a motion can be challenging'); Larry 10:11 AM (text-to-one-phone counter-proposal — not anonymous); Chip 10:27 AM (explains why Larry's method fails RROO ballot standards); Chip 10:55 AM ('ElectionChamp is set up'  — 15 board member emails loaded, test sent); Nov 7 Audio Recording 46:34–49:13: motion made, public hand-raise call, no second, motion dies; Sharon 49:13: adjourns; Gmail thread 1928ce26b2fe3d9c — 'PMTNM Board and General Membership Meetings' (approx. Oct 14, 2024): Larry announces online members should text votes to personal cell (505) 980-3941; meeting held at NM School of Music (Larry's school) — establishes 2-year pattern of non-anonymous online voting</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>A proper anonymous voting system was live and ready. Larry rejected it that morning in favor of a non-anonymous alternative, then ran the vote publicly with the subject of the motion in the room. Members who might have seconded the motion anonymously were instead exposed to full social and professional visibility. The motion's failure cannot be separated from the voting environment Larry created and the anonymous option he suppressed.</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Email-verified pre-meeting + Audio-verified in-meeting — anonymous voting deliberately bypassed — Trigger: Nov 5, 7:03 PM forward to MTNA/attorney preceded Nov 6 coordination</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="72" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49" ht="72" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>L-07</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Nov 7, 2025 (and ongoing 2024-2025)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Conflict of Interest / Structural Governance</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Ethics + Governance + Procedural</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Larry Blind (three simultaneous conflicting roles); Sharon Kunitz (failed to manage or disclose)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>PMTNM Handbook 2004 Section VII-Q (Nominating Committee chaired by Immediate Past President — controls VP succession); Section VI-C (President duty: 'keeps a close liaison with all officers' and should allocate duties to VP — not fulfilled while receiving exclusive advisory counsel from Past President); Robert's Rules of Order — Parliamentarian must be impartial and free of conflicts; Standard nonprofit governance — board members holding multiple conflicting roles must disclose them</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>At the November 7, 2025 board meeting and in the weeks leading up to it, Larry Blind simultaneously held THREE distinct roles — none of which were disclosed as conflicting and none of which had any handbook-defined boundaries or recusal process:
 (1) PAST PRESIDENT / INFORMAL ADVISOR TO SHARON: The 2004 PMTNM Handbook Section VI defines duties for State President, Vice President, EST, and District VPs. The Past President is NOT defined in Section VI. The advisory relationship is conventional — meaning no handbook language defines its scope, limits, or conflict-of-interest requirements. This gave Larry an unconstrained, informal advisory channel to Sharon with no procedural safeguards.
@@ -3449,116 +3506,116 @@
 NO CONFLICT DISCLOSURE, NO RECUSAL, NO PROCEDURE: There is no PMTNM conflict-of-interest policy in the handbook. No disclosure of Larry's three simultaneous roles was made at the Nov 7 meeting. No recusal procedure existed. Larry ruled on parliamentary questions at the same meeting where he had been advising the President against the VP and where he controlled the VP successor nomination process.</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>2004 PMTNM Handbook Section VII-Q (Nominating Committee: Past President chairs by convention — not formally defined in Section VI); 2004 Handbook Section VI-C (President duties: 'Keeps a close liaison with all officers' — not extended to VP during Larry's advisory relationship); Nov 7, 2025 10:00 AM email from Larry — reply to Sharon only, not Chip (Gmail thread 19a5ea6717e3582c): 'There may be a lot of talking, but getting someone to the point of a motion can be challenging' — advisory communication bypassing VP; Nov 7 Audio Recording: Larry as Parliamentarian ruling on procedural questions; Nov 7 Minutes: Larry named as Parliamentarian; Nov 5-6 hostile email from Larry to Chip (L-04): 'offensive, disrespectful, and does not deserve a response' — demonstrates pre-existing personal animus that preceded his impartial parliamentary role; No conflict-of-interest policy found in 2004 PMTNM Handbook</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>Three simultaneous conflicting roles — advisor, succession controller, parliamentary authority — held without disclosure or recusal. The informal advisory channel had no handbook boundaries. Larry's 10:00 AM email proves the advisory channel was used to coordinate meeting strategy against the VP hours before the meeting. Parliamentary rulings at Nov 7 were made by a person who had been advising the President in that direction since at least 10 AM. The Nominating Committee process is further compromised by Larry's documented financial conflicts (L-01 through L-06) and his use of organizational roles for personal and commercial benefit.</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Handbook-verified + Email evidence (10:00 AM advisory communication) + Audio record — three undisclosed simultaneous roles</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="72" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>G-03</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Oct 28, 2023 (approx.)</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Unilateral Conference Decision</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Governance + Conflict of Interest</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Lawrence Blind</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Standard nonprofit governance — significant organizational decisions require board approval and oversight; PMTNM Handbook (silent on conference programming authority, indicating governance gap); Fiduciary duty of loyalty — using organizational position and resources for personal/institutional benefit without disclosure</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The decision appears to have been communicated directly to PMTNM member teachers in late October 2023. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure. The fact of NMSM students' participation in the 2023 PMTNM conference is independently corroborated in L-02 (ethics complaint filed Nov 14, 2023 and conference program documentation).</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions; Independent corroboration: L-02 (Nov 14, 2023 ethics complaint to MTNA) and conference program/documentation from 2023 confirming NMSM student participation in PMTNM conference</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>Unilateral decision-making by a president without board oversight. Direct self-dealing: using PMTNM's conference platform to promote his own school and student base. Absence of conflict-of-interest management or disclosure. Pattern-consistent with leadership's broader governance approach (see G-01: 'PMTNM does not function under any legal mandates'). Even if conference programming fell within the president's delegated authority, the absence of any disclosure mechanism for conflicts of interest represents governance failure.</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>Documented via board minutes record (absence of decision) + independent corroboration via L-02 ethics complaint and conference documentation — Pattern consistent with unilateral leadership style</t>
         </is>
       </c>
     </row>
     <row r="50" ht="72" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Oct 28, 2023 (approx.)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Unilateral Conference Decision</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Governance + Conflict of Interest</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence Blind</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Standard nonprofit governance — significant organizational decisions require board approval and oversight; PMTNM Handbook (silent on conference programming authority, indicating governance gap); Fiduciary duty of loyalty — using organizational position and resources for personal/institutional benefit without disclosure</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The decision appears to have been communicated directly to PMTNM member teachers in late October 2023. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure. The fact of NMSM students' participation in the 2023 PMTNM conference is independently corroborated in L-02 (ethics complaint filed Nov 14, 2023 and conference program documentation).</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions; Independent corroboration: L-02 (Nov 14, 2023 ethics complaint to MTNA) and conference program/documentation from 2023 confirming NMSM student participation in PMTNM conference</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Unilateral decision-making by a president without board oversight. Direct self-dealing: using PMTNM's conference platform to promote his own school and student base. Absence of conflict-of-interest management or disclosure. Pattern-consistent with leadership's broader governance approach (see G-01: 'PMTNM does not function under any legal mandates'). Even if conference programming fell within the president's delegated authority, the absence of any disclosure mechanism for conflicts of interest represents governance failure.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Documented via board minutes record (absence of decision) + independent corroboration via L-02 ethics complaint and conference documentation — Pattern consistent with unilateral leadership style</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="72" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>L-08</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Nov 8, 2024; Nov 7, 2025</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Unmanaged Conflict of Interest / Proxy Voting</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Governance + Conflict of Interest</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>Marcus York; Lawrence Blind (as supervisor/authority)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>Nonprofit governance — voting members with conflicts of interest must be subject to formal conflict-of-interest procedures (disclosure, recusal, abstention); PMTNM governance standards requiring impartial board member conduct; Proxy voting prohibition under standard nonprofit law; Fiduciary duty of loyalty</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>Marcus York, an employee of NM School of Music (controlled by Lawrence Blind as owner/director), voted on critical financial matters at PMTNM board meetings while under employment relationship with Blind — with no formal conflict-of-interest procedure to manage or mitigate that relationship. Although PMTNM members likely knew York worked for Larry, the board took no formal action to address this conflict:
 NOVEMBER 8, 2024 BOARD MEETING (Blind was President):
@@ -3574,17 +3631,17 @@
 THE CONFLICT: York was voting (Nov 2024) on matters affecting the organization while being employed by someone with authority over him, while also serving on a committee chaired by that same person that controlled officer succession. NMSM's organizational authority structure gave Blind direct control over York's employment, creating the classic hallmark of proxy voting: a voting member whose interests are materially affected by someone else's authority.</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Board Minutes Nov 8, 2024: 'With a motion by Marcus York and a second by Sharon Kunitz the Treasurer's current financial report was unanimously approved'; 'Upon a motion by Janna Warren with a second by Marcus York [budget] was declared in order'; Meeting location: 'New Mexico School of Music, Albuquerque'; Board Minutes Nov 7, 2025: 'Nominating Committee Slate of Officers for 2026-2027: Chair Lawrence Blind thanked his committee members Astrid Groth and Marcus York'; Marcus York's NMSM email/employment confirmed in July 2024 communication identifying him as associated with 'the School of Music'</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>A voting board member whose employment is controlled by someone else (Blind) voted on financial matters while serving on a succession-control committee chaired by that same person. Although people knew York worked for Larry, the board took no formal action to manage this conflict — no required disclosure, no recusal procedure, no abstention protocol. PMTNM has no written conflict-of-interest policy. This pattern extends Blind's demonstrated use of organizational positions to embed people aligned with his interests — similar to how he controlled the 2023 TOTY vote through his employee Tatiana. York's situation represents proxy-voting conditions: voting on matters affecting the organization while under employment relationship with an interested party, with no organizational safeguards.</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Board minutes verified — unmanaged employment conflict documented across voting and committee roles</t>
         </is>
@@ -3604,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4123,19 +4180,19 @@
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish (EST)</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>TOTY manipulation: used business email to solicit votes for his own employee Tatiana</t>
+          <t>Official member list ('PMTNM. LIST AND EMAIL ADDRESSES') lists Sharon Kunitz as NCTM — contradicted by official MTNA data showing no NCTM designation; pattern of inaccurate record-keeping</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4204,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>L-01</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
+          <t>TOTY manipulation: used business email to solicit votes for his own employee Tatiana</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4221,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>L-02</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>PMTNM website used to promote NM School of Music during his presidency</t>
+          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4238,12 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
+          <t>PMTNM website used to promote NM School of Music during his presidency</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4255,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
+          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4272,12 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
+          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4289,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
+          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4306,12 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
+          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4323,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
+          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
         </is>
       </c>
     </row>
@@ -4283,46 +4340,46 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>L-07</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Triple role conflict Nov 7, 2025: Past President/informal advisor to Sharon + Nominating Committee Chair + Parliamentarian — three undisclosed simultaneous conflicting roles; advisory channel used morning of Nov 7 to coordinate meeting strategy against VP (10:00 AM email to Sharon only: 'getting someone to the point of a motion can be challenging')</t>
+          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
+          <t>Larry Blind (Past President / NMSM Owner)</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>L-07</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Triple role conflict Nov 7, 2025: Past President/informal advisor to Sharon + Nominating Committee Chair + Parliamentarian — three undisclosed simultaneous conflicting roles; advisory channel used morning of Nov 7 to coordinate meeting strategy against VP (10:00 AM email to Sharon only: 'getting someone to the point of a motion can be challenging')</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
           <t>Marcus York (Board Member / NMSM Employee)</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>L-08</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Voted on financial matters (Nov 2024) while employed by Larry Blind; served on Blind-chaired Nominating Committee (Nov 2024–2025) — no formal conflict-of-interest procedure invoked; unmanaged proxy voting situation due to Blind's employment authority over York</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (Former President)</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4391,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
+          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4408,12 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
+          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4425,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
+          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4442,12 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
         </is>
       </c>
     </row>
@@ -4402,29 +4459,29 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz (Former President)</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
           <t>M-05</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>VP excluded from board packet mailing; VP's agenda items not addressed</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4493,12 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4453,10 +4510,27 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Brian Shepard (MTNA CEO)</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
           <t>E-03</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Sep 2025 + Dec 2025 affiliate complaints — deferred entirely to affiliate self-governance</t>
         </is>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -329,8 +329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K51" headerRowCount="1">
-  <autoFilter ref="A1:K51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K52" headerRowCount="1">
+  <autoFilter ref="A1:K52"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Conflict of Interest</t>
+          <t>Conflict of Interest / Boss as Nominee</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Ethics + Procedural</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1260,27 +1260,27 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>MTNA Code of Ethics §3 (conflicts of interest); Nonprofit governance — board member conflicts; Robert's Rules — impartiality</t>
+          <t>MTNA Code of Ethics §3 (conflicts of interest); Nonprofit governance — board member conflicts; Robert's Rules — impartiality; NM nonprofit law — fiduciary duty</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Larry Blind sent the Teacher of the Year voting solicitation from his BUSINESS email (lblind@nmschoolofmusic.com) on behalf of PMTNM. The winning nominee, Tatiana, is employed by Larry's school (tatiana@nmschoolofmusic.com). Larry controls Tatiana's employment and used his position as PMTNM Past President to direct votes toward his own employee.</t>
+          <t>Larry Blind, an employee of NM School of Music owned by Tatiana Vetrinskaya, sent the Teacher of the Year voting solicitation from his NMSM business email (lblind@nmschoolofmusic.com) on behalf of PMTNM. The winning nominee was Tatiana Vetrinskaya (tatiana@nmschoolofmusic.com) — his employer and NMSM owner. Larry controls Tatiana's employment at NMSM while administering a process at PMTNM that determines whether she receives professional honors. He cannot be impartial about voting for or administering a process involving his boss. The email solicitation came from his business email address, blurring lines between his employer's resources and PMTNM business.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Oct 4, 2023 email from lblind@nmschoolofmusic.com soliciting TOTY votes (forwarded to Chip by Haewon Yang Sep 28, 2024); Tatiana's email address tatiana@nmschoolofmusic.com; Haewon thread 'FTC guidelines for MTNA and PMTNM' Sep 27-28, 2024</t>
+          <t>Oct 4, 2023 email from lblind@nmschoolofmusic.com soliciting TOTY votes (forwarded to Chip by Haewon Yang Sep 28, 2024); Tatiana's email address tatiana@nmschoolofmusic.com; NMSM organizational structure showing Tatiana as co-founder/owner; Haewon thread 'FTC guidelines for MTNA and PMTNM' Sep 27-28, 2024; Board Minutes and NMSM documentation showing Larry as NMSM employee</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Classic conflict of interest: supervisor voting-in a subordinate for a professional honor. Conducted via employer's email systems, suggesting NMSM resources used for PMTNM business.</t>
+          <t>An employee controlling a voting process that determines whether his boss receives professional honors. Maximum conflict of interest: Larry's employment and livelihood depend on Tatiana's goodwill, making impartial administration impossible. Used business email to conduct PMTNM business, blurring organizational boundaries.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Documented — Email evidence preserved</t>
+          <t>Email-verified — Relationship confirmed in NMSM documentation</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>TOTY Manipulation</t>
+          <t>TOTY Manipulation / Boss-as-Nominee</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Larry Blind; Tatiana Vetrinskaya (NMSM)</t>
+          <t>Larry Blind (NMSM employee); Tatiana Vetrinskaya (NMSM co-founder/owner)</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>MTNA Code of Ethics §3 (conflicts of interest); Nonprofit election integrity; Robert's Rules on impartiality</t>
+          <t>MTNA Code of Ethics §3 (conflicts of interest); Nonprofit election integrity; Robert's Rules on impartiality; Fiduciary duty of loyalty</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>2023 TOTY had two nominees: Terri Reck (nomination written by Jackie Zander-Wall, AMTA president) vs. Tatiana Vetrinskaya (nomination written by Larry Blind, her employer and NMSM director). Larry administered the vote from lblind@nmschoolofmusic.com and explicitly stated in his voting email: 'I decided to extend the nomination period' — a unilateral extension with no board approval. Chip's side-by-side analysis: Terri Reck's bio = 'dense list of information highlighting work done in the PMTNM community this past year.' Tatiana's bio (written by Larry) = 'storybook language throughout that causes emotional reactions, often unrelated to the question at hand. Highlights work done in NMSM.' Haewon Yang admitted voting for 'the person whose bio looked the best.' Tatiana won. No conflict of interest was disclosed by Larry.
+          <t>2023 TOTY had two nominees: Terri Reck (nomination written by Jackie Zander-Wall, AMTA president) vs. Tatiana Vetrinskaya (nomination written by Larry Blind, his BOSS and NMSM co-founder/owner). Larry administered the vote from his business email (lblind@nmschoolofmusic.com) and explicitly stated in his voting email: 'I decided to extend the nomination period' — a unilateral extension with no board approval. Larry's employment at NMSM depends on Tatiana's goodwill, making impartial administration impossible. Chip's side-by-side analysis: Terri Reck's bio = 'dense list of information highlighting work done in the PMTNM community this past year.' Tatiana's bio (written by Larry) = 'storybook language throughout that causes emotional reactions, often unrelated to the question at hand. Highlights work done in NMSM.' Haewon Yang admitted voting for 'the person whose bio looked the best.' Tatiana won. No conflict of interest was disclosed by Larry.
 VERBATIM FROM TATIANA'S ACTUAL SUBMISSION (submitted by lawrenceblind@msn.com, signed 9-30-23): Community service section = entirely NMSM activities. Closing line: 'business acumen... it is what I know she is most proud of.' [Note: 'business acumen' is not a PMTNM TOTY criterion.] Future-tense item listed under achievements: 'will present a workshop at 2023 PMTNM Conference' — event had not yet occurred at time of submission. Tatiana's listed email: tatiana@nmschoolofmusic.com (NMSM institutional address).
 VERBATIM FROM TERRI RECK'S ACTUAL SUBMISSION (submitted by zanderwall@gmail.com / Jacqueline Zander-Wall, signed 9/30/23): 47 years of teaching (1976–2023). Dalcroze certification across 6 institutions. 5 AMTA committee leadership roles. Harpsichord performances with SF Symphony, NM Symphony, NM Philharmonic. Students enrolled in PMTNM/MTNA programs. Music Bowl Chair for decades. Jewelry donated to PMTNM silent auctions.</t>
         </is>
@@ -3525,27 +3525,27 @@
     <row r="50" ht="72" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>G-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Oct 28, 2023 (approx.)</t>
+          <t>Oct 4, 2023 — Oct 9, 2023</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Unilateral Conference Decision</t>
+          <t>TOTY Process Monopoly — Employee Administers Vote on Boss's Nomination</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Governance + Conflict of Interest</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Governance + Procedural</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3555,67 +3555,129 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Standard nonprofit governance — significant organizational decisions require board approval and oversight; PMTNM Handbook (silent on conference programming authority, indicating governance gap); Fiduciary duty of loyalty — using organizational position and resources for personal/institutional benefit without disclosure</t>
+          <t>Nonprofit governance — conflicts of interest must be managed through recusal or independent administration; Robert's Rules of Order — procedural fairness; NM nonprofit law — fiduciary duty</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The decision appears to have been communicated directly to PMTNM member teachers in late October 2023. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure. The fact of NMSM students' participation in the 2023 PMTNM conference is independently corroborated in L-02 (ethics complaint filed Nov 14, 2023 and conference program documentation).</t>
+          <t>Larry Blind, an NMSM employee, held three simultaneous operational roles in the 2023 PMTNM Teacher of the Year process:
+(1) PMTNM PRESIDENT: Convened the voting process and set procedural rules (Oct 4, 2023 email: 'I decided to extend the nomination period')
+(2) WEBSITE ADMINISTRATOR/PLATFORM CONTROLLER: Managed the voting platform (Google Form link: https://forms.gle/LqpzibHS4V3tJVWK9), set the deadline unilaterally ('You must register your vote by Monday, October 9'), and controlled communications to voters
+(3) VOTE RECEIVER/CONTACT PERSON: Was the sole contact for voting questions ('Text me at 505-980-3941 if you have any questions or trouble voting')
+SIMULTANEOUSLY, his BOSS (Tatiana Vetrinskaya, NMSM co-founder/owner) was the winning TOTY nominee. Larry could not be impartial about administering a process that would determine whether his employer received professional honors. He had maximum incentive to ensure she won — his employment depends on her goodwill.
+NO RECUSAL PROCEDURE existed. No independent administrator was appointed. No conflict of interest was disclosed. The employee simply controlled the entire process involving his boss.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions; Independent corroboration: L-02 (Nov 14, 2023 ethics complaint to MTNA) and conference program/documentation from 2023 confirming NMSM student participation in PMTNM conference</t>
+          <t>Oct 4, 2023 email from lblind@nmschoolofmusic.com (PMTNM President, acting as sole administrator): 'I decided to extend the nomination period'; 'Please read the attached nomination forms...click on the link below to place your vote'; 'You must register your vote by Monday, October 9'; 'Text me at 505-980-3941 if you have any questions'; NMSM organizational documentation confirming Tatiana as owner, Larry as employee; L-01 documentation of boss-as-nominee relationship</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Unilateral decision-making by a president without board oversight. Direct self-dealing: using PMTNM's conference platform to promote his own school and student base. Absence of conflict-of-interest management or disclosure. Pattern-consistent with leadership's broader governance approach (see G-01: 'PMTNM does not function under any legal mandates'). Even if conference programming fell within the president's delegated authority, the absence of any disclosure mechanism for conflicts of interest represents governance failure.</t>
+          <t>A single individual — Larry Blind, NMSM employee — controlled every aspect of a voting process that determined whether his boss would receive organizational honors. No procedural safeguards existed: no recusal, no independent administration, no conflict disclosure. This is the definition of a rigged process. The monopolistic control combined with Larry's personal interest in the outcome (Tatiana is his employer) made fair administration impossible.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Documented via board minutes record (absence of decision) + independent corroboration via L-02 ethics complaint and conference documentation — Pattern consistent with unilateral leadership style</t>
+          <t>Procedurally-verified — monopolistic control of conflict-of-interest vote documented</t>
         </is>
       </c>
     </row>
     <row r="51" ht="72" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Oct 28, 2023 (approx.)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Unilateral Conference Decision</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Governance + Conflict of Interest</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Lawrence Blind</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Standard nonprofit governance — significant organizational decisions require board approval and oversight; PMTNM Handbook (silent on conference programming authority, indicating governance gap); Fiduciary duty of loyalty — using organizational position and resources for personal/institutional benefit without disclosure</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Larry Blind, as PMTNM president, unilaterally decided to invite non-PMTNM students from his own school (NM School of Music) to participate in a PMTNM conference benefit concert scheduled for November 12, 2023. The decision appears to have been communicated directly to PMTNM member teachers in late October 2023. No board vote was recorded. No board meeting minutes document board discussion or approval of this programming decision. The handbook is silent on conference programming authority, leaving unclear whether this was within the president's delegated power or required board approval. Regardless, the decision involved a direct conflict of interest (his own school) that was neither disclosed nor managed through any recusal or conflict-of-interest procedure. The fact of NMSM students' participation in the 2023 PMTNM conference is independently corroborated in L-02 (ethics complaint filed Nov 14, 2023 and conference program documentation).</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Board meeting minutes from Oct/Nov 2023 — no documentation of board discussion, motion, or vote regarding conference programming or NMSM student participation; PMTNM 2004 Handbook — contains no section defining decision-making authority for conference programming or board approval requirements for conference content decisions; Independent corroboration: L-02 (Nov 14, 2023 ethics complaint to MTNA) and conference program/documentation from 2023 confirming NMSM student participation in PMTNM conference</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Unilateral decision-making by a president without board oversight. Direct self-dealing: using PMTNM's conference platform to promote his own school and student base. Absence of conflict-of-interest management or disclosure. Pattern-consistent with leadership's broader governance approach (see G-01: 'PMTNM does not function under any legal mandates'). Even if conference programming fell within the president's delegated authority, the absence of any disclosure mechanism for conflicts of interest represents governance failure.</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Documented via board minutes record (absence of decision) + independent corroboration via L-02 ethics complaint and conference documentation — Pattern consistent with unilateral leadership style</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="72" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>L-08</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Nov 8, 2024; Nov 7, 2025</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Unmanaged Conflict of Interest / Proxy Voting</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Governance + Conflict of Interest</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Marcus York; Lawrence Blind (as supervisor/authority)</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Nonprofit governance — voting members with conflicts of interest must be subject to formal conflict-of-interest procedures (disclosure, recusal, abstention); PMTNM governance standards requiring impartial board member conduct; Proxy voting prohibition under standard nonprofit law; Fiduciary duty of loyalty</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Marcus York, an employee of NM School of Music (controlled by Lawrence Blind as owner/director), voted on critical financial matters at PMTNM board meetings while under employment relationship with Blind — with no formal conflict-of-interest procedure to manage or mitigate that relationship. Although PMTNM members likely knew York worked for Larry, the board took no formal action to address this conflict:
 NOVEMBER 8, 2024 BOARD MEETING (Blind was President):
@@ -3631,17 +3693,17 @@
 THE CONFLICT: York was voting (Nov 2024) on matters affecting the organization while being employed by someone with authority over him, while also serving on a committee chaired by that same person that controlled officer succession. NMSM's organizational authority structure gave Blind direct control over York's employment, creating the classic hallmark of proxy voting: a voting member whose interests are materially affected by someone else's authority.</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Board Minutes Nov 8, 2024: 'With a motion by Marcus York and a second by Sharon Kunitz the Treasurer's current financial report was unanimously approved'; 'Upon a motion by Janna Warren with a second by Marcus York [budget] was declared in order'; Meeting location: 'New Mexico School of Music, Albuquerque'; Board Minutes Nov 7, 2025: 'Nominating Committee Slate of Officers for 2026-2027: Chair Lawrence Blind thanked his committee members Astrid Groth and Marcus York'; Marcus York's NMSM email/employment confirmed in July 2024 communication identifying him as associated with 'the School of Music'</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>A voting board member whose employment is controlled by someone else (Blind) voted on financial matters while serving on a succession-control committee chaired by that same person. Although people knew York worked for Larry, the board took no formal action to manage this conflict — no required disclosure, no recusal procedure, no abstention protocol. PMTNM has no written conflict-of-interest policy. This pattern extends Blind's demonstrated use of organizational positions to embed people aligned with his interests — similar to how he controlled the 2023 TOTY vote through his employee Tatiana. York's situation represents proxy-voting conditions: voting on matters affecting the organization while under employment relationship with an interested party, with no organizational safeguards.</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Board minutes verified — unmanaged employment conflict documented across voting and committee roles</t>
         </is>
@@ -3661,7 +3723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4199,7 +4261,7 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -4209,194 +4271,194 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TOTY manipulation: used business email to solicit votes for his own employee Tatiana</t>
+          <t>TOTY conflict of interest: administering voting process for his BOSS Tatiana (NMSM owner) — can't be impartial when his employment depends on her goodwill</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>G-05</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
+          <t>TOTY process monopoly: controlled nomination deadline, voting platform, and all communications while his boss was the nominee — no recusal, no independent administration</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>L-02</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>PMTNM website used to promote NM School of Music during his presidency</t>
+          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
+          <t>PMTNM website used to promote NM School of Music during his presidency</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
+          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
+          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
+          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
+          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
+          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Larry Blind (Past President / NMSM Owner)</t>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>L-07</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Triple role conflict Nov 7, 2025: Past President/informal advisor to Sharon + Nominating Committee Chair + Parliamentarian — three undisclosed simultaneous conflicting roles; advisory channel used morning of Nov 7 to coordinate meeting strategy against VP (10:00 AM email to Sharon only: 'getting someone to the point of a motion can be challenging')</t>
+          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>L-07</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Triple role conflict Nov 7, 2025: Past President/informal advisor to Sharon + Nominating Committee Chair + Parliamentarian — three undisclosed simultaneous conflicting roles; advisory channel used morning of Nov 7 to coordinate meeting strategy against VP (10:00 AM email to Sharon only: 'getting someone to the point of a motion can be challenging')</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
           <t>Marcus York (Board Member / NMSM Employee)</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>L-08</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Voted on financial matters (Nov 2024) while employed by Larry Blind; served on Blind-chaired Nominating Committee (Nov 2024–2025) — no formal conflict-of-interest procedure invoked; unmanaged proxy voting situation due to Blind's employment authority over York</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (Former President)</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -4408,12 +4470,12 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
+          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4487,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
+          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4504,12 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
+          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
         </is>
       </c>
     </row>
@@ -4459,12 +4521,12 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
         </is>
       </c>
     </row>
@@ -4476,29 +4538,29 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz (Former President)</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
           <t>M-05</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>VP excluded from board packet mailing; VP's agenda items not addressed</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4572,12 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4527,10 +4589,27 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Brian Shepard (MTNA CEO)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
           <t>E-03</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Sep 2025 + Dec 2025 affiliate complaints — deferred entirely to affiliate self-governance</t>
         </is>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Conflict of Interest / Bias</t>
+          <t>Conflict of Interest / Bias / Hostile Escalation</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1431,27 +1431,31 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Robert's Rules of Order — Parliamentarian must be impartial; Due process rights of meeting participants</t>
+          <t>Robert's Rules of Order — Parliamentarian must be impartial; Due process rights of meeting participants; Fiduciary duty not to use authority for personal disputes</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Larry Blind sent a hostile email to Chip on Nov 5-6, 2025 — the night before the board meeting — calling Chip's communication 'offensive, disrespectful, and does not deserve a response.' Larry then served as Parliamentarian at the Nov 7 meeting. The minutes attribute a parliamentary 'time call' to him that does not appear in the recording.</t>
+          <t>ESCALATION SEQUENCE (Nov 5-7, 2025):
+(1) NOV 5, 6:18 PM — Chip sends professional governance email on existing 'Budget Committee REMINDER' thread. Documents serious compliance issues (5+ year filing gap) and respectfully asks Jeanne to retire with dignity. Explicitly states 'This is not an ultimatum.' References 'heavy and dark conversations' in context of scrutinizing documented failures — professional language for governance accountability.
+(2) NOV 5, 9:08 PM — DELIBERATE ESCALATION: Instead of responding on the Budget Committee thread, Larry creates a SEPARATE EMAIL THREAD with only Chip's name as subject line: 'Willis Glen Miller, III.' In this new thread (broadcast to full board: Sharon, Jeanne, Laura, Heather), Larry calls Chip's governance concerns 'offensive, disrespectful, and does not deserve a response.' This is not a reply to the budget/compliance issues — it's a personal attack designed to discredit Chip before the board meeting. The separate thread structure shows intentional escalation from procedural discussion to personal attack.
+(3) NOV 7, MORNING — Chip discovers Larry's hostile email the morning of the board meeting.
+(4) NOV 7, BOARD MEETING — Larry serves as Parliamentarian despite his demonstrated personal animus toward the VP. Minutes attribute a parliamentary 'time call' to him that does not appear in the audio recording. Larry uses his parliamentary authority to rule against Chip's no-confidence motion — the motion Chip raised after being personally attacked by Larry the night before.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Nov 5-6 email (Larry → Chip, CC Sharon, Jeanne, Laura); Nov 7 Board Meeting Audio Recording; INTERNAL_Minutes Review; Proposed Corrections to Minutes</t>
+          <t>Nov 5, 6:18 PM email from Chip (on Budget Committee REMINDER thread): documents compliance issues, professional tone, explicit disclaimer 'This is not an ultimatum'; Nov 5, 9:08 PM email from Larry (NEW THREAD titled 'Willis Glen Miller, III', CC'd to Sharon/Jeanne/Laura/Heather): 'offensive, disrespectful, and does not deserve a response'; Nov 6 morning: Chip's discovery of hostile email sent night before meeting; Nov 7 Board Meeting Audio Recording showing no time call; Nov 7 Minutes recording fabricated 'time call'; INTERNAL_Minutes Review; Proposed Corrections to Minutes</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Parliamentarian's demonstrated bias toward the VP directly undermines procedural fairness of the meeting. The fabricated 'time call' in the minutes may have been used to cut off Chip's presentation.</t>
+          <t>A board member personally attacked the VP in a separate, emphasized thread broadcast to the full board the night before a meeting. The next morning, that same person served as the neutral Parliamentarian and used parliamentary authority to rule against the VP's motion. The 'time call' recorded in the minutes does not appear in the audio — suggesting it was fabricated to justify the ruling. This is not impartiality; it's weaponization of a procedural role in service of a personal dispute.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Audio-verified — Strong procedural violation</t>
+          <t>Timeline-verified, Audio-verified, Thread-structure-verified — Deliberate escalation from governance issue to personal attack to abuse of authority</t>
         </is>
       </c>
     </row>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -329,8 +329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K52" headerRowCount="1">
-  <autoFilter ref="A1:K52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Violations" displayName="Violations" ref="A1:K53" headerRowCount="1">
+  <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3713,6 +3713,64 @@
         </is>
       </c>
     </row>
+    <row r="53" ht="72" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Sep 11–12, 2025</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>EST Dismissal + Refusal to Clarify</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>PMTNM Handbook EST duties — support organizational mission; Professional responsibility to engage colleagues in good faith</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>VP Chip Miller forwarded the MTNA Foundation newsletter to the board. Jeanne responded directly to the VP with a dismissive characterization: 'Boring and irrelevant to most of us.' The VP immediately requested clarification, sending a polite follow-up: 'Can you clarify?' Jeanne never responded — she did not defend the characterization, explain her objection to the content, or engage the VP in dialogue. She simply ignored the request for clarification.
+This establishes a pattern: (1) Jeanne dismisses the VP's initiatives; (2) When challenged respectfully to explain, she does not respond; (3) Silence becomes a tool to delegitimize without defending. Sharon Kunitz was CC'd on the clarification request and also said nothing. Three weeks later (Oct 2), Sharon publicly praised the same Foundation content, directly contradicting her earlier silence when Jeanne dismissed it. The silence-then-contradiction pattern shows that Jeanne's dismissal was not standard leadership disagreement — it was an undefended attack that others (Sharon) later contradicted.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Email Sep 11, 2025 (Jeanne to VP: 'Boring and irrelevant to most of us'); Email Sep 12, 2025 12:44 AM (VP to Jeanne + Sharon: 'Can you clarify?'); Email Oct 2, 2025 (Sharon to same thread: 'Great article on Foundation! Beautifully written and presented')</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>EST using dismissive language toward organizational mission (MTNA Foundation) without explanation or engagement. Pattern: attack without defending, silence when asked to clarify. Establishes that VP's professional judgment was not respected by leadership, and that EST would use dismissal rather than dialogue to manage disagreement.</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Documented — establishes pattern of non-engagement preceding escalation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3727,7 +3785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3811,12 +3869,12 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>F-14</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Unauthorized spending Jul–Nov 2025: 4+ months into fiscal year with no approved budget; continued storage, honorarium, and operating expenses without board authorization</t>
+          <t>Foundation dismissal + refusal to clarify — Called MTNA Foundation newsletter 'Boring and irrelevant to most of us' to VP; did not respond when VP asked for clarification; pattern of attack without engagement</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3886,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-14</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CPA report 5 months late; budget adopted after fiscal year began</t>
+          <t>Unauthorized spending Jul–Nov 2025: 4+ months into fiscal year with no approved budget; continued storage, honorarium, and operating expenses without board authorization</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3903,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial report 'approved' in minutes — no motion/vote in recording</t>
+          <t>CPA report 5 months late; budget adopted after fiscal year began</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3920,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>F-05</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Sole control of all bank accounts, CPA contact, financial records</t>
+          <t>Financial report 'approved' in minutes — no motion/vote in recording</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3937,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Personal furniture stored in PMTNM storage unit — admitted before attorney</t>
+          <t>Sole control of all bank accounts, CPA contact, financial records</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3954,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EST honorarium $1,750/yr with no performance measures</t>
+          <t>Personal furniture stored in PMTNM storage unit — admitted before attorney</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3971,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>F-08</t>
+          <t>F-07</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Stated Teri Reck 'hadn't contributed' — potentially inaccurate/defamatory</t>
+          <t>EST honorarium $1,750/yr with no performance measures</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3988,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>F-09</t>
+          <t>F-08</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Blocked membership booklet: '90 cents to mail' vs. 30%+ budget on storage</t>
+          <t>Stated Teri Reck 'hadn't contributed' — potentially inaccurate/defamatory</t>
         </is>
       </c>
     </row>
@@ -3947,12 +4005,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>F-10</t>
+          <t>F-09</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Storage unit: $4,600 actual vs. $3,000 budgeted — 53% overrun; even Larry questioned it</t>
+          <t>Blocked membership booklet: '90 cents to mail' vs. 30%+ budget on storage</t>
         </is>
       </c>
     </row>
@@ -3964,12 +4022,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-10</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2025 TOTY: Three attempts to nullify Terri Reck nomination; directly contradicted by board members</t>
+          <t>Storage unit: $4,600 actual vs. $3,000 budgeted — 53% overrun; even Larry questioned it</t>
         </is>
       </c>
     </row>
@@ -3981,12 +4039,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Auditing Committee unilaterally eliminated — written admission to Kathy Black: 'It has not had an Auditing Comm. since hiring a CPA'</t>
+          <t>2025 TOTY: Three attempts to nullify Terri Reck nomination; directly contradicted by board members</t>
         </is>
       </c>
     </row>
@@ -3998,12 +4056,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Board meeting minutes stored in storage unit (with personal furniture); attorney demand for records refused as 'not physically possible'; no online banking</t>
+          <t>Auditing Committee unilaterally eliminated — written admission to Kathy Black: 'It has not had an Auditing Comm. since hiring a CPA'</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4073,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Minutes falsification (Nov 7, 2025): budget 'approved as presented' — audio shows no motion, second, or vote; minutes fabricated to lock in unauthorized $1,750 honorarium</t>
+          <t>Board meeting minutes stored in storage unit (with personal furniture); attorney demand for records refused as 'not physically possible'; no online banking</t>
         </is>
       </c>
     </row>
@@ -4032,12 +4090,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>F-15</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>No spring board meeting or budget committee in spring 2025; budget prepared 4 months into fiscal year — handbook requires spring preparation</t>
+          <t>Minutes falsification (Nov 7, 2025): budget 'approved as presented' — audio shows no motion, second, or vote; minutes fabricated to lock in unauthorized $1,750 honorarium</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4107,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>F-16</t>
+          <t>F-15</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>NM Secretary of State annual report overdue since Nov 15, 2019 — 6+ year lapse; internal PMTNM document claims 'all required documents have been filed' — direct contradiction</t>
+          <t>No spring board meeting or budget committee in spring 2025; budget prepared 4 months into fiscal year — handbook requires spring preparation</t>
         </is>
       </c>
     </row>
@@ -4066,12 +4124,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-16</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NM AG registration (2018, 2023, 2024): sole responsible party for all 5 financial functions all three years; PMTNM address = personal home all three years; 'no solicitation' false all three years; eleven-year pattern confirmed (2014-2024)</t>
+          <t>NM Secretary of State annual report overdue since Nov 15, 2019 — 6+ year lapse; internal PMTNM document claims 'all required documents have been filed' — direct contradiction</t>
         </is>
       </c>
     </row>
@@ -4083,12 +4141,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>F-13</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>VIP Staffing contract (Oct 23, 2025): commercial staffing agreement executed without board authorization; no mention in Nov 7 minutes</t>
+          <t>NM AG registration (2018, 2023, 2024): sole responsible party for all 5 financial functions all three years; PMTNM address = personal home all three years; 'no solicitation' false all three years; eleven-year pattern confirmed (2014-2024)</t>
         </is>
       </c>
     </row>
@@ -4100,12 +4158,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-13</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ON RECORD Oct 7, 2025: 'PMTNM does not function under any legal mandates!'</t>
+          <t>VIP Staffing contract (Oct 23, 2025): commercial staffing agreement executed without board authorization; no mention in Nov 7 minutes</t>
         </is>
       </c>
     </row>
@@ -4117,12 +4175,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Nov 7, 2025: vote of no confidence motion made formally; Larry controlled the second process; Sharon adjourned immediately after motion died; Grealish (subject of motion) had direct conflict of interest; escalation to MTNA/attorney Nov 5 preceded coordination</t>
+          <t>ON RECORD Oct 7, 2025: 'PMTNM does not function under any legal mandates!'</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4192,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Minutes: '10-min limit' — Sharon's own email says 15 min</t>
+          <t>Nov 7, 2025: vote of no confidence motion made formally; Larry controlled the second process; Sharon adjourned immediately after motion died; Grealish (subject of motion) had direct conflict of interest; escalation to MTNA/attorney Nov 5 preceded coordination</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4209,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Minutes: financial report 'approved' — no vote in recording</t>
+          <t>Minutes: '10-min limit' — Sharon's own email says 15 min</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4226,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Minutes: 'time called by Parliamentarian' — not in recording</t>
+          <t>Minutes: financial report 'approved' — no vote in recording</t>
         </is>
       </c>
     </row>
@@ -4185,12 +4243,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Minutes: VP report 'not submitted' — contradicted by documentary evidence</t>
+          <t>Minutes: 'time called by Parliamentarian' — not in recording</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4260,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Handbook withheld for 6 months; falsely claimed online availability</t>
+          <t>Minutes: VP report 'not submitted' — contradicted by documentary evidence</t>
         </is>
       </c>
     </row>
@@ -4219,12 +4277,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Nov 7 minutes distributed 4 months late — after petition filed</t>
+          <t>Handbook withheld for 6 months; falsely claimed online availability</t>
         </is>
       </c>
     </row>
@@ -4236,12 +4294,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025 minutes not distributed for 7 months</t>
+          <t>Nov 7 minutes distributed 4 months late — after petition filed</t>
         </is>
       </c>
     </row>
@@ -4253,29 +4311,29 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Spring 2025 minutes not distributed for 7 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Jeanne Grealish (EST)</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
           <t>R-04</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Official member list ('PMTNM. LIST AND EMAIL ADDRESSES') lists Sharon Kunitz as NCTM — contradicted by official MTNA data showing no NCTM designation; pattern of inaccurate record-keeping</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>L-01</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>TOTY conflict of interest: administering voting process for his BOSS Tatiana (NMSM owner) — can't be impartial when his employment depends on her goodwill</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4345,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>G-05</t>
+          <t>L-01</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>TOTY process monopoly: controlled nomination deadline, voting platform, and all communications while his boss was the nominee — no recusal, no independent administration</t>
+          <t>TOTY conflict of interest: administering voting process for his BOSS Tatiana (NMSM owner) — can't be impartial when his employment depends on her goodwill</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4362,12 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>G-05</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
+          <t>TOTY process monopoly: controlled nomination deadline, voting platform, and all communications while his boss was the nominee — no recusal, no independent administration</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4379,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>L-02</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>PMTNM website used to promote NM School of Music during his presidency</t>
+          <t>NMSM students at PMTNM conference — using nonprofit event to market his school</t>
         </is>
       </c>
     </row>
@@ -4338,12 +4396,12 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
+          <t>PMTNM website used to promote NM School of Music during his presidency</t>
         </is>
       </c>
     </row>
@@ -4355,12 +4413,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
+          <t>Served as Parliamentarian after sending hostile email to VP — compromised impartiality; Nov 7 pre-meeting email: 'getting someone to the point of a motion can be challenging' — telegraphed plan to prevent no-confidence motion; rejected Chip's RROO-compliant anonymous voting in favor of text-to-one-phone non-anonymous method; ran the motion vote publicly with Grealish in the room</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4430,12 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
+          <t>TOTY 2023: solicited votes from NMSM email; winner is NMSM co-founder/employee; extended deadline unilaterally</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4447,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
+          <t>NMSM biography: 'perform internationally' misleading; Carnegie Hall framing unsubstantiated; uncredentialed faculty</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4464,12 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
+          <t>NMSM employee handbook invoked to block MTNA ethics investigation</t>
         </is>
       </c>
     </row>
@@ -4423,12 +4481,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
+          <t>First ethics complaint (Nov 2023) — MTNA took no action on conference abuse</t>
         </is>
       </c>
     </row>
@@ -4440,46 +4498,46 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>L-07</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Triple role conflict Nov 7, 2025: Past President/informal advisor to Sharon + Nominating Committee Chair + Parliamentarian — three undisclosed simultaneous conflicting roles; advisory channel used morning of Nov 7 to coordinate meeting strategy against VP (10:00 AM email to Sharon only: 'getting someone to the point of a motion can be challenging')</t>
+          <t>TOTY 2023: no conflict disclosure; winning bio emphasized NMSM not PMTNM community service</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
+          <t>Larry Blind (NMSM Employee / PMTNM President)</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>L-07</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Triple role conflict Nov 7, 2025: Past President/informal advisor to Sharon + Nominating Committee Chair + Parliamentarian — three undisclosed simultaneous conflicting roles; advisory channel used morning of Nov 7 to coordinate meeting strategy against VP (10:00 AM email to Sharon only: 'getting someone to the point of a motion can be challenging')</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
           <t>Marcus York (Board Member / NMSM Employee)</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>L-08</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Voted on financial matters (Nov 2024) while employed by Larry Blind; served on Blind-chaired Nominating Committee (Nov 2024–2025) — no formal conflict-of-interest procedure invoked; unmanaged proxy voting situation due to Blind's employment authority over York</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Sharon Kunitz (Former President)</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4549,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
+          <t>Conflict of interest: receives scholarship money controlled by Grealish's sole sign-off</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4566,12 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
+          <t>Reinforced financial records refusal — falsely characterized VP's duties</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4583,12 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
+          <t>Committed on record to place agenda items on Nov 7 agenda — broke commitment</t>
         </is>
       </c>
     </row>
@@ -4542,12 +4600,12 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+          <t>11-month pattern: blocked financial access, dismissed budget process, broke agenda commitment</t>
         </is>
       </c>
     </row>
@@ -4559,29 +4617,29 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Silent when Jeanne said Foundation article was 'Boring and irrelevant' — then praised it 21 days later</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Sharon Kunitz (Former President)</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
           <t>M-05</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>VP excluded from board packet mailing; VP's agenda items not addressed</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Brian Shepard (MTNA CEO)</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4651,12 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+          <t>Nov 2023 ethics complaint — no action</t>
         </is>
       </c>
     </row>
@@ -4610,10 +4668,27 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2024 ethics complaint re: Evan/Tatiana/NMSM — acknowledged, no action</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>Brian Shepard (MTNA CEO)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
           <t>E-03</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Sep 2025 + Dec 2025 affiliate complaints — deferred entirely to affiliate self-governance</t>
         </is>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>EST Dismissal + Refusal to Clarify</t>
+          <t>EST Public Dismissal of VP Communications + Refusal to Clarify</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3734,9 +3734,9 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3746,28 +3746,29 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>PMTNM Handbook EST duties — support organizational mission; Professional responsibility to engage colleagues in good faith</t>
+          <t>PMTNM Handbook EST duties — support organizational mission and VP authority; Professional responsibility to engage in good faith; MTNA Code of Ethics §5 (Professional Conduct)</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>VP Chip Miller forwarded the MTNA Foundation newsletter to the board. Jeanne responded directly to the VP with a dismissive characterization: 'Boring and irrelevant to most of us.' The VP immediately requested clarification, sending a polite follow-up: 'Can you clarify?' Jeanne never responded — she did not defend the characterization, explain her objection to the content, or engage the VP in dialogue. She simply ignored the request for clarification.
-This establishes a pattern: (1) Jeanne dismisses the VP's initiatives; (2) When challenged respectfully to explain, she does not respond; (3) Silence becomes a tool to delegitimize without defending. Sharon Kunitz was CC'd on the clarification request and also said nothing. Three weeks later (Oct 2), Sharon publicly praised the same Foundation content, directly contradicting her earlier silence when Jeanne dismissed it. The silence-then-contradiction pattern shows that Jeanne's dismissal was not standard leadership disagreement — it was an undefended attack that others (Sharon) later contradicted.</t>
+          <t>VP Chip Miller sent the MTNA Foundation newsletter directly to all PMTNM membership via Constant Contact (email marketing platform), paid for by the VP personally, as part of organizational communication to the membership. Jeanne responded publicly with a dismissive characterization: 'Boring and irrelevant to most of us.' This response was not a private aside — it was made to the VP in the context of a membership mailing and used language ('most of us') that claimed to speak for the organization.
+The VP immediately requested clarification, sending a polite follow-up directly to Jeanne: 'Can you clarify?' Jeanne never responded — she did not defend the characterization, explain her objection to the content, or engage the VP in dialogue. She simply ignored the request.
+This establishes a pattern of public delegitimization without defense: (1) VP invests personal funds in organization's mission communication; (2) EST publicly dismisses it to the VP; (3) EST claims to speak for membership ('most of us'); (4) When asked to explain, EST refuses to engage. Sharon Kunitz was CC'd on the clarification request and said nothing. Three weeks later (Oct 2), Sharon publicly praised the same Foundation content to the same thread, directly contradicting her earlier silence when Jeanne dismissed it. The silence-then-contradiction pattern shows that Jeanne's dismissal was not standard leadership disagreement — it was an undefended public attack that others (Sharon) later contradicted, suggesting it reflected EST's personal opinion, not organizational consensus.</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Email Sep 11, 2025 (Jeanne to VP: 'Boring and irrelevant to most of us'); Email Sep 12, 2025 12:44 AM (VP to Jeanne + Sharon: 'Can you clarify?'); Email Oct 2, 2025 (Sharon to same thread: 'Great article on Foundation! Beautifully written and presented')</t>
+          <t>Email Sep 11, 2025 (Jeanne: 'Boring and irrelevant to most of us' — response to Constant Contact membership mailing); Email Sep 12, 2025 12:44 AM (VP to Jeanne + Sharon: 'Can you clarify?' — request for explanation, ignored); Email Oct 2, 2025 (Sharon to same thread: 'Great article on Foundation! Beautifully written and presented' — contradicting Jeanne's earlier dismissal); Constant Contact record showing VP-paid mailing to known PMTNM membership list</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>EST using dismissive language toward organizational mission (MTNA Foundation) without explanation or engagement. Pattern: attack without defending, silence when asked to clarify. Establishes that VP's professional judgment was not respected by leadership, and that EST would use dismissal rather than dialogue to manage disagreement.</t>
+          <t>EST publicly delegitimizing VP's organizational communications to the membership while claiming to speak for 'most of us' (the membership), then refusing to defend or clarify the dismissal when directly challenged. Establishes that EST did not respect VP's authority or judgment, and used dismissive language designed to undermine VP's credibility with the membership. Pattern of public attack without willingness to defend or engage.</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Documented — establishes pattern of non-engagement preceding escalation</t>
+          <t>Documented — established pattern of attacks on VP credibility and authority</t>
         </is>
       </c>
     </row>

--- a/PMTNM_Violations_Database.xlsx
+++ b/PMTNM_Violations_Database.xlsx
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>EST Public Dismissal of VP Communications + Refusal to Clarify</t>
+          <t>EST Dismissal of VP Initiative + Refusal to Engage</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3734,9 +3734,9 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3746,29 +3746,29 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>PMTNM Handbook EST duties — support organizational mission and VP authority; Professional responsibility to engage in good faith; MTNA Code of Ethics §5 (Professional Conduct)</t>
+          <t>PMTNM Handbook EST duties — support organizational mission and VP authority; Professional responsibility to engage colleagues in good faith; MTNA Code of Ethics §5 (Professional Conduct)</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>VP Chip Miller sent the MTNA Foundation newsletter directly to all PMTNM membership via Constant Contact (email marketing platform), paid for by the VP personally, as part of organizational communication to the membership. Jeanne responded publicly with a dismissive characterization: 'Boring and irrelevant to most of us.' This response was not a private aside — it was made to the VP in the context of a membership mailing and used language ('most of us') that claimed to speak for the organization.
-The VP immediately requested clarification, sending a polite follow-up directly to Jeanne: 'Can you clarify?' Jeanne never responded — she did not defend the characterization, explain her objection to the content, or engage the VP in dialogue. She simply ignored the request.
-This establishes a pattern of public delegitimization without defense: (1) VP invests personal funds in organization's mission communication; (2) EST publicly dismisses it to the VP; (3) EST claims to speak for membership ('most of us'); (4) When asked to explain, EST refuses to engage. Sharon Kunitz was CC'd on the clarification request and said nothing. Three weeks later (Oct 2), Sharon publicly praised the same Foundation content to the same thread, directly contradicting her earlier silence when Jeanne dismissed it. The silence-then-contradiction pattern shows that Jeanne's dismissal was not standard leadership disagreement — it was an undefended public attack that others (Sharon) later contradicted, suggesting it reflected EST's personal opinion, not organizational consensus.</t>
+          <t>VP Chip Miller sent the MTNA Foundation newsletter directly to all PMTNM membership via Constant Contact (email marketing platform), paid for by the VP personally, as organizational communication to the membership. Jeanne received the mailing and responded directly to the VP with a dismissive characterization: 'Boring and irrelevant to most of us.' This private response to the VP dismissed an organizational initiative that the VP had funded personally.
+The VP immediately requested clarification, sending a polite follow-up directly to Jeanne: 'Can you clarify?' Jeanne never responded — she did not defend the characterization, explain her objection to the content, or engage the VP in dialogue. She simply ignored the request for explanation.
+This establishes a pattern: (1) VP invests personal funds to communicate organizational mission to membership; (2) EST dismisses the initiative to the VP, claiming to speak for membership ('most of us'); (3) When asked to explain, EST refuses to engage. Sharon Kunitz was CC'd on the clarification request and said nothing. Three weeks later (Oct 2), Sharon publicly praised the same Foundation content to the same thread, directly contradicting her earlier silence when Jeanne dismissed it. The contradiction shows that Jeanne's dismissal was not shared organizational concern — it appeared to be EST's personal opinion, yet EST would not defend it when challenged.</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Email Sep 11, 2025 (Jeanne: 'Boring and irrelevant to most of us' — response to Constant Contact membership mailing); Email Sep 12, 2025 12:44 AM (VP to Jeanne + Sharon: 'Can you clarify?' — request for explanation, ignored); Email Oct 2, 2025 (Sharon to same thread: 'Great article on Foundation! Beautifully written and presented' — contradicting Jeanne's earlier dismissal); Constant Contact record showing VP-paid mailing to known PMTNM membership list</t>
+          <t>Email Sep 11, 2025 (Jeanne to VP: 'Boring and irrelevant to most of us' — dismissive response to Foundation mailing); Email Sep 12, 2025 12:44 AM (VP to Jeanne + Sharon: 'Can you clarify?' — request for explanation, ignored); Email Oct 2, 2025 (Sharon to same thread: 'Great article on Foundation! Beautifully written and presented' — contradicting Jeanne's dismissal); Constant Contact record showing VP-paid mailing to known PMTNM membership list</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>EST publicly delegitimizing VP's organizational communications to the membership while claiming to speak for 'most of us' (the membership), then refusing to defend or clarify the dismissal when directly challenged. Establishes that EST did not respect VP's authority or judgment, and used dismissive language designed to undermine VP's credibility with the membership. Pattern of public attack without willingness to defend or engage.</t>
+          <t>EST dismissing VP's organizational initiative (funded by VP personally) and refusing to defend or clarify that dismissal when directly challenged. Establishes that EST did not respect VP's authority or judgment, and pattern of attack without willingness to engage. Suggests EST's concerns were personal opinion, not organizational consensus (given Sharon's later contradiction).</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Documented — established pattern of attacks on VP credibility and authority</t>
+          <t>Documented — establishes pattern of non-engagement with VP</t>
         </is>
       </c>
     </row>
